--- a/LocalizationStringTable.xlsx
+++ b/LocalizationStringTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\업무\2026년\6월\0630\00. LocalizationStringTable\LocalizationStringTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CocosProject\FortuneofRaSecretTreasure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9938F4D-A058-4D1D-9846-6864F8CB9350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C7D589-1394-4BAE-979C-F3BC498EEC86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{01A4B2FD-E311-460F-AD11-CF593C8E3E63}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{01A4B2FD-E311-460F-AD11-CF593C8E3E63}"/>
   </bookViews>
   <sheets>
     <sheet name="FortuneOfRA_SecretTreasure" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="742">
   <si>
     <t>Key</t>
   </si>
@@ -1450,1518 +1450,1135 @@
     <t>UI_POPUP_PAY_PAGE1_CONTENTS1</t>
   </si>
   <si>
-    <t>Before the base game reel spin initiates, a number of positions are replaced with any one symbol except  &lt;Sprite=10&gt;  and  &lt;Sprite=11&gt; . 
+    <t>UI_POPUP_PAY_PAGE2_TITLE1</t>
+  </si>
+  <si>
+    <t>WILD/TRAIL</t>
+  </si>
+  <si>
+    <t>百搭 / 轨迹</t>
+  </si>
+  <si>
+    <t>百搭 / 軌跡</t>
+  </si>
+  <si>
+    <t>Wild / Trail</t>
+  </si>
+  <si>
+    <t>ワイルド／トレイル</t>
+  </si>
+  <si>
+    <t>ไวลด์ / เทรล</t>
+  </si>
+  <si>
+    <t>UI_POPUP_PAY_PAGE2_CONTENTS1</t>
+  </si>
+  <si>
+    <t>UI_POPUP_PAY_PAGE2_TITLE2</t>
+  </si>
+  <si>
+    <t>UI_POPUP_PAY_PAGE2_CONTENTS2</t>
+  </si>
+  <si>
+    <t>SHOU BONUS</t>
+  </si>
+  <si>
+    <t>寿奖励</t>
+  </si>
+  <si>
+    <t>壽獎勵</t>
+  </si>
+  <si>
+    <t>Shou Bonus</t>
+  </si>
+  <si>
+    <t>ショウボーナス</t>
+  </si>
+  <si>
+    <t>โบนัสโชว</t>
+  </si>
+  <si>
+    <t>UNEXPECTED LUCKY</t>
+  </si>
+  <si>
+    <t>意外好运</t>
+  </si>
+  <si>
+    <t>意外好運</t>
+  </si>
+  <si>
+    <t>Di-inaasahang Suwerte</t>
+  </si>
+  <si>
+    <t>思いがけない幸運</t>
+  </si>
+  <si>
+    <t>โชคที่ไม่คาดคิด</t>
+  </si>
+  <si>
+    <t>UI_POPUP_PAY_PAGE4_TITLE1</t>
+  </si>
+  <si>
+    <t>UI_POPUP_PAY_PAGE4_CONTENTS1</t>
+  </si>
+  <si>
+    <t>UI_POPUP_PAY_PAGE4_CONTENTS2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_POPUP_PAY_PAGE4_CONTENTS3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FEATURE SELECTION</t>
+  </si>
+  <si>
+    <t>功能选择</t>
+  </si>
+  <si>
+    <t>功能選擇</t>
+  </si>
+  <si>
+    <t>Pagpili ng Feature</t>
+  </si>
+  <si>
+    <t>フィーチャー選択</t>
+  </si>
+  <si>
+    <t>การเลือกฟีเจอร์</t>
+  </si>
+  <si>
+    <t>UI_POPUP_PAY_PAGE5_TITLE1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_POPUP_PAY_PAGE5_CONTENTS1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FREE GAMES BONUS</t>
+  </si>
+  <si>
+    <t>免费游戏奖励</t>
+  </si>
+  <si>
+    <t>免費遊戲獎勵</t>
+  </si>
+  <si>
+    <t>Free Games Bonus</t>
+  </si>
+  <si>
+    <t>フリースピンボーナス</t>
+  </si>
+  <si>
+    <t>โบนัสฟรีเกม</t>
+  </si>
+  <si>
+    <t>UI_POPUP_PAY_PAGE6_TITLE1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_POPUP_PAY_PAGE6_CONTENTS1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TOP UP BONUS</t>
+  </si>
+  <si>
+    <t>加码奖励</t>
+  </si>
+  <si>
+    <t>加碼獎勵</t>
+  </si>
+  <si>
+    <t>Top Up Bonus</t>
+  </si>
+  <si>
+    <t>トップアップボーナス</t>
+  </si>
+  <si>
+    <t>โบนัสเพิ่มรางวัล</t>
+  </si>
+  <si>
+    <t>UI_POPUP_PAY_PAGE7_TITLE1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_POPUP_PAY_PAGE7_CONTENTS1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JACKPOT BONUS</t>
+  </si>
+  <si>
+    <t>累积大奖奖励</t>
+  </si>
+  <si>
+    <t>累積大獎獎勵</t>
+  </si>
+  <si>
+    <t>Jackpot Bonus</t>
+  </si>
+  <si>
+    <t>ジャックポットボーナス</t>
+  </si>
+  <si>
+    <t>โบนัสแจ็กพอต</t>
+  </si>
+  <si>
+    <t>UI_POPUP_PAY_PAGE8_TITLE1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_POPUP_PAY_PAGE8_CONTENTS1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GAME RULES</t>
+  </si>
+  <si>
+    <t>游戏规则</t>
+  </si>
+  <si>
+    <t>遊戲規則</t>
+  </si>
+  <si>
+    <t>Mga Patakaran ng Laro</t>
+  </si>
+  <si>
+    <t>ゲームルール</t>
+  </si>
+  <si>
+    <t>กติกาเกม</t>
+  </si>
+  <si>
+    <t>S$</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RM</t>
+  </si>
+  <si>
+    <t>₫</t>
+  </si>
+  <si>
+    <t>Singapore(sg)</t>
+  </si>
+  <si>
+    <t>Malaysia(ms)</t>
+  </si>
+  <si>
+    <t>Vietnam(vi)</t>
+  </si>
+  <si>
+    <t>Pelancaran pertama mungkin mengambil masa lebih lama untuk dimuatkan.</t>
+  </si>
+  <si>
+    <t>Lần khởi chạy đầu tiên có thể mất nhiều thời gian tải hơn.</t>
+  </si>
+  <si>
+    <t>TEMUI PELBAGAI CIRI DAN KEJUTAN!</t>
+  </si>
+  <si>
+    <t>KHÁM PHÁ CÁC TÍNH NĂNG VÀ BẤT NGỜ KHÁC NHAU!</t>
+  </si>
+  <si>
+    <t>KETIK KEGEMARAN ANDA, LEPASKAN KESERONOKAN!</t>
+  </si>
+  <si>
+    <t>CHẠM VÀO MỤC YÊU THÍCH, GIẢI PHÓNG NIỀM VUI!</t>
+  </si>
+  <si>
+    <t>TEMUI KEGEMBIRAAN REZEKI YANG TIDAK DISANGKA!</t>
+  </si>
+  <si>
+    <t>KHÁM PHÁ SỰ PHẤN KHÍCH CỦA VẬN MAY BẤT NGỜ!</t>
+  </si>
+  <si>
+    <t>MASUK KE FREE SPINS DAN HADAPI LEGENDA PURBA!</t>
+  </si>
+  <si>
+    <t>VÀO FREE SPINS VÀ ĐỐI MẶT VỚI HUYỀN THOẠI CỔ ĐẠI!</t>
+  </si>
+  <si>
+    <t>HARAPKAN LEBIH BANYAK SIMBOL MERAH DAN HIJAU BERSINAR!</t>
+  </si>
+  <si>
+    <t>HÃY HY VỌNG NHIỀU BIỂU TƯỢNG ĐỎ VÀ XANH LÁ TỎA SÁNG HƠN!</t>
+  </si>
+  <si>
+    <t>DEDAHKAN ARTIFAK PURBA MENERUSI MATA RA!</t>
+  </si>
+  <si>
+    <t>KHÁM PHÁ NHỮNG DI VẬT CỔ ĐẠI QUA CON MẮT CỦA RA!</t>
+  </si>
+  <si>
+    <t>TARUHAN</t>
+  </si>
+  <si>
+    <t>CƯỢC</t>
+  </si>
+  <si>
+    <t>KREDIT</t>
+  </si>
+  <si>
+    <t>TÍN DỤNG</t>
+  </si>
+  <si>
+    <t>KLIK UNTUK BERTUKAR ANTARA
+PAPARAN WANG DAN SYILING</t>
+  </si>
+  <si>
+    <t>NHẤP ĐỂ CHUYỂN GIỮA
+CHẾ ĐỘ XEM TIỀN VÀ XU</t>
+  </si>
+  <si>
+    <t>SEMOGA BERJAYA!</t>
+  </si>
+  <si>
+    <t>CHÚC MAY MẮN!</t>
+  </si>
+  <si>
+    <t>LETAKKAN TARUHAN ANDA!</t>
+  </si>
+  <si>
+    <t>ĐẶT CƯỢC CỦA BẠN!</t>
+  </si>
+  <si>
+    <t>PUTAR UNTUK MENANG!</t>
+  </si>
+  <si>
+    <t>QUAY ĐỂ THẮNG!</t>
+  </si>
+  <si>
+    <t>AUTO SPIN BERBAKI</t>
+  </si>
+  <si>
+    <t>SỐ AUTO SPIN CÒN LẠI</t>
+  </si>
+  <si>
+    <t>FREE SPIN BERBAKI</t>
+  </si>
+  <si>
+    <t>SỐ FREE SPIN CÒN LẠI</t>
+  </si>
+  <si>
+    <t>JUMLAH KEMENANGAN</t>
+  </si>
+  <si>
+    <t>TỔNG TIỀN THẮNG</t>
+  </si>
+  <si>
+    <t>MENANG</t>
+  </si>
+  <si>
+    <t>THẮNG</t>
+  </si>
+  <si>
+    <t>TETAPAN AUTOPLAY</t>
+  </si>
+  <si>
+    <t>CÀI ĐẶT AUTOPLAY</t>
+  </si>
+  <si>
+    <t>BILANGAN AUTOSPIN</t>
+  </si>
+  <si>
+    <t>SỐ LƯỢNG AUTOSPIN</t>
+  </si>
+  <si>
+    <t>PUTARAN PANTAS</t>
+  </si>
+  <si>
+    <t>QUAY NHANH</t>
+  </si>
+  <si>
+    <t>MULAKAN AUTOPLAY ({Count})</t>
+  </si>
+  <si>
+    <t>BẮT ĐẦU AUTOPLAY ({Count})</t>
+  </si>
+  <si>
+    <t>PUTARAN TURBO</t>
+  </si>
+  <si>
+    <t>QUAY TURBO</t>
+  </si>
+  <si>
+    <t>PENGGANDA TARUHAN</t>
+  </si>
+  <si>
+    <t>HỆ SỐ NHÂN CƯỢC</t>
+  </si>
+  <si>
+    <t>NILAI SYILING</t>
+  </si>
+  <si>
+    <t>GIÁ TRỊ XU</t>
+  </si>
+  <si>
+    <t>TARUHAN MAKS</t>
+  </si>
+  <si>
+    <t>CƯỢC TỐI ĐA</t>
+  </si>
+  <si>
+    <t>JUMLAH TARUHAN</t>
+  </si>
+  <si>
+    <t>TỔNG CƯỢC</t>
+  </si>
+  <si>
+    <t>AKTIFKAN</t>
+  </si>
+  <si>
+    <t>KÍCH HOẠT</t>
+  </si>
+  <si>
+    <t>BELI</t>
+  </si>
+  <si>
+    <t>MUA</t>
+  </si>
+  <si>
+    <t>BATAL</t>
+  </si>
+  <si>
+    <t>HỦY</t>
+  </si>
+  <si>
+    <t>BELI BONUS</t>
+  </si>
+  <si>
+    <t>MUA BONUS</t>
+  </si>
+  <si>
+    <t>TETAPAN SISTEM</t>
+  </si>
+  <si>
+    <t>CÀI ĐẶT HỆ THỐNG</t>
+  </si>
+  <si>
+    <t>MUZIK LATAR</t>
+  </si>
+  <si>
+    <t>NHẠC NỀN</t>
+  </si>
+  <si>
+    <t>HIDUPKAN ATAU MATIKAN 
+MUZIK PERMAINAN</t>
+  </si>
+  <si>
+    <t>BẬT HOẶC TẮT 
+ NHẠC TRÒ CHƠI</t>
+  </si>
+  <si>
+    <t>SIARAN</t>
+  </si>
+  <si>
+    <t>PHÁT SÓNG</t>
+  </si>
+  <si>
+    <t>HIDUPKAN ATAU MATIKAN
+SIARAN KEMENANGAN PERMAINAN</t>
+  </si>
+  <si>
+    <t>BẬT HOẶC TẮT
+PHÁT SÓNG CHIẾN THẮNG TRÒ CHƠI</t>
+  </si>
+  <si>
+    <t>SKRIN PENGENALAN</t>
+  </si>
+  <si>
+    <t>MÀN HÌNH GIỚI THIỆU</t>
+  </si>
+  <si>
+    <t>PAPARKAN SKRIN PENGENALAN SEBELUM 
+MEMULAKAN PERMAINAN</t>
+  </si>
+  <si>
+    <t>HIỂN THỊ MÀN HÌNH GIỚI THIỆU TRƯỚC 
+KHI BẮT ĐẦU TRÒ CHƠI</t>
+  </si>
+  <si>
+    <t>KESAN BUNYI</t>
+  </si>
+  <si>
+    <t>HIỆU ỨNG ÂM THANH</t>
+  </si>
+  <si>
+    <t>HIDUPKAN ATAU MATIKAN 
+BUNYI PERMAINAN</t>
+  </si>
+  <si>
+    <t>BẬT HOẶC TẮT 
+ÂM THANH TRÒ CHƠI</t>
+  </si>
+  <si>
+    <t>KELANTANGAN</t>
+  </si>
+  <si>
+    <t>ÂM LƯỢNG</t>
+  </si>
+  <si>
+    <t>SAHKAN</t>
+  </si>
+  <si>
+    <t>XÁC NHẬN</t>
+  </si>
+  <si>
+    <t>Rangkaian</t>
+  </si>
+  <si>
+    <t>Mạng</t>
+  </si>
+  <si>
+    <t>Anda telah terputus sambungan daripada pelayan.</t>
+  </si>
+  <si>
+    <t>Bạn đã bị ngắt kết nối khỏi máy chủ.</t>
+  </si>
+  <si>
+    <t>Log Masuk Semula</t>
+  </si>
+  <si>
+    <t>Đăng nhập lại</t>
+  </si>
+  <si>
+    <t>BAKI TIDAK MENCUKUPI</t>
+  </si>
+  <si>
+    <t>SỐ DƯ KHÔNG ĐỦ</t>
+  </si>
+  <si>
+    <t>Sila tambah nilai dana dalam dompet tunai anda.
+Jika baki tidak dikemas kini selepas tambah nilai,
+sila muat semula dompet tunai anda.</t>
+  </si>
+  <si>
+    <t>Vui lòng nạp tiền vào ví tiền mặt của bạn.
+Nếu số dư không được cập nhật sau khi nạp,
+vui lòng làm mới ví tiền mặt của bạn.</t>
+  </si>
+  <si>
+    <t>Ralat</t>
+  </si>
+  <si>
+    <t>Lỗi</t>
+  </si>
+  <si>
+    <t>ID Simbol salah.
+Anda telah terputus sambungan daripada pelayan.</t>
+  </si>
+  <si>
+    <t>ID Biểu tượng sai.
+Bạn đã bị ngắt kết nối khỏi máy chủ.</t>
+  </si>
+  <si>
+    <t>Pautan permainan ini telah tamat tempoh.</t>
+  </si>
+  <si>
+    <t>Liên kết trò chơi này đã hết hạn.</t>
+  </si>
+  <si>
+    <t>Permintaan tidak sah.</t>
+  </si>
+  <si>
+    <t>Yêu cầu không hợp lệ.</t>
+  </si>
+  <si>
+    <t>Dalam permainan bonus, &lt;Sprite=10&gt; kekal pada papan dan meningkatkan peluang kemenangan anda.                    Apabila anda mengumpul &lt;Sprite=11&gt;, anda menerima hadiah simbol.                    &lt;Sprite=10&gt; kekal di medan sehingga permainan tamat. Apabila ia bertindan, pengganda meningkat.</t>
+  </si>
+  <si>
+    <t>Trong trò chơi bonus, &lt;Sprite=10&gt; vẫn ở trên bảng và tăng cơ hội thắng của bạn.                    Khi bạn thu thập &lt;Sprite=11&gt;, bạn nhận được phần thưởng biểu tượng.                    &lt;Sprite=10&gt; vẫn ở trên sân cho đến khi trò chơi kết thúc. Khi nó xếp chồng, hệ số nhân tăng lên.</t>
+  </si>
+  <si>
+    <t>Setiap kali  &lt;Sprite=11&gt;  muncul, anda dianugerahkan hadiah simbol.</t>
+  </si>
+  <si>
+    <t>Mỗi khi  &lt;Sprite=11&gt;  xuất hiện, bạn được trao phần thưởng biểu tượng.</t>
+  </si>
+  <si>
+    <t>BAYARAN</t>
+  </si>
+  <si>
+    <t>TRẢ THƯỞNG</t>
+  </si>
+  <si>
+    <t>TUAH TIDAK DISANGKA</t>
+  </si>
+  <si>
+    <t>MAY MẮN BẤT NGỜ</t>
+  </si>
+  <si>
+    <t>PERATURAN PERMAINAN</t>
+  </si>
+  <si>
+    <t>LUẬT CHƠI</t>
+  </si>
+  <si>
+    <t>Before the base game reel spin initiates, a number of positions are replaced with any one symbol except  &lt;img src = '11' height=50 offset=-8 /&gt;  and  &lt;img src = '13' height=50 offset=-8 /&gt; . 
 Only highest winner paid per winning combination.
 Winning combinations may contain only one symbol from each adjacent reel, beginning with the leftmost reel.
 Like symbols, or their substitute, on a single reel are not part of the same winning combination, but may create separate winning combinations.
 All ways wins are multiplied by the bet multiplier.</t>
   </si>
   <si>
-    <t>기본 게임 릴 스핀이 시작되기 전에, 일부 위치가  &lt;Sprite=10&gt;  및  &lt;Sprite=11&gt; 을 제외한 임의의 하나의 심볼로 대체됩니다.
+    <t>기본 게임 릴 스핀이 시작되기 전에, 일부 위치가  &lt;img src = '11' height=50 offset=-8 /&gt;  및  &lt;img src = '13' height=50 offset=-8 /&gt; 을 제외한 임의의 하나의 심볼로 대체됩니다.
 각 당첨 조합당 가장 높은 당첨만 지급됩니다.
 당첨 조합은 가장 왼쪽 릴부터 시작하여 인접한 각 릴에서 하나의 심볼만 포함할 수 있습니다.
 같은 릴에 있는 동일한 심볼 또는 그 대체 심볼은 동일한 당첨 조합으로 간주되지 않으며, 별도의 당첨 조합을 생성할 수 있습니다.
 모든 Ways 당첨은 베팅 배수에 따라 곱해집니다.</t>
   </si>
   <si>
-    <t>在基础游戏转轴开始旋转之前，一些位置会被替换为除  &lt;Sprite=10&gt;  和  &lt;Sprite=11&gt;  之外的任意一个符号。
+    <t>在基础游戏转轴开始旋转之前，一些位置会被替换为除  &lt;img src = '11' height=50 offset=-8 /&gt;  和  &lt;img src = '13' height=50 offset=-8 /&gt;  之外的任意一个符号。
 每个中奖组合仅支付最高奖金。
 中奖组合从最左侧转轴开始，每个相邻转轴中只能包含一个符号。
 同一转轴上的相同符号或其替代符号不属于同一中奖组合，但可以形成独立的中奖组合。
 所有 Ways 赢奖将根据投注倍数进行乘算。</t>
   </si>
   <si>
-    <t>在基礎遊戲轉軸開始旋轉之前，一些位置會被替換為除  &lt;Sprite=10&gt;  和  &lt;Sprite=11&gt;  之外的任意一個符號。
+    <t>在基礎遊戲轉軸開始旋轉之前，一些位置會被替換為除  &lt;img src = '11' height=50 offset=-8 /&gt;  和  &lt;img src = '13' height=50 offset=-8 /&gt;  之外的任意一個符號。
 每個中獎組合僅支付最高獎金。
 中獎組合從最左側轉軸開始，每個相鄰轉軸中只能包含一個符號。
 同一轉軸上的相同符號或其替代符號不屬於同一中獎組合，但可以形成獨立的中獎組合。
 所有 Ways 贏獎將根據投注倍數進行乘算。</t>
   </si>
   <si>
-    <t>Bago magsimula ang pag-ikot ng reel sa base game, ang ilang posisyon ay papalitan ng anumang isang simbolo maliban sa  &lt;Sprite=10&gt;  at  &lt;Sprite=11&gt; .
+    <t>Bago magsimula ang pag-ikot ng reel sa base game, ang ilang posisyon ay papalitan ng anumang isang simbolo maliban sa  &lt;img src = '11' height=50 offset=-8 /&gt;  at  &lt;img src = '13' height=50 offset=-8 /&gt; .
 Tanging ang pinakamataas na panalo lamang ang babayaran sa bawat winning combination.
 Ang mga winning combination ay maaaring maglaman lamang ng isang simbolo mula sa bawat magkatabing reel, simula sa pinakakaliwang reel.
 Ang magkakaparehong simbolo, o ang kanilang kapalit, sa iisang reel ay hindi bahagi ng parehong winning combination, ngunit maaaring bumuo ng hiwalay na mga winning combination.
 Ang lahat ng Ways wins ay minumultiply ayon sa bet multiplier.</t>
   </si>
   <si>
-    <t>ベースゲームのリールスピンが開始される前に、いくつかの位置が  &lt;Sprite=10&gt;  および  &lt;Sprite=11&gt;  を除く任意の1つのシンボルに置き換えられます。
+    <t>ベースゲームのリールスピンが開始される前に、いくつかの位置が  &lt;img src = '11' height=50 offset=-8 /&gt;  および  &lt;img src = '13' height=50 offset=-8 /&gt;  を除く任意の1つのシンボルに置き換えられます。
 各当選組み合わせごとに最も高い配当のみが支払われます。
 当選組み合わせは、最も左のリールから始まり、隣接する各リールから1つのシンボルのみを含むことができます。
 同一リール上の同じシンボル、またはその代替シンボルは同一の当選組み合わせには含まれず、別々の当選組み合わせを形成する場合があります。
 すべてのWaysの当選はベット倍率によって乗算されます。</t>
   </si>
   <si>
-    <t>ก่อนที่วงล้อในเกมหลักจะเริ่มหมุน บางตำแหน่งจะถูกแทนที่ด้วยสัญลักษณ์ใดสัญลักษณ์หนึ่ง ยกเว้น  &lt;Sprite=10&gt;  และ  &lt;Sprite=11&gt;
+    <t>ก่อนที่วงล้อในเกมหลักจะเริ่มหมุน บางตำแหน่งจะถูกแทนที่ด้วยสัญลักษณ์ใดสัญลักษณ์หนึ่ง ยกเว้น  &lt;img src = '11' height=50 offset=-8 /&gt;  และ  &lt;img src = '13' height=50 offset=-8 /&gt;
 จะจ่ายรางวัลเฉพาะชุดที่ชนะสูงสุดต่อหนึ่งชุดการชนะเท่านั้น
 ชุดการชนะสามารถมีสัญลักษณ์ได้เพียงหนึ่งสัญลักษณ์จากแต่ละวงล้อที่อยู่ติดกัน โดยเริ่มจากวงล้อซ้ายสุด
 สัญลักษณ์ที่เหมือนกัน หรือสัญลักษณ์ทดแทน บนวงล้อเดียวกันจะไม่ถือว่าเป็นส่วนหนึ่งของชุดการชนะเดียวกัน แต่สามารถสร้างชุดการชนะแยกกันได้
 การชนะทั้งหมดแบบ Ways จะถูกคูณด้วยตัวคูณการเดิมพัน</t>
   </si>
   <si>
-    <t>UI_POPUP_PAY_PAGE2_TITLE1</t>
-  </si>
-  <si>
-    <t>WILD/TRAIL</t>
-  </si>
-  <si>
-    <t>百搭 / 轨迹</t>
-  </si>
-  <si>
-    <t>百搭 / 軌跡</t>
-  </si>
-  <si>
-    <t>Wild / Trail</t>
-  </si>
-  <si>
-    <t>ワイルド／トレイル</t>
-  </si>
-  <si>
-    <t>ไวลด์ / เทรล</t>
-  </si>
-  <si>
-    <t>UI_POPUP_PAY_PAGE2_CONTENTS1</t>
-  </si>
-  <si>
-    <t>appears on reels 2, 3, and 4 and is WILD for all symbols appearing in the base game except  &lt;Sprite=11&gt; .</t>
-  </si>
-  <si>
-    <t>릴 2, 3, 4에 등장하며,  &lt;Sprite=11&gt;  을 제외한 기본 게임의 모든 심볼에 대해 WILD로 적용됩니다.</t>
-  </si>
-  <si>
-    <t>出现在第2、3、4转轴上，并对除  &lt;Sprite=11&gt;  之外的所有基础游戏符号作为WILD。</t>
-  </si>
-  <si>
-    <t>出現在第2、3、4轉軸上，並對除  &lt;Sprite=11&gt;  之外的所有基礎遊戲符號作為WILD。</t>
-  </si>
-  <si>
-    <t>Lumilitaw sa reels 2, 3, at 4 at nagsisilbing WILD para sa lahat ng simbolo sa base game maliban sa  &lt;Sprite=11&gt; .</t>
-  </si>
-  <si>
-    <t>リール2、3、4に出現し、 &lt;Sprite=11&gt;  を除くベースゲームのすべてのシンボルに対してWILDとして機能します。</t>
-  </si>
-  <si>
-    <t>ปรากฏบนวงล้อ 2, 3 และ 4 และทำหน้าที่เป็น WILD สำหรับสัญลักษณ์ทั้งหมดในเกมหลัก ยกเว้น  &lt;Sprite=11&gt;</t>
-  </si>
-  <si>
-    <t>UI_POPUP_PAY_PAGE2_TITLE2</t>
-  </si>
-  <si>
-    <t>UI_POPUP_PAY_PAGE2_CONTENTS2</t>
-  </si>
-  <si>
-    <t>SHOU BONUS</t>
-  </si>
-  <si>
-    <t>寿奖励</t>
-  </si>
-  <si>
-    <t>壽獎勵</t>
-  </si>
-  <si>
-    <t>Shou Bonus</t>
-  </si>
-  <si>
-    <t>ショウボーナス</t>
-  </si>
-  <si>
-    <t>โบนัสโชว</t>
-  </si>
-  <si>
-    <t>During the base game, each  &lt;Sprite=11&gt;  will display a credit value between 10% and 500% of the total bet amount.</t>
-  </si>
-  <si>
-    <t>기본 게임 동안, 각  &lt;Sprite=11&gt;  은 총 베팅 금액의 10%에서 500% 사이의 크레딧 값을 표시합니다.</t>
-  </si>
-  <si>
-    <t>在基础游戏期间，每个  &lt;Sprite=11&gt;  会显示总投注金额10%至500%之间的积分数值。</t>
-  </si>
-  <si>
-    <t>在基礎遊戲期間，每個  &lt;Sprite=11&gt;  會顯示總投注金額10%至500%之間的分數數值。</t>
-  </si>
-  <si>
-    <t>Sa base game, ang bawat  &lt;Sprite=11&gt;  ay magpapakita ng credit value na nasa pagitan ng 10% hanggang 500% ng kabuuang halaga ng taya.</t>
-  </si>
-  <si>
-    <t>ベースゲーム中、各  &lt;Sprite=11&gt;  は総ベット額の10%から500%のクレジット値を表示します。</t>
-  </si>
-  <si>
-    <t>ในระหว่างเกมหลัก แต่ละ  &lt;Sprite=11&gt;  จะแสดงมูลค่าเครดิตระหว่าง 10% ถึง 500% ของจำนวนเดิมพันทั้งหมด</t>
+    <t>Sebelum putaran gelung base game bermula, beberapa kedudukan digantikan dengan mana-mana satu simbol kecuali  &lt;img src = '11' height=50 offset=-8 /&gt;  dan  &lt;img src = '13' height=50 offset=-8 /&gt; . 
+Hanya kemenangan tertinggi dibayar bagi setiap kombinasi menang.
+Kombinasi menang hanya boleh mengandungi satu simbol daripada setiap gelung bersebelahan, bermula dari gelung paling kiri.
+Simbol yang sama, atau penggantinya, pada satu gelung bukan sebahagian daripada kombinasi menang yang sama, tetapi boleh mencipta kombinasi menang yang berasingan.
+Semua kemenangan ways didarab dengan pengganda taruhan.</t>
+  </si>
+  <si>
+    <t>Trước khi reel của trò chơi cơ bản bắt đầu quay, một số vị trí được thay thế bằng bất kỳ biểu tượng nào ngoại trừ  &lt;img src = '11' height=50 offset=-8 /&gt;  và  &lt;img src = '13' height=50 offset=-8 /&gt; . 
+Chỉ phần thắng cao nhất được trả cho mỗi tổ hợp thắng.
+Các tổ hợp thắng chỉ có thể chứa một biểu tượng từ mỗi reel liền kề, bắt đầu từ reel ngoài cùng bên trái.
+Các biểu tượng giống nhau, hoặc biểu tượng thay thế, trên cùng một reel không thuộc cùng một tổ hợp thắng, nhưng có thể tạo ra các tổ hợp thắng riêng biệt.
+Tất cả phần thắng theo ways đều được nhân với hệ số nhân cược.</t>
+  </si>
+  <si>
+    <t>appears on reels 2, 3, and 4 and is WILD for all symbols appearing in the base game except  &lt;img src = '13' height=50 offset=20 /&gt; .</t>
+  </si>
+  <si>
+    <t>릴 2, 3, 4에 등장하며,  &lt;img src = '13' height=50 offset=20 /&gt;  을 제외한 기본 게임의 모든 심볼에 대해 WILD로 적용됩니다.</t>
+  </si>
+  <si>
+    <t>出现在第2、3、4转轴上，并对除  &lt;img src = '13' height=50 offset=20 /&gt;  之外的所有基础游戏符号作为WILD。</t>
+  </si>
+  <si>
+    <t>出現在第2、3、4轉軸上，並對除  &lt;img src = '13' height=50 offset=20 /&gt;  之外的所有基礎遊戲符號作為WILD。</t>
+  </si>
+  <si>
+    <t>Lumilitaw sa reels 2, 3, at 4 at nagsisilbing WILD para sa lahat ng simbolo sa base game maliban sa  &lt;img src = '13' height=50 offset=20 /&gt; .</t>
+  </si>
+  <si>
+    <t>リール2、3、4に出現し、 &lt;img src = '13' height=50 offset=20 /&gt;  を除くベースゲームのすべてのシンボルに対してWILDとして機能します。</t>
+  </si>
+  <si>
+    <t>ปรากฏบนวงล้อ 2, 3 และ 4 และทำหน้าที่เป็น WILD สำหรับสัญลักษณ์ทั้งหมดในเกมหลัก ยกเว้น  &lt;img src = '13' height=50 offset=20 /&gt;</t>
+  </si>
+  <si>
+    <t>muncul pada gelung 2, 3, dan 4 dan menjadi WILD untuk semua simbol yang muncul dalam base game kecuali  &lt;img src = '13' height=50 offset=20 /&gt; .</t>
+  </si>
+  <si>
+    <t>xuất hiện trên reel 2, 3 và 4 và là WILD cho tất cả biểu tượng xuất hiện trong trò chơi cơ bản ngoại trừ  &lt;img src = '13' height=50 offset=20 /&gt; .</t>
+  </si>
+  <si>
+    <t>During the base game, each  &lt;img src = '13' height=50 offset=20 /&gt;  will display a credit value between 10% and 500% of the total bet amount.</t>
+  </si>
+  <si>
+    <t>기본 게임 동안, 각  &lt;img src = '13' height=50 offset=20 /&gt;  은 총 베팅 금액의 10%에서 500% 사이의 크레딧 값을 표시합니다.</t>
+  </si>
+  <si>
+    <t>在基础游戏期间，每个  &lt;img src = '13' height=50 offset=20 /&gt;  会显示总投注金额10%至500%之间的积分数值。</t>
+  </si>
+  <si>
+    <t>在基礎遊戲期間，每個  &lt;img src = '13' height=50 offset=20 /&gt;  會顯示總投注金額10%至500%之間的分數數值。</t>
+  </si>
+  <si>
+    <t>Sa base game, ang bawat  &lt;img src = '13' height=50 offset=20 /&gt;  ay magpapakita ng credit value na nasa pagitan ng 10% hanggang 500% ng kabuuang halaga ng taya.</t>
+  </si>
+  <si>
+    <t>ベースゲーム中、各  &lt;img src = '13' height=50 offset=20 /&gt;  は総ベット額の10%から500%のクレジット値を表示します。</t>
+  </si>
+  <si>
+    <t>ในระหว่างเกมหลัก แต่ละ  &lt;img src = '13' height=50 offset=20 /&gt;  จะแสดงมูลค่าเครดิตระหว่าง 10% ถึง 500% ของจำนวนเดิมพันทั้งหมด</t>
+  </si>
+  <si>
+    <t>Semasa base game, setiap  &lt;img src = '13' height=50 offset=20 /&gt;  akan memaparkan nilai kredit antara 10% dan 500% daripada jumlah taruhan.</t>
+  </si>
+  <si>
+    <t>Trong trò chơi cơ bản, mỗi  &lt;img src = '13' height=50 offset=20 /&gt;  sẽ hiển thị giá trị tín dụng từ 10% đến 500% tổng số tiền cược.</t>
   </si>
   <si>
     <t>UI_POPUP_PAY_PAGE3_TITLE1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>UI_POPUP_PAY_PAGE3_CONTENTS1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UNEXPECTED LUCKY</t>
-  </si>
-  <si>
-    <t>意外好运</t>
-  </si>
-  <si>
-    <t>意外好運</t>
-  </si>
-  <si>
-    <t>Di-inaasahang Suwerte</t>
-  </si>
-  <si>
-    <t>思いがけない幸運</t>
-  </si>
-  <si>
-    <t>โชคที่ไม่คาดคิด</t>
-  </si>
-  <si>
-    <t>Regardless of the number of &lt;Sprite=0&gt; collected from the reel result, the Feature Game may be triggered at random. 
-If a lucky event occurs, some symbols appearing on the reels will transform into &lt;Sprite=0&gt; until
+  </si>
+  <si>
+    <t>Regardless of the number of &lt;img src = '13' height=50 offset=20/&gt;  collected from the reel result, the Feature Game may be triggered at random. 
+If a lucky event occurs, some symbols appearing on the reels will transform into &lt;img src = '13' height=50 offset=20/&gt;  until
 the minimum requirement of 6 Shou Symbols for Feature entry is met.
-The transformed &lt;Sprite=0&gt; will be assigned a Credit Value based on a random chance, after which the Feature Select screen will be displayed.
-This lucky event may occur even if no &lt;Sprite=0&gt; appears in the reel result, and the outcome is determined independently on every spin.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>릴 결과에서 획득한 &lt;Sprite=0&gt; 개수와 관계없이, 일정 확률에 따라 Feature Game이 발동될 수도 있습니다. 예상치 못한 행운이 발생하면,
-릴에 등장한 일부 심볼이 6개의 Shou Symbol이 될 때까지 &lt;Sprite=0&gt;으로 변환됩니다.
-변환된 &lt;Sprite=0&gt;에는 일정 확률에 따라 Credit이 부여되며, 이후 Feature Select 화면이 표시됩니다.
-해당 행운 당첨은 &lt;Sprite=0&gt;이 릴 결과에 등장하지 않은 경우에도 발생할 수 있으며, 각 스핀마다 독립적으로 판정됩니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>无</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>论从卷轴结果中收集到多少个</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;Sprite=0&gt;，都可能</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>随机触</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>发</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Feature Game。
-若</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>发生幸运事件，卷轴上出现的部分符号将转变为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;Sprite=0&gt;，直至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>满足进入功能所需的最低条件——</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>个</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Shou 符</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>号。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+The transformed &lt;img src = '13' height=50 offset=20/&gt;  will be assigned a Credit Value based on a random chance, after which the Feature Select screen will be displayed.
+This lucky event may occur even if no &lt;img src = '13' height=50 offset=20/&gt;  appears in the reel result, and the outcome is determined independently on every spin.</t>
+  </si>
+  <si>
+    <t>릴 결과에서 획득한 &lt;img src = '13' height=50 offset=20/&gt;  개수와 관계없이, 일정 확률에 따라 Feature Game이 발동될 수도 있습니다. 예상치 못한 행운이 발생하면,
+릴에 등장한 일부 심볼이 6개의 Shou Symbol이 될 때까지 &lt;img src = '13' height=50 offset=20/&gt; 으로 변환됩니다.
+변환된 &lt;img src = '13' height=50 offset=20/&gt; 에는 일정 확률에 따라 Credit이 부여되며, 이후 Feature Select 화면이 표시됩니다.
+해당 행운 당첨은 &lt;img src = '13' height=50 offset=20/&gt; 이 릴 결과에 등장하지 않은 경우에도 발생할 수 있으며, 각 스핀마다 독립적으로 판정됩니다.</t>
+  </si>
+  <si>
+    <t>无论从卷轴结果中收集到多少个 &lt;img src = '13' height=50 offset=20/&gt; ，都可能随机触发 Feature Game。
+若发生幸运事件，卷轴上出现的部分符号将转变为 &lt;img src = '13' height=50 offset=20/&gt; ，直至满足进入功能所需的最低条件——6 个 Shou 符号。
+转变后的 &lt;img src = '13' height=50 offset=20/&gt;  将根据随机机率被赋予 Credit Value，随后会显示 Feature Select 画面。
+即使卷轴结果中没有出现任何 &lt;img src = '13' height=50 offset=20/&gt; ，此幸运事件仍可能发生，且其结果在每次旋转中均独立决定。</t>
+  </si>
+  <si>
+    <t>無論從捲軸結果中收集到多少個 &lt;img src = '13' height=50 offset=20/&gt; ，都可能隨機觸發 Feature Game。
+若發生幸運事件，捲軸上出現的部分符號將轉變為 &lt;img src = '13' height=50 offset=20/&gt; ，直至滿足進入功能所需的最低條件——6 個 Shou 符號。
+轉變後的 &lt;img src = '13' height=50 offset=20/&gt;  將根據隨機機率被賦予 Credit Value，隨後會顯示 Feature Select 畫面。
+即使捲軸結果中沒有出現任何 &lt;img src = '13' height=50 offset=20/&gt; ，此幸運事件仍可能發生，且其結果在每次旋轉中均獨立決定。</t>
+  </si>
+  <si>
+    <t>Anuman ang bilang ng &lt;img src = '13' height=50 offset=20/&gt;  na nakolekta mula sa reel result, maaaring ma-trigger nang random ang Feature Game.
+Kapag may naganap na lucky event, ang ilang simbolo na lumalabas sa reels ay magtatransform sa &lt;img src = '13' height=50 offset=20/&gt;  hanggang matugunan ang minimum na kinakailangan na 6 Shou Symbol para sa pagpasok sa feature.
+Ang na-transform na &lt;img src = '13' height=50 offset=20/&gt;  ay bibigyan ng Credit Value batay sa random na tsansa, pagkatapos nito ay ipapakita ang Feature Select screen.
+Maaaring maganap ang lucky event na ito kahit walang &lt;img src = '13' height=50 offset=20/&gt;  na lumitaw sa reel result, at ang resulta ay independiyenteng tinutukoy sa bawat spin.</t>
+  </si>
+  <si>
+    <t>リール結果で集めた &lt;img src = '13' height=50 offset=20/&gt;  の数に関係なく、Feature Game がランダムに発動することがあります。
+ラッキーイベントが発生すると、フィーチャー突入に必要な最低条件である 6 個の Shou シンボルを満たすまで、リール上に出現した一部のシンボルが &lt;img src = '13' height=50 offset=20/&gt;  に変化します。
+変化した &lt;img src = '13' height=50 offset=20/&gt;  にはランダムな確率に基づいて Credit Value が付与され、その後 Feature Select 画面が表示されます。
+このラッキーイベントは、リール結果に &lt;img src = '13' height=50 offset=20/&gt;  が 1 つも出現しなくても発生することがあり、その結果は毎回のスピンで独立して決定されます。</t>
+  </si>
+  <si>
+    <t>ไม่ว่าจะเก็บ &lt;img src = '13' height=50 offset=20/&gt;  ได้กี่ตัวจากผลลัพธ์ของรีล Feature Game ก็อาจถูกกระตุ้นแบบสุ่มได้
+หากเกิดเหตุการณ์นำโชค สัญลักษณ์บางตัวที่ปรากฏบนรีลจะแปลงร่างเป็น &lt;img src = '13' height=50 offset=20/&gt;  จนกว่าจะครบเงื่อนไขขั้นต่ำคือ Shou Symbol 6 ตัวสำหรับการเข้าสู่ฟีเจอร์
+&lt;img src = '13' height=50 offset=20/&gt;  ที่แปลงร่างแล้วจะได้รับ Credit Value ตามโอกาสแบบสุ่ม จากนั้นจะแสดงหน้าจอ Feature Select
+เหตุการณ์นำโชคนี้อาจเกิดขึ้นได้แม้ไม่มี &lt;img src = '13' height=50 offset=20/&gt;  ปรากฏในผลลัพธ์ของรีล และผลลัพธ์จะถูกกำหนดอย่างเป็นอิสระในทุก ๆ การหมุน</t>
+  </si>
+  <si>
+    <t>Tanpa mengira bilangan &lt;img src = '13' height=50 offset=20/&gt;  yang dikumpulkan daripada hasil gelung, Feature Game mungkin dicetuskan secara rawak. 
+Jika peristiwa bertuah berlaku, sebahagian simbol yang muncul pada gelung akan bertukar menjadi &lt;img src = '13' height=50 offset=20/&gt;  sehingga
+keperluan minimum 6 Shou Symbols untuk kemasukan Feature dipenuhi.
+&lt;img src = '13' height=50 offset=20/&gt;  yang ditukar akan diberikan Credit Value berdasarkan peluang rawak, selepas itu skrin Feature Select akan dipaparkan.
+Peristiwa bertuah ini boleh berlaku walaupun tiada &lt;img src = '13' height=50 offset=20/&gt;  muncul dalam hasil gelung, dan keputusannya ditentukan secara bebas pada setiap putaran.</t>
+  </si>
+  <si>
+    <t>Bất kể số lượng &lt;img src = '13' height=50 offset=20/&gt;  thu thập được từ kết quả reel, Feature Game có thể được kích hoạt ngẫu nhiên. 
+Nếu một sự kiện may mắn xảy ra, một số biểu tượng xuất hiện trên reel sẽ biến đổi thành &lt;img src = '13' height=50 offset=20/&gt;  cho đến khi
+đạt được yêu cầu tối thiểu 6 Shou Symbols để vào Feature.
+&lt;img src = '13' height=50 offset=20/&gt;  đã biến đổi sẽ được gán Credit Value dựa trên cơ hội ngẫu nhiên, sau đó màn hình Feature Select sẽ được hiển thị.
+Sự kiện may mắn này có thể xảy ra ngay cả khi không có &lt;img src = '13' height=50 offset=20/&gt;  nào xuất hiện trong kết quả reel, và kết quả được xác định độc lập trên mỗi lượt quay.</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5 High Symbols: A Free Games Bonus with a value of 128 &lt;img src = '10' height=50 offset=-5/&gt; , 118 &lt;img src = '9' height=50 offset=-5/&gt; , 108 &lt;img src = '8' height=50 offset=-5/&gt; , 98 &lt;img src = '7' height=50 offset=-5/&gt; , or 88 &lt;img src = '6' height=50 offset=-5/&gt; , or a Top Up Bonus with a value of 88 &lt;img src = '6' height=50 offset=-5/&gt; is awarded. &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5개의 High Symbols: 128 &lt;img src = '10' height=50 offset=-5/&gt;  , 118 &lt;img src = '9' height=50 offset=-5/&gt;  , 108 &lt;img src = '8' height=50 offset=-5/&gt;  , 98 &lt;img src = '7' height=50 offset=-5/&gt;  , 또는 88     &lt;img src = '6' height=50 offset=-5/&gt;  의 값을 가지는 Free Games Bonus 또는 88     &lt;img src = '6' height=50 offset=-5/&gt;  의 값을 가지는 Top Up Bonus가 지급됩니다. &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5 High Symbols: Ang Free Games Bonus na may value na 128 &lt;img src = '10' height=50 offset=-5/&gt;  , 118 &lt;img src = '9' height=50 offset=-5/&gt;  , 108 &lt;img src = '8' height=50 offset=-5/&gt;  , 98 &lt;img src = '7' height=50 offset=-5/&gt;  , o 88 &lt;img src = '6' height=50 offset=-5/&gt;  , o ang Top Up Bonus na may value na 88     &lt;img src = '6' height=50 offset=-5/&gt;  ay ibinibigay. &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5個高階符號：數值為 128 &lt;img src = '10' height=50 offset=-5/&gt;  、118 &lt;img src = '9' height=50 offset=-5/&gt;  、108 &lt;img src = '8' height=50 offset=-5/&gt;  、98 &lt;img src = '7' height=50 offset=-5/&gt;  或 88 &lt;img src = '6' height=50 offset=-5/&gt;  的 Free Games Bonus，或數值為 88     &lt;img src = '6' height=50 offset=-5/&gt;  的 Top Up Bonus。 &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5个高等级符号：数值为 128 &lt;img src = '10' height=50 offset=-5/&gt; 、118 &lt;img src = '9' height=50 offset=-5/&gt;  、108 &lt;img src = '8' height=50 offset=-5/&gt;  、 98 &lt;img src = '7' height=50 offset=-5/&gt;  或 88 &lt;img src = '6' height=50 offset=-5/&gt;  的 Free Games Bonus，或数值为 88     &lt;img src = '6' height=50 offset=-5/&gt;  的 Top Up Bonus。 &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5 High Symbols: จะได้รับ Free Games Bonus ที่มีค่า 128 &lt;img src = '10' height=50 offset=-5/&gt;  , 118 &lt;img src = '9' height=50 offset=-5/&gt;, 108 &lt;img src = '8' height=50 offset=-5/&gt;  , 98 &lt;img src = '7' height=50 offset=-5/&gt;  หรือ 88 &lt;img src = '6' height=50 offset=-5/&gt;  หรือ Top Up Bonus ที่มีค่า 88 &lt;img src = '6' height=50 offset=-5/&gt; &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5つのHigh Symbols：128 &lt;img src = '10' height=50 offset=-5/&gt;  、118 &lt;img src = '9' height=50 offset=-5/&gt;  、108 &lt;img src = '8' height=50 offset=-5/&gt;  、98 &lt;img src = '7' height=50 offset=-5/&gt;  、または88 &lt;img src = '6' height=50 offset=-5/&gt;  の値を持つFree Games Bonus、または88 &lt;img src = '6' height=50 offset=-5/&gt;  の値を持つTop Up Bonusが付与されます。 &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5 High Symbols: Free Games Bonus dengan nilai 128 &lt;img src = '10' height=50 offset=-5/&gt; , 118 &lt;img src = '9' height=50 offset=-5/&gt; , 108 &lt;img src = '8' height=50 offset=-5/&gt; , 98 &lt;img src = '7' height=50 offset=-5/&gt; , atau 88 &lt;img src = '6' height=50 offset=-5/&gt; , atau Top Up Bonus dengan nilai 88 &lt;img src = '6' height=50 offset=-5/&gt;  dianugerahkan. &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5 High Symbols: Một Free Games Bonus với giá trị 128 &lt;img src = '10' height=50 offset=-5/&gt; , 118 &lt;img src = '9' height=50 offset=-5/&gt; , 108 &lt;img src = '8' height=50 offset=-5/&gt; , 98 &lt;img src = '7' height=50 offset=-5/&gt; , hoặc 88 &lt;img src = '6' height=50 offset=-5/&gt; , hoặc một Top Up Bonus với giá trị 88 &lt;img src = '6' height=50 offset=-5/&gt;  được trao. &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>Only the selected symbol,&lt;img src = '5' height=70 offset= -15/&gt;,  &lt;img src = '4' height=70 offset= -15/&gt;  ,&lt;img src = '3' height=70 offset= -15/&gt;   , &lt;img src = '2' height=70 offset= -15/&gt;  , &lt;img src = '1' height=70 offset= -15/&gt; ,&lt;img src = '0' height=70 offset= -15/&gt;, and  &lt;img src = '13' height=50 offset= -5/&gt;  will appear during the Free Games Bonus.</t>
+  </si>
+  <si>
+    <t>선택된 심볼인 &lt;img src = '5' height=70 offset= -15/&gt;  ,&lt;img src = '4' height=70 offset= -15/&gt;  ,&lt;img src = '3' height=70 offset= -15/&gt;  ,&lt;img src = '2' height=70 offset= -15/&gt;  ,&lt;img src = '1' height=70 offset= -15/&gt;  ,&lt;img src = '0' height=70 offset= -15/&gt;  , 및  &lt;img src = '13' height=50 offset= -5/&gt;  만 Free Games Bonus 동안 등장합니다.</t>
+  </si>
+  <si>
+    <t>在 Free Games Bonus 期间，仅会出现所选的符号 &lt;img src = '5' height=70 offset= -15/&gt;、&lt;img src = '4' height=70 offset= -15/&gt;、&lt;img src = '3' height=70 offset= -15/&gt;、&lt;img src = '2' height=70 offset= -15/&gt;、 &lt;img src = '1' height=70 offset= -15/&gt;、&lt;img src = '0' height=70 offset= -15/&gt; 以及  &lt;img src = '13' height=50 offset= -5/&gt;  。</t>
+  </si>
+  <si>
+    <t>在 Free Games Bonus 期間，僅會出現所選的符號 &lt;img src = '5' height=70 offset= -15/&gt;、 &lt;img src = '4' height=70 offset= -15/&gt;、&lt;img src = '3' height=70 offset= -15/&gt;、 &lt;img src = '2' height=70 offset= -15/&gt;、&lt;img src = '1' height=70 offset= -15/&gt;、&lt;img src = '0' height=70 offset= -15/&gt; 以及  &lt;img src = '13' height=50 offset= -5/&gt;  。</t>
+  </si>
+  <si>
+    <t>Tanging ang napiling simbolo,  &lt;img src = '5' height=70 offset= -15/&gt;  , &lt;img src = '4' height=70 offset= -15/&gt;  ,&lt;img src = '3' height=70 offset= -15/&gt;  ,&lt;img src = '2' height=70 offset= -15/&gt;  ,&lt;img src = '1' height=70 offset= -15/&gt;  ,&lt;img src = '0' height=70 offset= -15/&gt;  , at  &lt;img src = '13' height=50 offset= -5/&gt;  lamang ang lalabas sa panahon ng Free Games Bonus.</t>
+  </si>
+  <si>
+    <t>選択されたシンボルである&lt;img src = '5' height=70 offset= -15/&gt;、       &lt;img src = '4' height=70 offset= -15/&gt;、&lt;img src = '3' height=70 offset= -15/&gt;、&lt;img src = '2' height=70 offset= -15/&gt;、&lt;img src = '1' height=70 offset= -15/&gt;、&lt;img src = '0' height=70 offset= -15/&gt; および &lt;img src = '13' height=50 offset= -5/&gt;  のみがFree Games Bonus中に出現します。</t>
+  </si>
+  <si>
+    <t>ในระหว่าง Free Games Bonus จะมีเพียงสัญลักษณ์ที่เลือกไว้เท่านั้นที่ปรากฏ ได้แก่    &lt;img src = '5' height=70 offset= -15/&gt;  , &lt;img src = '4' height=70 offset= -15/&gt;  ,&lt;img src = '3' height=70 offset= -15/&gt;  ,&lt;img src = '2' height=70 offset= -15/&gt;  , &lt;img src = '1' height=70 offset= -15/&gt;  ,&lt;img src = '0' height=70 offset= -15/&gt; และ &lt;img src = '13' height=50 offset= -5/&gt;</t>
+  </si>
+  <si>
+    <t>Only the selected symbol, &lt;img src = '5' height=70 offset= -15/&gt;  , &lt;img src = '4' height=70 offset= -15/&gt;  ,&lt;img src = '3' height=70 offset= -15/&gt;  ,&lt;img src = '2' height=70 offset= -15/&gt;  ,&lt;img src = '1' height=70 offset= -15/&gt;  ,&lt;img src = '0' height=70 offset= -15/&gt;  , and &lt;img src = '13' height=50 offset= -5/&gt;  will appear during the Free Games Bonus.</t>
+  </si>
+  <si>
+    <t>Hanya simbol yang dipilih,&lt;img src = '5' height=70 offset= -15/&gt;  ,&lt;img src = '4' height=70 offset= -15/&gt;  ,&lt;img src = '3' height=70 offset= -15/&gt;  ,&lt;img src = '2' height=70 offset= -15/&gt;  ,&lt;img src = '1' height=70 offset= -15/&gt;  ,&lt;img src = '0' height=70 offset= -15/&gt;  , dan  &lt;img src = '13' height=50 offset= -5/&gt;  akan muncul semasa Free Games Bonus.</t>
+  </si>
+  <si>
+    <t>Chỉ biểu tượng được chọn,&lt;img src = '5' height=70 offset= -15/&gt;  ,&lt;img src = '4' height=70 offset= -15/&gt;  ,&lt;img src = '3' height=70 offset= -15/&gt;  , &lt;img src = '2' height=70 offset= -15/&gt;  ,&lt;img src = '1' height=70 offset= -15/&gt;  ,&lt;img src = '0' height=70 offset= -15/&gt;  , và  &lt;img src = '13' height=50 offset= -5/&gt;sẽ xuất hiện trong Free Games Bonus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 or more scattered   &lt;img src = '13' height=50 offset=0/&gt;  during the base game will award the sum of the values displayed on   &lt;img src = '13' height=50 offset=0/&gt;  and the Feature Selection.
+If at least 1 position does not contain  &lt;img src = '13' height=50 offset=0/&gt;, then the Feature Selection offers the choice of the Free Games Bonus or the Top Up Bonus.
+ &lt;img src = '13' height=50 offset=0/&gt;  and  &lt;img src = '11' height=50 offset=0/&gt; do not appear during the Free Games Bonus.
 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>转变后的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;Sprite=0&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>将根据随机机率被</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>赋予</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Credit Value，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>随后会</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>显示</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Feature Select </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>画面。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-即使卷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>轴结果中没有出现任何</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;Sprite=0&gt;，此幸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>运事件仍可能发生，且其结果在每次旋转中均独立决定。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>無論從捲軸結果中收集到多少個 &lt;Sprite=0&gt;，都可能隨機觸發 Feature Game。
-若發生幸運事件，捲軸上出現的部分符號將轉變</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>為</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;Sprite=0&gt;，直至滿足進入功能所需的最低條件——6 個 Shou 符號。
-轉變後的 &lt;Sprite=0&gt; 將根據隨機機率被賦予 Credit Value，隨後會顯示 Feature Select 畫面。
-即使捲軸結果中沒有出現任何 &lt;Sprite=0&gt;，此幸運事件仍可能發生，且其結果在每次旋轉中均獨立決定。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Anuman ang bilang ng &lt;Sprite=0&gt; na nakolekta mula sa reel result, maaaring ma-trigger nang random ang Feature Game.
-Kapag may naganap na lucky event, ang ilang simbolo na lumalabas sa reels ay magtatransform sa &lt;Sprite=0&gt; hanggang matugunan ang minimum na kinakailangan na 6 Shou Symbol para sa pagpasok sa feature.
-Ang na-transform na &lt;Sprite=0&gt; ay bibigyan ng Credit Value batay sa random na tsansa, pagkatapos nito ay ipapakita ang Feature Select screen.
-Maaaring maganap ang lucky event na ito kahit walang &lt;Sprite=0&gt; na lumitaw sa reel result, at ang resulta ay independiyenteng tinutukoy sa bawat spin.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>リ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ール結果で集めた</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;Sprite=0&gt; の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>数に関係なく、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Feature Game がランダムに</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>発動することがあります。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-ラッキ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ーイベントが発生すると、フィーチャー突入に必要な最低条件である</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 6 個の Shou シンボルを</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>満たすまで、リール上に出現した一部のシンボルが</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;Sprite=0&gt; に</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>変化します。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+  </si>
+  <si>
+    <t>기본 게임 중 6개 이상의   &lt;img src = '13' height=50 offset=0/&gt;  이 흩어져 등장하면,  &lt;img src = '13' height=50 offset=0/&gt;에 표시된 값의 합과 피처 선택이 지급됩니다.
+최소 1개의 위치에   &lt;img src = '13' height=50 offset=0/&gt;  이 포함되지 않은 경우, 피처 선택에서 Free Games Bonus 또는 Top Up Bonus 중 하나를 선택할 수 있습니다.
+Free Games Bonus 동안에는   &lt;img src = '13' height=50 offset=0/&gt;  및   &lt;img src = '11' height=50 offset=0/&gt;  이 등장하지 않습니다.</t>
+  </si>
+  <si>
+    <t>在基础游戏中，若有6个或以上的   &lt;img src = '13' height=50 offset=0/&gt;  分散出现，将奖励   &lt;img src = '13' height=50 offset=0/&gt;  上显示的数值总和以及功能选择。
+如果至少有1个位置不包含   &lt;img src = '13' height=50 offset=0/&gt; ，则功能选择提供 Free Games Bonus 或 Top Up Bonus 的选择。
+在 Free Games Bonus 期间，  &lt;img src = '13' height=50 offset=0/&gt;  和   &lt;img src = '11' height=50 offset=0/&gt;  不会出现。</t>
+  </si>
+  <si>
+    <t>在基礎遊戲中，若有6個或以上的   &lt;img src = '13' height=50 offset=0/&gt;  分散出現，將獎勵   &lt;img src = '13' height=50 offset=0/&gt;  上顯示的數值總和以及功能選擇。
+如果至少有1個位置不包含   &lt;img src = '13' height=50 offset=0/&gt; ，則功能選擇提供 Free Games Bonus 或 Top Up Bonus 的選擇。
+在 Free Games Bonus 期間，  &lt;img src = '13' height=50 offset=0/&gt;  和   &lt;img src = '11' height=50 offset=0/&gt;  不會出現。</t>
+  </si>
+  <si>
+    <t>Kung 6 o higit pang   &lt;img src = '13' height=50 offset=0/&gt;  ang lumitaw nang hiwa-hiwalay sa base game, ibibigay ang kabuuan ng mga value na ipinapakita sa   &lt;img src = '13' height=50 offset=0/&gt;  at ang Feature Selection.
+Kung may hindi bababa sa 1 posisyon na walang   &lt;img src = '13' height=50 offset=0/&gt;  , ang Feature Selection ay mag-aalok ng pagpili sa pagitan ng Free Games Bonus o Top Up Bonus.
+Ang   &lt;img src = '13' height=50 offset=0/&gt;  at   &lt;img src = '11' height=50 offset=0/&gt;  ay hindi lalabas sa panahon ng Free Games Bonus.</t>
+  </si>
+  <si>
+    <t>ベースゲーム中に6個以上の   &lt;img src = '13' height=50 offset=0/&gt;  が分散して出現した場合、  &lt;img src = '13' height=50 offset=0/&gt;  に表示された値の合計とフィーチャー選択が付与されます。
+少なくとも1つの位置に   &lt;img src = '13' height=50 offset=0/&gt;  が含まれていない場合、フィーチャー選択でFree Games BonusまたはTop Up Bonusのいずれかを選択できます。
+Free Games Bonus中は   &lt;img src = '13' height=50 offset=0/&gt;  および   &lt;img src = '11' height=50 offset=0/&gt;  は出現しません。</t>
+  </si>
+  <si>
+    <t>หากมี   &lt;img src = '13' height=50 offset=0/&gt;  ปรากฏแบบกระจาย 6 ตัวขึ้นไปในเกมหลัก จะได้รับผลรวมของค่าที่แสดงบน   &lt;img src = '13' height=50 offset=0/&gt;  และการเลือกฟีเจอร์
+หากมีอย่างน้อย 1 ตำแหน่งที่ไม่มี   &lt;img src = '13' height=50 offset=0/&gt;  การเลือกฟีเจอร์จะให้เลือก Free Games Bonus หรือ Top Up Bonus
+ในระหว่าง Free Games Bonus จะไม่มี   &lt;img src = '13' height=50 offset=0/&gt;  และ  &lt;img src = '11' height=50 offset=0/&gt; ปรากฏ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 atau lebih   &lt;img src = '13' height=50 offset=0/&gt;  yang bertaburan semasa base game akan menganugerahkan jumlah nilai yang dipaparkan pada   &lt;img src = '13' height=50 offset=0/&gt;  dan Feature Selection.
+Jika sekurang-kurangnya 1 kedudukan tidak mengandungi  &lt;img src = '13' height=50 offset=0/&gt;, maka Feature Selection menawarkan pilihan Free Games Bonus atau Top Up Bonus.
+ &lt;img src = '13' height=50 offset=0/&gt;  dan  &lt;img src = '11' height=50 offset=0/&gt; tidak muncul semasa Free Games Bonus.
 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>変化した</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;Sprite=0&gt; にはランダムな確率に基づいて Credit Value が付</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>与され、その後</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Feature Select </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>画面が表示されます。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-このラッキ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ーイベントは、リール結果に</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &lt;Sprite=0&gt; が 1 つも出現しなくても</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>発生することがあり、その結果は毎回のスピンで独立して決定されます。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t>ไม่ว่าจะเก็บ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;Sprite=0&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t>ได้กี่ตัวจากผลลัพธ์ของรีล</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Feature Game </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t>ก็อาจถูกกระตุ้นแบบสุ่มได้</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
+  </si>
+  <si>
+    <t xml:space="preserve">6 hoặc nhiều   &lt;img src = '13' height=50 offset=0/&gt;  rải rác trong trò chơi cơ bản sẽ trao tổng các giá trị hiển thị trên   &lt;img src = '13' height=50 offset=0/&gt;  và Feature Selection.
+Nếu có ít nhất 1 vị trí không chứa  &lt;img src = '13' height=50 offset=0/&gt;, thì Feature Selection cung cấp lựa chọn Free Games Bonus hoặc Top Up Bonus.
+ &lt;img src = '13' height=50 offset=0/&gt;  và  &lt;img src = '11' height=50 offset=0/&gt; không xuất hiện trong Free Games Bonus.
 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t>หากเกิดเหตุการณ์นำโชค</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t>สัญลักษณ์บางตัวที่ปรากฏบนรีลจะแปลงร่างเป็น</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;Sprite=0&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t>จนกว่าจะครบเงื่อนไขขั้นต่ำคือ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Shou Symbol 6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t>ตัวสำหรับการเข้าสู่ฟีเจอร์</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-&lt;Sprite=0&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t>ที่แปลงร่างแล้วจะได้รับ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Credit Value </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t>ตามโอกาสแบบสุ่ม</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t>จากนั้นจะแสดงหน้าจอ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Feature Select
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t>เหตุการณ์นำโชคนี้อาจเกิดขึ้นได้แม้ไม่มี</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&lt;Sprite=0&gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t>ปรากฏในผลลัพธ์ของรีล</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t>และผลลัพธ์จะถูกกำหนดอย่างเป็นอิสระในทุก</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t>ๆ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-        <charset val="222"/>
-      </rPr>
-      <t>การหมุน</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI_POPUP_PAY_PAGE4_TITLE1</t>
-  </si>
-  <si>
-    <t>UI_POPUP_PAY_PAGE4_CONTENTS1</t>
-  </si>
-  <si>
-    <t>UI_POPUP_PAY_PAGE4_CONTENTS2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI_POPUP_PAY_PAGE4_CONTENTS3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FEATURE SELECTION</t>
-  </si>
-  <si>
-    <t>功能选择</t>
-  </si>
-  <si>
-    <t>功能選擇</t>
-  </si>
-  <si>
-    <t>Pagpili ng Feature</t>
-  </si>
-  <si>
-    <t>フィーチャー選択</t>
-  </si>
-  <si>
-    <t>การเลือกฟีเจอร์</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 or more scattered  &lt;Sprite=11&gt;  during the base game will award the sum of the values displayed on  &lt;Sprite=11&gt;  and the Feature Selection.
-If at least 1 position does not contain &lt;Sprite=11&gt;, then the Feature Selection offers the choice of the Free Games Bonus or the Top Up Bonus.
-&lt;Sprite=11&gt;  and &lt;Sprite=10&gt; do not appear during the Free Games Bonus.
-</t>
-  </si>
-  <si>
-    <t>기본 게임 중 6개 이상의  &lt;Sprite=11&gt;  이 흩어져 등장하면, &lt;Sprite=11&gt;에 표시된 값의 합과 피처 선택이 지급됩니다.
-최소 1개의 위치에  &lt;Sprite=11&gt;  이 포함되지 않은 경우, 피처 선택에서 Free Games Bonus 또는 Top Up Bonus 중 하나를 선택할 수 있습니다.
-Free Games Bonus 동안에는  &lt;Sprite=11&gt;  및  &lt;Sprite=10&gt;  이 등장하지 않습니다.</t>
-  </si>
-  <si>
-    <t>在基础游戏中，若有6个或以上的  &lt;Sprite=11&gt;  分散出现，将奖励  &lt;Sprite=11&gt;  上显示的数值总和以及功能选择。
-如果至少有1个位置不包含  &lt;Sprite=11&gt; ，则功能选择提供 Free Games Bonus 或 Top Up Bonus 的选择。
-在 Free Games Bonus 期间， &lt;Sprite=11&gt;  和  &lt;Sprite=10&gt;  不会出现。</t>
-  </si>
-  <si>
-    <t>在基礎遊戲中，若有6個或以上的  &lt;Sprite=11&gt;  分散出現，將獎勵  &lt;Sprite=11&gt;  上顯示的數值總和以及功能選擇。
-如果至少有1個位置不包含  &lt;Sprite=11&gt; ，則功能選擇提供 Free Games Bonus 或 Top Up Bonus 的選擇。
-在 Free Games Bonus 期間， &lt;Sprite=11&gt;  和  &lt;Sprite=10&gt;  不會出現。</t>
-  </si>
-  <si>
-    <t>Kung 6 o higit pang  &lt;Sprite=11&gt;  ang lumitaw nang hiwa-hiwalay sa base game, ibibigay ang kabuuan ng mga value na ipinapakita sa  &lt;Sprite=11&gt;  at ang Feature Selection.
-Kung may hindi bababa sa 1 posisyon na walang  &lt;Sprite=11&gt;  , ang Feature Selection ay mag-aalok ng pagpili sa pagitan ng Free Games Bonus o Top Up Bonus.
-Ang  &lt;Sprite=11&gt;  at  &lt;Sprite=10&gt;  ay hindi lalabas sa panahon ng Free Games Bonus.</t>
-  </si>
-  <si>
-    <t>ベースゲーム中に6個以上の  &lt;Sprite=11&gt;  が分散して出現した場合、 &lt;Sprite=11&gt;  に表示された値の合計とフィーチャー選択が付与されます。
-少なくとも1つの位置に  &lt;Sprite=11&gt;  が含まれていない場合、フィーチャー選択でFree Games BonusまたはTop Up Bonusのいずれかを選択できます。
-Free Games Bonus中は  &lt;Sprite=11&gt;  および  &lt;Sprite=10&gt;  は出現しません。</t>
-  </si>
-  <si>
-    <t>หากมี  &lt;Sprite=11&gt;  ปรากฏแบบกระจาย 6 ตัวขึ้นไปในเกมหลัก จะได้รับผลรวมของค่าที่แสดงบน  &lt;Sprite=11&gt;  และการเลือกฟีเจอร์
-หากมีอย่างน้อย 1 ตำแหน่งที่ไม่มี  &lt;Sprite=11&gt;  การเลือกฟีเจอร์จะให้เลือก Free Games Bonus หรือ Top Up Bonus
-ในระหว่าง Free Games Bonus จะไม่มี  &lt;Sprite=11&gt;  และ &lt;Sprite=10&gt; ปรากฏ</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5 High Symbols: A Free Games Bonus with a value of 128     &lt;Sprite=6&gt; , 118     &lt;Sprite=7&gt; , 108     &lt;Sprite=8&gt; , 98     &lt;Sprite=9&gt; , or 88     &lt;Sprite=10&gt; , or a Top Up Bonus with a value of 88     &lt;Sprite=10&gt; is awarded. &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5개의 High Symbols: 128     &lt;Sprite=6&gt;  , 118     &lt;Sprite=7&gt;  , 108     &lt;Sprite=8&gt;  , 98     &lt;Sprite=9&gt;  , 또는 88     &lt;Sprite=10&gt;  의 값을 가지는 Free Games Bonus 또는 88     &lt;Sprite=10&gt;  의 값을 가지는 Top Up Bonus가 지급됩니다. &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5个高等级符号：数值为 128     &lt;Sprite=6&gt; 、118     &lt;Sprite=7&gt;  、108     &lt;Sprite=8&gt;  、 98     &lt;Sprite=9&gt;  或 88     &lt;Sprite=10&gt;  的 Free Games Bonus，或数值为 88     &lt;Sprite=10&gt;  的 Top Up Bonus。 &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5個高階符號：數值為 128     &lt;Sprite=6&gt;  、118     &lt;Sprite=7&gt;  、108     &lt;Sprite=8&gt;  、98     &lt;Sprite=9&gt;  或 88     &lt;Sprite=10&gt;  的 Free Games Bonus，或數值為 88     &lt;Sprite=10&gt;  的 Top Up Bonus。 &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5 High Symbols: Ang Free Games Bonus na may value na 128     &lt;Sprite=6&gt;  , 118     &lt;Sprite=7&gt;  , 108     &lt;Sprite=8&gt;  , 98     &lt;Sprite=9&gt;  , o 88     &lt;Sprite=10&gt;  , o ang Top Up Bonus na may value na 88     &lt;Sprite=10&gt;  ay ibinibigay. &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5つのHigh Symbols：128     &lt;Sprite=6&gt;  、118     &lt;Sprite=7&gt;  、108     &lt;Sprite=8&gt;  、98     &lt;Sprite=9&gt;  、または88     &lt;Sprite=10&gt;  の値を持つFree Games Bonus、または88     &lt;Sprite=10&gt;  の値を持つTop Up Bonusが付与されます。 &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5 High Symbols: จะได้รับ Free Games Bonus ที่มีค่า 128     &lt;Sprite=6&gt;  , 118     &lt;Sprite=7&gt;, 108     &lt;Sprite=8&gt;  , 98     &lt;Sprite=9&gt;  หรือ 88     &lt;Sprite=10&gt;  หรือ Top Up Bonus ที่มีค่า 88     &lt;Sprite=10&gt; &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>Only the selected symbol,       &lt;Sprite=2&gt;  ,       &lt;Sprite=0&gt;  ,       &lt;Sprite=5&gt;  ,       &lt;Sprite=1&gt;  ,       &lt;Sprite=4&gt;  ,       &lt;Sprite=3&gt;  , and  &lt;Sprite=11&gt;  will appear during the Free Games Bonus.</t>
-  </si>
-  <si>
-    <t>선택된 심볼인       &lt;Sprite=2&gt;  ,       &lt;Sprite=0&gt;  ,       &lt;Sprite=5&gt;  ,       &lt;Sprite=1&gt;  ,       &lt;Sprite=4&gt;  ,       &lt;Sprite=3&gt;  , 및  &lt;Sprite=11&gt;  만 Free Games Bonus 동안 등장합니다.</t>
-  </si>
-  <si>
-    <t>在 Free Games Bonus 期间，仅会出现所选的符号       &lt;Sprite=2&gt;、       &lt;Sprite=0&gt;、       &lt;Sprite=5&gt;、       &lt;Sprite=1&gt;、       &lt;Sprite=4&gt;、       &lt;Sprite=3&gt; 以及  &lt;Sprite=11&gt;  。</t>
-  </si>
-  <si>
-    <t>在 Free Games Bonus 期間，僅會出現所選的符號       &lt;Sprite=2&gt;、       &lt;Sprite=0&gt;、       &lt;Sprite=5&gt;、       &lt;Sprite=1&gt;、       &lt;Sprite=4&gt;、       &lt;Sprite=3&gt; 以及  &lt;Sprite=11&gt;  。</t>
-  </si>
-  <si>
-    <t>Tanging ang napiling simbolo,       &lt;Sprite=2&gt;  ,       &lt;Sprite=0&gt;  ,       &lt;Sprite=5&gt;  ,       &lt;Sprite=1&gt;  ,       &lt;Sprite=4&gt;  ,       &lt;Sprite=3&gt;  , at  &lt;Sprite=11&gt;  lamang ang lalabas sa panahon ng Free Games Bonus.</t>
-  </si>
-  <si>
-    <t>選択されたシンボルである       &lt;Sprite=2&gt;、       &lt;Sprite=0&gt;、       &lt;Sprite=5&gt;、       &lt;Sprite=1&gt;、       &lt;Sprite=4&gt;、       &lt;Sprite=3&gt; および  &lt;Sprite=11&gt;  のみがFree Games Bonus中に出現します。</t>
-  </si>
-  <si>
-    <t>ในระหว่าง Free Games Bonus จะมีเพียงสัญลักษณ์ที่เลือกไว้เท่านั้นที่ปรากฏ ได้แก่       &lt;Sprite=2&gt;  ,       &lt;Sprite=0&gt;  ,       &lt;Sprite=5&gt;  ,       &lt;Sprite=1&gt;  ,       &lt;Sprite=4&gt;  ,       &lt;Sprite=3&gt; และ  &lt;Sprite=11&gt;</t>
-  </si>
-  <si>
-    <t>UI_POPUP_PAY_PAGE5_TITLE1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI_POPUP_PAY_PAGE5_CONTENTS1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FREE GAMES BONUS</t>
-  </si>
-  <si>
-    <t>免费游戏奖励</t>
-  </si>
-  <si>
-    <t>免費遊戲獎勵</t>
-  </si>
-  <si>
-    <t>Free Games Bonus</t>
-  </si>
-  <si>
-    <t>フリースピンボーナス</t>
-  </si>
-  <si>
-    <t>โบนัสฟรีเกม</t>
   </si>
   <si>
     <t>6 free games are awarded.
-If at least 1  &lt;Sprite=12&gt;  appears on screen, then the sum of all values displayed on the triggering symbols is awarded for each  &lt;Sprite=12&gt;  on screen.
+If at least 1  &lt;img src = '12' height=50 offset= 15/&gt;  appears on screen, then the sum of all values displayed on the triggering symbols is awarded for each  &lt;img src = '12' height=50 offset= 15/&gt;  on screen.
 Additionally, if the Top Up Bonus was available during the Feature Selection, the value displayed on the Fortune Grand Jackpot meter may be awarded.
 An alternate set of reels is used during the Free Games Bonus. Winning combinations for these reels are identical to the base game except where otherwise stated.
-&lt;Sprite=12&gt;  only appears on reels 2–4 and is WILD for all symbols except  &lt;Sprite=11&gt;  .
-The “Shou Bonus” during the Free Games Bonus is the cumulative awards of all  &lt;Sprite=12&gt;  and the sum of all values displayed on each  &lt;Sprite=11&gt;  during the base game.
+&lt;img src = '12' height=50 offset= 15/&gt;  only appears on reels 2–4 and is WILD for all symbols except  &lt;img src = '13' height=50 offset= 15/&gt;  .
+The “Shou Bonus” during the Free Games Bonus is the cumulative awards of all  &lt;img src = '12' height=50 offset= 15/&gt;  and the sum of all values displayed on each  &lt;img src = '13' height=50 offset= 15/&gt;  during the base game.
 The “Shou Bonus” does not include any jackpots awarded.</t>
   </si>
   <si>
     <t>6회의 프리 게임이 지급됩니다.
-화면에 최소 1개의   &lt;Sprite=12&gt;  가 나타나면, 트리거된 심볼에 표시된 모든 값의 합이 화면에 있는 각   &lt;Sprite=12&gt;  마다 지급됩니다.
+화면에 최소 1개의   &lt;img src = '12' height=50 offset= 15/&gt;  가 나타나면, 트리거된 심볼에 표시된 모든 값의 합이 화면에 있는 각   &lt;img src = '12' height=50 offset= 15/&gt;  마다 지급됩니다.
 또한, 피처 선택 중 Top Up Bonus가 활성화되어 있었다면 Fortune Grand Jackpot 미터에 표시된 값이 지급될 수 있습니다.
 프리 게임 보너스 동안에는 별도의 릴 세트가 사용됩니다. 이 릴의 당첨 조합은 별도 명시가 없는 한 기본 게임과 동일합니다.
-  &lt;Sprite=12&gt;  는 릴 2–4에서만 등장하며,   &lt;Sprite=11&gt;  을 제외한 모든 심볼에 대해 WILD로 적용됩니다.
-프리 게임 보너스 동안의 “Shou Bonus”는 모든   &lt;Sprite=12&gt;  의 누적 보상과 기본 게임 동안 각   &lt;Sprite=11&gt;  에 표시된 모든 값의 합입니다.
+  &lt;img src = '12' height=50 offset= 15/&gt;  는 릴 2–4에서만 등장하며,   &lt;img src = '13' height=50 offset= 15/&gt;  을 제외한 모든 심볼에 대해 WILD로 적용됩니다.
+프리 게임 보너스 동안의 “Shou Bonus”는 모든   &lt;img src = '12' height=50 offset= 15/&gt;  의 누적 보상과 기본 게임 동안 각   &lt;img src = '13' height=50 offset= 15/&gt;  에 표시된 모든 값의 합입니다.
 “Shou Bonus”에는 어떤 잭팟 보상도 포함되지 않습니다.</t>
   </si>
   <si>
     <t>奖励6次免费游戏。
-如果屏幕上至少出现1个   &lt;Sprite=12&gt;  ，则触发符号上显示的所有数值总和会根据屏幕上的每个   &lt;Sprite=12&gt;   进行奖励。
+如果屏幕上至少出现1个   &lt;img src = '12' height=50 offset= 15/&gt;  ，则触发符号上显示的所有数值总和会根据屏幕上的每个   &lt;img src = '12' height=50 offset= 15/&gt;   进行奖励。
 此外，如果在功能选择期间启用了 Top Up Bonus，则可能会奖励 Fortune Grand Jackpot 计量器上显示的数值。
 在免费游戏奖励期间将使用另一组转轴。除非另有说明，这些转轴的中奖组合与基础游戏相同。
-  &lt;Sprite=12&gt;   仅出现在第2–4转轴上，并对除   &lt;Sprite=11&gt;   之外的所有符号作为WILD。
-免费游戏奖励期间的“Shou Bonus”为所有   &lt;Sprite=12&gt;   的累计奖励，以及基础游戏期间每个   &lt;Sprite=11&gt;   上显示的所有数值总和。
+  &lt;img src = '12' height=50 offset= 15/&gt;   仅出现在第2–4转轴上，并对除   &lt;img src = '13' height=50 offset= 15/&gt;   之外的所有符号作为WILD。
+免费游戏奖励期间的“Shou Bonus”为所有   &lt;img src = '12' height=50 offset= 15/&gt;   的累计奖励，以及基础游戏期间每个   &lt;img src = '13' height=50 offset= 15/&gt;   上显示的所有数值总和。
 “Shou Bonus”不包含任何已奖励的累积奖金。</t>
   </si>
   <si>
     <t>獎勵6次免費遊戲。
-如果畫面上至少出現1個   &lt;Sprite=12&gt;  ，則觸發符號上顯示的所有數值總和會根據畫面上的每個   &lt;Sprite=12&gt;   進行獎勵。
+如果畫面上至少出現1個   &lt;img src = '12' height=50 offset= 15/&gt;  ，則觸發符號上顯示的所有數值總和會根據畫面上的每個   &lt;img src = '12' height=50 offset= 15/&gt;   進行獎勵。
 此外，如果在功能選擇期間啟用了 Top Up Bonus，則可能會獎勵 Fortune Grand Jackpot 計量器上顯示的數值。
 在免費遊戲獎勵期間將使用另一組轉軸。除非另有說明，這些轉軸的中獎組合與基礎遊戲相同。
-  &lt;Sprite=12&gt;   僅出現在第2–4轉軸上，並對除   &lt;Sprite=11&gt;   之外的所有符號作為WILD。
-免費遊戲獎勵期間的「Shou Bonus」為所有   &lt;Sprite=12&gt;   的累積獎勵，以及基礎遊戲期間每個   &lt;Sprite=11&gt;   上顯示的所有數值總和。
+  &lt;img src = '12' height=50 offset= 15/&gt;   僅出現在第2–4轉軸上，並對除   &lt;img src = '13' height=50 offset= 15/&gt;   之外的所有符號作為WILD。
+免費遊戲獎勵期間的「Shou Bonus」為所有   &lt;img src = '12' height=50 offset= 15/&gt;   的累積獎勵，以及基礎遊戲期間每個   &lt;img src = '13' height=50 offset= 15/&gt;   上顯示的所有數值總和。
 「Shou Bonus」不包含任何已獲得的累積獎金。</t>
   </si>
   <si>
     <t>6 na free games ang ibinibigay.
-Kung may hindi bababa sa 1   &lt;Sprite=12&gt;   na lumitaw sa screen, ang kabuuan ng lahat ng value na ipinakita sa mga triggering symbol ay ibibigay para sa bawat   &lt;Sprite=12&gt;   na nasa screen.
+Kung may hindi bababa sa 1   &lt;img src = '12' height=50 offset= 15/&gt;   na lumitaw sa screen, ang kabuuan ng lahat ng value na ipinakita sa mga triggering symbol ay ibibigay para sa bawat   &lt;img src = '12' height=50 offset= 15/&gt;   na nasa screen.
 Bukod dito, kung available ang Top Up Bonus sa panahon ng Feature Selection, maaaring maibigay ang value na ipinapakita sa Fortune Grand Jackpot meter.
 Isang alternatibong set ng reels ang gagamitin sa panahon ng Free Games Bonus. Ang mga winning combination para sa mga reel na ito ay katulad ng sa base game maliban kung may ibang nakasaad.
-Ang   &lt;Sprite=12&gt;   ay lumilitaw lamang sa reels 2–4 at nagsisilbing WILD para sa lahat ng simbolo maliban sa   &lt;Sprite=11&gt;  .
-Ang “Shou Bonus” sa panahon ng Free Games Bonus ay ang pinagsama-samang gantimpala ng lahat ng   &lt;Sprite=12&gt;   at ang kabuuan ng lahat ng value na ipinakita sa bawat   &lt;Sprite=11&gt;   sa base game.
+Ang   &lt;img src = '12' height=50 offset= 15/&gt;   ay lumilitaw lamang sa reels 2–4 at nagsisilbing WILD para sa lahat ng simbolo maliban sa   &lt;img src = '13' height=50 offset= 15/&gt;  .
+Ang “Shou Bonus” sa panahon ng Free Games Bonus ay ang pinagsama-samang gantimpala ng lahat ng   &lt;img src = '12' height=50 offset= 15/&gt;   at ang kabuuan ng lahat ng value na ipinakita sa bawat   &lt;img src = '13' height=50 offset= 15/&gt;   sa base game.
 Ang “Shou Bonus” ay hindi kasama ang anumang jackpot na napanalunan.</t>
   </si>
   <si>
     <t>6回のフリーゲームが付与されます。
-画面上に少なくとも1つの   &lt;Sprite=12&gt;   が出現した場合、トリガーとなったシンボルに表示されたすべての値の合計が、画面上の各   &lt;Sprite=12&gt;   ごとに付与されます。
+画面上に少なくとも1つの   &lt;img src = '12' height=50 offset= 15/&gt;   が出現した場合、トリガーとなったシンボルに表示されたすべての値の合計が、画面上の各   &lt;img src = '12' height=50 offset= 15/&gt;   ごとに付与されます。
 さらに、フィーチャー選択中にTop Up Bonusが利用可能であった場合、Fortune Grand Jackpotメーターに表示された値が付与されることがあります。
 フリーゲームボーナス中は別のリールセットが使用されます。特に記載がない限り、これらのリールの当選組み合わせはベースゲームと同一です。
-  &lt;Sprite=12&gt;   はリール2–4にのみ出現し、  &lt;Sprite=11&gt;   を除くすべてのシンボルに対してWILDとして機能します。
-フリーゲームボーナス中の「Shou Bonus」は、すべての   &lt;Sprite=12&gt;   の累計報酬と、ベースゲーム中に各   &lt;Sprite=11&gt;   に表示されたすべての値の合計です。
+  &lt;img src = '12' height=50 offset= 15/&gt;   はリール2–4にのみ出現し、  &lt;img src = '13' height=50 offset= 15/&gt;   を除くすべてのシンボルに対してWILDとして機能します。
+フリーゲームボーナス中の「Shou Bonus」は、すべての   &lt;img src = '12' height=50 offset= 15/&gt;   の累計報酬と、ベースゲーム中に各   &lt;img src = '13' height=50 offset= 15/&gt;   に表示されたすべての値の合計です。
 「Shou Bonus」には、獲得したジャックポットは含まれません。</t>
   </si>
   <si>
     <t>จะได้รับฟรีเกม 6 ครั้ง
-หากมี   &lt;Sprite=12&gt;   ปรากฏบนหน้าจออย่างน้อย 1 ตัว จะได้รับผลรวมของค่าทั้งหมดที่แสดงบนสัญลักษณ์ที่ทริกเกอร์ สำหรับแต่ละ   &lt;Sprite=12&gt;   ที่อยู่บนหน้าจอ
+หากมี   &lt;img src = '12' height=50 offset= 15/&gt;   ปรากฏบนหน้าจออย่างน้อย 1 ตัว จะได้รับผลรวมของค่าทั้งหมดที่แสดงบนสัญลักษณ์ที่ทริกเกอร์ สำหรับแต่ละ   &lt;img src = '12' height=50 offset= 15/&gt;   ที่อยู่บนหน้าจอ
 นอกจากนี้ หาก Top Up Bonus พร้อมใช้งานในระหว่างการเลือกฟีเจอร์ อาจได้รับค่าที่แสดงบนมิเตอร์ Fortune Grand Jackpot
 ในระหว่างโบนัสฟรีเกม จะใช้ชุดวงล้ออีกชุดหนึ่ง โดยรูปแบบการชนะของวงล้อนี้จะเหมือนกับเกมหลัก เว้นแต่จะมีการระบุไว้เป็นอย่างอื่น
-  &lt;Sprite=12&gt;   จะปรากฏเฉพาะบนวงล้อ 2–4 และทำหน้าที่เป็น WILD สำหรับสัญลักษณ์ทั้งหมด ยกเว้น   &lt;Sprite=11&gt;  
-“Shou Bonus” ในระหว่างโบนัสฟรีเกม คือรางวัลสะสมของ   &lt;Sprite=12&gt;   ทั้งหมด และผลรวมของค่าทั้งหมดที่แสดงบนแต่ละ   &lt;Sprite=11&gt;   ในเกมหลัก
+  &lt;img src = '12' height=50 offset= 15/&gt;   จะปรากฏเฉพาะบนวงล้อ 2–4 และทำหน้าที่เป็น WILD สำหรับสัญลักษณ์ทั้งหมด ยกเว้น   &lt;img src = '13' height=50 offset= 15/&gt;  
+“Shou Bonus” ในระหว่างโบนัสฟรีเกม คือรางวัลสะสมของ   &lt;img src = '12' height=50 offset= 15/&gt;   ทั้งหมด และผลรวมของค่าทั้งหมดที่แสดงบนแต่ละ   &lt;img src = '13' height=50 offset= 15/&gt;   ในเกมหลัก
 “Shou Bonus” จะไม่รวมแจ็คพอตใด ๆ ที่ได้รับ</t>
   </si>
   <si>
-    <t>UI_POPUP_PAY_PAGE6_TITLE1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI_POPUP_PAY_PAGE6_CONTENTS1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TOP UP BONUS</t>
-  </si>
-  <si>
-    <t>加码奖励</t>
-  </si>
-  <si>
-    <t>加碼獎勵</t>
-  </si>
-  <si>
-    <t>Top Up Bonus</t>
-  </si>
-  <si>
-    <t>トップアップボーナス</t>
-  </si>
-  <si>
-    <t>โบนัสเพิ่มรางวัล</t>
+    <t>6 free game dianugerahkan.
+Jika sekurang-kurangnya 1  &lt;img src = '12' height=50 offset= 15/&gt;  muncul pada skrin, maka jumlah semua nilai yang dipaparkan pada simbol pencetus dianugerahkan bagi setiap  &lt;img src = '12' height=50 offset= 15/&gt;  pada skrin.
+Selain itu, jika Top Up Bonus tersedia semasa Feature Selection, nilai yang dipaparkan pada meter Fortune Grand Jackpot mungkin dianugerahkan.
+Set gelung yang berbeza digunakan semasa Free Games Bonus. Kombinasi menang bagi gelung ini adalah sama seperti base game kecuali jika dinyatakan sebaliknya.
+&lt;img src = '12' height=50 offset= 15/&gt;  hanya muncul pada gelung 2–4 dan menjadi WILD untuk semua simbol kecuali  &lt;img src = '13' height=50 offset= 15/&gt;  .
+“Shou Bonus” semasa Free Games Bonus ialah jumlah kumulatif semua  &lt;img src = '12' height=50 offset= 15/&gt;  dan jumlah semua nilai yang dipaparkan pada setiap  &lt;img src = '13' height=50 offset= 15/&gt;  semasa base game.
+“Shou Bonus” tidak termasuk sebarang jackpot yang dianugerahkan.</t>
+  </si>
+  <si>
+    <t>Trao 6 free game.
+Nếu có ít nhất 1  &lt;img src = '12' height=50 offset= 15/&gt;  xuất hiện trên màn hình, thì tổng tất cả giá trị hiển thị trên các biểu tượng kích hoạt được trao cho mỗi  &lt;img src = '12' height=50 offset= 15/&gt;  trên màn hình.
+Ngoài ra, nếu Top Up Bonus có sẵn trong Feature Selection, giá trị hiển thị trên đồng hồ Fortune Grand Jackpot có thể được trao.
+Một bộ reel khác được sử dụng trong Free Games Bonus. Các tổ hợp thắng cho những reel này giống hệt trò chơi cơ bản trừ khi có quy định khác.
+&lt;img src = '12' height=50 offset= 15/&gt;  chỉ xuất hiện trên reel 2–4 và là WILD cho tất cả biểu tượng ngoại trừ  &lt;img src = '13' height=50 offset= 15/&gt;  .
+“Shou Bonus” trong Free Games Bonus là tổng phần thưởng tích lũy của tất cả  &lt;img src = '12' height=50 offset= 15/&gt;  và tổng tất cả giá trị hiển thị trên mỗi  &lt;img src = '13' height=50 offset= 15/&gt;  trong trò chơi cơ bản.
+“Shou Bonus” không bao gồm bất kỳ jackpot nào được trao.</t>
   </si>
   <si>
     <t>6 spins are awarded.
-All    &lt;Sprite=11&gt;    appearing on the triggering spin are held during the bonus.
-If 1 or more    &lt;Sprite=12&gt;    land on screen, each    &lt;Sprite=12&gt;    will display the sum of all credit values displayed on the triggering symbols.
-After all    &lt;Sprite=12&gt;    have been evaluated, each    &lt;Sprite=13&gt;    that landed on screen for the current spin is evaluated one at a time.
-  &lt;Sprite=13&gt;    displays the sum of all credit values currently displayed on held positions.
-Each    &lt;Sprite=12&gt;    and    &lt;Sprite=13&gt;    that land will be held for the remainder of the bonus.
+All    &lt;img src = '13' height=50 offset= 5/&gt;    appearing on the triggering spin are held during the bonus.
+If 1 or more    &lt;img src = '12' height=50 offset= 5/&gt;    land on screen, each    &lt;img src = '12' height=50 offset= 5/&gt;    will display the sum of all credit values displayed on the triggering symbols.
+After all    &lt;img src = '12' height=50 offset= 5/&gt;    have been evaluated, each    &lt;img src = '14' height=50 offset= 5/&gt;    that landed on screen for the current spin is evaluated one at a time.
+  &lt;img src = '14' height=50 offset= 5/&gt;    displays the sum of all credit values currently displayed on held positions.
+Each    &lt;img src = '12' height=50 offset= 5/&gt;    and    &lt;img src = '14' height=50 offset= 5/&gt;    that land will be held for the remainder of the bonus.
 Each spin, if the number of spins played is 12 or fewer, “+1 Spin” may appear on a random position that is not held.
 “+1 Spin” awards 1 additional spin.
 If all 15 positions are held, the value displayed in the Grand Jackpot meter is awarded.
-Remaining spins will be played only if there is at least 1 position not covered by    &lt;Sprite=11&gt;   ,    &lt;Sprite=12&gt;   , or    &lt;Sprite=13&gt;   .
-All symbols other than “+1 Spin”,    &lt;Sprite=12&gt;   , and    &lt;Sprite=13&gt;    appearing on the reels will be grayed out and are not evaluated.
+Remaining spins will be played only if there is at least 1 position not covered by    &lt;img src = '13' height=50 offset= 5/&gt;   ,    &lt;img src = '12' height=50 offset= 5/&gt;   , or    &lt;img src = '14' height=50 offset= 5/&gt;   .
+All symbols other than “+1 Spin”,    &lt;img src = '12' height=50 offset= 5/&gt;   , and    &lt;img src = '14' height=50 offset= 5/&gt;    appearing on the reels will be grayed out and are not evaluated.
 An alternate set of reels is used during the Top Up Bonus.
-  &lt;Sprite=11&gt;    does not appear on the reels during the Top Up Bonus. Bonus spins do not award additional bonuses.</t>
+  &lt;img src = '13' height=50 offset= 5/&gt;    does not appear on the reels during the Top Up Bonus. Bonus spins do not award additional bonuses.</t>
   </si>
   <si>
     <t>6회의 스핀이 지급됩니다.
-트리거 스핀에 등장한 모든   &lt;Sprite=11&gt;  은 보너스 동안 유지됩니다.
-화면에 1개 이상의   &lt;Sprite=12&gt;  가 등장하면, 각   &lt;Sprite=12&gt;  는 트리거된 심볼에 표시된 모든 크레딧 값의 합을 표시합니다.
-모든   &lt;Sprite=12&gt;  의 평가가 완료된 후, 현재 스핀에서 화면에 등장한 각   &lt;Sprite=13&gt;  이 하나씩 순차적으로 평가됩니다.
-  &lt;Sprite=13&gt;  은 현재 유지된 위치에 표시된 모든 크레딧 값의 합을 표시합니다.
-등장한 각   &lt;Sprite=12&gt;   및   &lt;Sprite=13&gt;  은 보너스 종료 시까지 유지됩니다.
+트리거 스핀에 등장한 모든   &lt;img src = '13' height=50 offset= 5/&gt;  은 보너스 동안 유지됩니다.
+화면에 1개 이상의   &lt;img src = '12' height=50 offset= 5/&gt;  가 등장하면, 각   &lt;img src = '12' height=50 offset= 5/&gt;  는 트리거된 심볼에 표시된 모든 크레딧 값의 합을 표시합니다.
+모든   &lt;img src = '12' height=50 offset= 5/&gt;  의 평가가 완료된 후, 현재 스핀에서 화면에 등장한 각   &lt;img src = '14' height=50 offset= 5/&gt;  이 하나씩 순차적으로 평가됩니다.
+  &lt;img src = '14' height=50 offset= 5/&gt;  은 현재 유지된 위치에 표시된 모든 크레딧 값의 합을 표시합니다.
+등장한 각   &lt;img src = '12' height=50 offset= 5/&gt;   및   &lt;img src = '14' height=50 offset= 5/&gt;  은 보너스 종료 시까지 유지됩니다.
 각 스핀마다, 플레이된 스핀 수가 12회 이하인 경우, 유지되지 않은 임의의 위치에 “+1 Spin”이 등장할 수 있습니다.
 “+1 Spin”은 추가로 1회의 스핀을 제공합니다.
 15개의 모든 위치가 유지되면, Grand Jackpot 미터에 표시된 값이 지급됩니다.
-남은 스핀은   &lt;Sprite=11&gt;  ,   &lt;Sprite=12&gt;  , 또는   &lt;Sprite=13&gt;  으로 덮이지 않은 위치가 최소 1개 있을 경우에만 진행됩니다.
-“+1 Spin”,   &lt;Sprite=12&gt;  ,   &lt;Sprite=13&gt;  을 제외한 모든 릴의 심볼은 회색으로 표시되며 평가되지 않습니다.
+남은 스핀은   &lt;img src = '13' height=50 offset= 5/&gt;  ,   &lt;img src = '12' height=50 offset= 5/&gt;  , 또는   &lt;img src = '14' height=50 offset= 5/&gt;  으로 덮이지 않은 위치가 최소 1개 있을 경우에만 진행됩니다.
+“+1 Spin”,   &lt;img src = '12' height=50 offset= 5/&gt;  ,   &lt;img src = '14' height=50 offset= 5/&gt;  을 제외한 모든 릴의 심볼은 회색으로 표시되며 평가되지 않습니다.
 Top Up 보너스 동안에는 별도의 릴 세트가 사용됩니다.
-Top Up 보너스 동안에는   &lt;Sprite=11&gt;  이 릴에 등장하지 않습니다. 보너스 스핀에서는 추가 보너스가 지급되지 않습니다.</t>
+Top Up 보너스 동안에는   &lt;img src = '13' height=50 offset= 5/&gt;  이 릴에 등장하지 않습니다. 보너스 스핀에서는 추가 보너스가 지급되지 않습니다.</t>
   </si>
   <si>
     <t>奖励6次旋转。
-在触发旋转中出现的所有   &lt;Sprite=11&gt;   会在奖金期间保持不变。
-如果屏幕上出现1个或以上的   &lt;Sprite=12&gt;  ，每个   &lt;Sprite=12&gt;   会显示触发符号上所有积分数值的总和。
-在所有   &lt;Sprite=12&gt;   评估完成后，本次旋转中出现的每个   &lt;Sprite=13&gt;   将逐一进行评估。
-  &lt;Sprite=13&gt;   会显示当前已锁定位置上的所有积分数值总和。
-每个出现的   &lt;Sprite=12&gt;   和   &lt;Sprite=13&gt;   都会在奖金剩余期间保持锁定。
+在触发旋转中出现的所有   &lt;img src = '13' height=50 offset= 5/&gt;   会在奖金期间保持不变。
+如果屏幕上出现1个或以上的   &lt;img src = '12' height=50 offset= 5/&gt;  ，每个   &lt;img src = '12' height=50 offset= 5/&gt;   会显示触发符号上所有积分数值的总和。
+在所有   &lt;img src = '12' height=50 offset= 5/&gt;   评估完成后，本次旋转中出现的每个   &lt;img src = '14' height=50 offset= 5/&gt;   将逐一进行评估。
+  &lt;img src = '14' height=50 offset= 5/&gt;   会显示当前已锁定位置上的所有积分数值总和。
+每个出现的   &lt;img src = '12' height=50 offset= 5/&gt;   和   &lt;img src = '14' height=50 offset= 5/&gt;   都会在奖金剩余期间保持锁定。
 每次旋转，如果已进行的旋转次数不超过12次，“+1 Spin”可能会出现在一个未锁定的随机位置。
 “+1 Spin”会奖励额外1次旋转。
 如果15个位置全部被锁定，将奖励Grand Jackpot计量器中显示的数值。
-仅当至少有1个位置未被   &lt;Sprite=11&gt;  、  &lt;Sprite=12&gt;   或   &lt;Sprite=13&gt;   覆盖时，才会继续进行剩余旋转。
-除“+1 Spin”、  &lt;Sprite=12&gt;   和   &lt;Sprite=13&gt;   外，出现在转轴上的所有符号将显示为灰色且不参与评估。
+仅当至少有1个位置未被   &lt;img src = '13' height=50 offset= 5/&gt;  、  &lt;img src = '12' height=50 offset= 5/&gt;   或   &lt;img src = '14' height=50 offset= 5/&gt;   覆盖时，才会继续进行剩余旋转。
+除“+1 Spin”、  &lt;img src = '12' height=50 offset= 5/&gt;   和   &lt;img src = '14' height=50 offset= 5/&gt;   外，出现在转轴上的所有符号将显示为灰色且不参与评估。
 在Top Up Bonus期间将使用另一组转轴。
-在Top Up Bonus期间，  &lt;Sprite=11&gt;   不会出现在转轴上。奖金旋转不会触发额外奖金。</t>
+在Top Up Bonus期间，  &lt;img src = '13' height=50 offset= 5/&gt;   不会出现在转轴上。奖金旋转不会触发额外奖金。</t>
   </si>
   <si>
     <t>獎勵6次旋轉。
-在觸發旋轉中出現的所有   &lt;Sprite=11&gt;   會在獎勵期間保持不變。
-如果畫面上出現1個或以上的   &lt;Sprite=12&gt;  ，每個   &lt;Sprite=12&gt;   會顯示觸發符號上所有分數數值的總和。
-在所有   &lt;Sprite=12&gt;   評估完成後，本次旋轉中出現的每個   &lt;Sprite=13&gt;   將逐一進行評估。
-  &lt;Sprite=13&gt;   會顯示當前已鎖定位置上的所有分數數值總和。
-每個出現的   &lt;Sprite=12&gt;   和   &lt;Sprite=13&gt;   都會在獎勵剩餘期間保持鎖定。
+在觸發旋轉中出現的所有   &lt;img src = '13' height=50 offset= 5/&gt;   會在獎勵期間保持不變。
+如果畫面上出現1個或以上的   &lt;img src = '12' height=50 offset= 5/&gt;  ，每個   &lt;img src = '12' height=50 offset= 5/&gt;   會顯示觸發符號上所有分數數值的總和。
+在所有   &lt;img src = '12' height=50 offset= 5/&gt;   評估完成後，本次旋轉中出現的每個   &lt;img src = '14' height=50 offset= 5/&gt;   將逐一進行評估。
+  &lt;img src = '14' height=50 offset= 5/&gt;   會顯示當前已鎖定位置上的所有分數數值總和。
+每個出現的   &lt;img src = '12' height=50 offset= 5/&gt;   和   &lt;img src = '14' height=50 offset= 5/&gt;   都會在獎勵剩餘期間保持鎖定。
 每次旋轉，如果已進行的旋轉次數不超過12次，「+1 Spin」可能會出現在一個未鎖定的隨機位置。
 「+1 Spin」會獎勵額外1次旋轉。
 如果15個位置全部被鎖定，將獎勵Grand Jackpot計量器中顯示的數值。
-僅當至少有1個位置未被   &lt;Sprite=11&gt;  、  &lt;Sprite=12&gt;   或   &lt;Sprite=13&gt;   覆蓋時，才會繼續進行剩餘旋轉。
-除「+1 Spin」、  &lt;Sprite=12&gt;   和   &lt;Sprite=13&gt;   外，出現在轉軸上的所有符號將顯示為灰色且不參與評估。
+僅當至少有1個位置未被   &lt;img src = '13' height=50 offset= 5/&gt;  、  &lt;img src = '12' height=50 offset= 5/&gt;   或   &lt;img src = '14' height=50 offset= 5/&gt;   覆蓋時，才會繼續進行剩餘旋轉。
+除「+1 Spin」、  &lt;img src = '12' height=50 offset= 5/&gt;   和   &lt;img src = '14' height=50 offset= 5/&gt;   外，出現在轉軸上的所有符號將顯示為灰色且不參與評估。
 在Top Up Bonus期間將使用另一組轉軸。
-在Top Up Bonus期間，  &lt;Sprite=11&gt;   不會出現在轉軸上。獎勵旋轉不會觸發額外獎勵。</t>
+在Top Up Bonus期間，  &lt;img src = '13' height=50 offset= 5/&gt;   不會出現在轉軸上。獎勵旋轉不會觸發額外獎勵。</t>
   </si>
   <si>
     <t>6 na spins ang ibinibigay.
-Lahat ng   &lt;Sprite=11&gt;   na lumitaw sa triggering spin ay mananatili sa buong bonus.
-Kung may 1 o higit pang   &lt;Sprite=12&gt;   na lumapag sa screen, ang bawat   &lt;Sprite=12&gt;   ay magpapakita ng kabuuan ng lahat ng credit value na ipinakita sa triggering symbols.
-Matapos ma-evaluate ang lahat ng   &lt;Sprite=12&gt;  , ang bawat   &lt;Sprite=13&gt;   na lumapag sa screen sa kasalukuyang spin ay i-eevaluate isa-isa.
-Ang   &lt;Sprite=13&gt;   ay magpapakita ng kabuuan ng lahat ng credit value na kasalukuyang ipinapakita sa mga held na posisyon.
-Ang bawat   &lt;Sprite=12&gt;   at   &lt;Sprite=13&gt;   na lumapag ay mananatili hanggang sa matapos ang bonus.
+Lahat ng   &lt;img src = '13' height=50 offset= 5/&gt;   na lumitaw sa triggering spin ay mananatili sa buong bonus.
+Kung may 1 o higit pang   &lt;img src = '12' height=50 offset= 5/&gt;   na lumapag sa screen, ang bawat   &lt;img src = '12' height=50 offset= 5/&gt;   ay magpapakita ng kabuuan ng lahat ng credit value na ipinakita sa triggering symbols.
+Matapos ma-evaluate ang lahat ng   &lt;img src = '12' height=50 offset= 5/&gt;  , ang bawat   &lt;img src = '14' height=50 offset= 5/&gt;   na lumapag sa screen sa kasalukuyang spin ay i-eevaluate isa-isa.
+Ang   &lt;img src = '14' height=50 offset= 5/&gt;   ay magpapakita ng kabuuan ng lahat ng credit value na kasalukuyang ipinapakita sa mga held na posisyon.
+Ang bawat   &lt;img src = '12' height=50 offset= 5/&gt;   at   &lt;img src = '14' height=50 offset= 5/&gt;   na lumapag ay mananatili hanggang sa matapos ang bonus.
 Sa bawat spin, kung ang bilang ng mga spin na nalaro ay 12 o mas kaunti, maaaring lumitaw ang “+1 Spin” sa isang random na posisyon na hindi pa held.
 Ang “+1 Spin” ay nagbibigay ng karagdagang 1 spin.
 Kung lahat ng 15 posisyon ay held, ibibigay ang value na ipinapakita sa Grand Jackpot meter.
-Ang natitirang spins ay lalaruin lamang kung may hindi bababa sa 1 posisyon na hindi natatakpan ng   &lt;Sprite=11&gt;  ,   &lt;Sprite=12&gt;  , o   &lt;Sprite=13&gt;  .
-Lahat ng simbolo maliban sa “+1 Spin”,   &lt;Sprite=12&gt;  , at   &lt;Sprite=13&gt;   na lumilitaw sa reels ay magiging kulay abo at hindi ie-evaluate.
+Ang natitirang spins ay lalaruin lamang kung may hindi bababa sa 1 posisyon na hindi natatakpan ng   &lt;img src = '13' height=50 offset= 5/&gt;  ,   &lt;img src = '12' height=50 offset= 5/&gt;  , o   &lt;img src = '14' height=50 offset= 5/&gt;  .
+Lahat ng simbolo maliban sa “+1 Spin”,   &lt;img src = '12' height=50 offset= 5/&gt;  , at   &lt;img src = '14' height=50 offset= 5/&gt;   na lumilitaw sa reels ay magiging kulay abo at hindi ie-evaluate.
 Isang alternatibong set ng reels ang gagamitin sa panahon ng Top Up Bonus.
-Hindi lumilitaw ang   &lt;Sprite=11&gt;   sa reels sa panahon ng Top Up Bonus. Ang bonus spins ay hindi nagbibigay ng karagdagang bonus.</t>
+Hindi lumilitaw ang   &lt;img src = '13' height=50 offset= 5/&gt;   sa reels sa panahon ng Top Up Bonus. Ang bonus spins ay hindi nagbibigay ng karagdagang bonus.</t>
   </si>
   <si>
     <t>6回のスピンが付与されます。
-トリガースピンで出現したすべての   &lt;Sprite=11&gt;   はボーナス中に保持されます。
-画面上に1つ以上の   &lt;Sprite=12&gt;   が停止した場合、各   &lt;Sprite=12&gt;   はトリガーシンボルに表示されたすべてのクレジット値の合計を表示します。
-すべての   &lt;Sprite=12&gt;   の評価後、現在のスピンで画面に停止した各   &lt;Sprite=13&gt;   が1つずつ評価されます。
-  &lt;Sprite=13&gt;   は現在保持されている位置に表示されているすべてのクレジット値の合計を表示します。
-停止した各   &lt;Sprite=12&gt;   および   &lt;Sprite=13&gt;   はボーナス終了まで保持されます。
+トリガースピンで出現したすべての   &lt;img src = '13' height=50 offset= 5/&gt;   はボーナス中に保持されます。
+画面上に1つ以上の   &lt;img src = '12' height=50 offset= 5/&gt;   が停止した場合、各   &lt;img src = '12' height=50 offset= 5/&gt;   はトリガーシンボルに表示されたすべてのクレジット値の合計を表示します。
+すべての   &lt;img src = '12' height=50 offset= 5/&gt;   の評価後、現在のスピンで画面に停止した各   &lt;img src = '14' height=50 offset= 5/&gt;   が1つずつ評価されます。
+  &lt;img src = '14' height=50 offset= 5/&gt;   は現在保持されている位置に表示されているすべてのクレジット値の合計を表示します。
+停止した各   &lt;img src = '12' height=50 offset= 5/&gt;   および   &lt;img src = '14' height=50 offset= 5/&gt;   はボーナス終了まで保持されます。
 各スピンで、プレイ済みスピン数が12回以下の場合、保持されていないランダムな位置に「+1 Spin」が出現することがあります。
 「+1 Spin」は追加で1回のスピンを付与します。
 15すべての位置が保持された場合、Grand Jackpotメーターに表示されている値が付与されます。
-残りのスピンは、  &lt;Sprite=11&gt;  、  &lt;Sprite=12&gt;  、または   &lt;Sprite=13&gt;   によって覆われていない位置が少なくとも1つある場合にのみ実行されます。
-「+1 Spin」、  &lt;Sprite=12&gt;  、  &lt;Sprite=13&gt;   を除くすべてのシンボルはグレー表示となり、評価されません。
+残りのスピンは、  &lt;img src = '13' height=50 offset= 5/&gt;  、  &lt;img src = '12' height=50 offset= 5/&gt;  、または   &lt;img src = '14' height=50 offset= 5/&gt;   によって覆われていない位置が少なくとも1つある場合にのみ実行されます。
+「+1 Spin」、  &lt;img src = '12' height=50 offset= 5/&gt;  、  &lt;img src = '14' height=50 offset= 5/&gt;   を除くすべてのシンボルはグレー表示となり、評価されません。
 Top Upボーナス中は別のリールセットが使用されます。
-Top Upボーナス中は   &lt;Sprite=11&gt;   はリールに出現しません。ボーナススピンでは追加のボーナスは付与されません。</t>
+Top Upボーナス中は   &lt;img src = '13' height=50 offset= 5/&gt;   はリールに出現しません。ボーナススピンでは追加のボーナスは付与されません。</t>
   </si>
   <si>
     <t>จะได้รับ 6 สปิน
-สัญลักษณ์   &lt;Sprite=11&gt;   ทั้งหมดที่ปรากฏในสปินที่ทริกเกอร์จะถูกคงไว้ตลอดโบนัส
-หากมี   &lt;Sprite=12&gt;   อย่างน้อย 1 ตัวลงบนหน้าจอ แต่ละ   &lt;Sprite=12&gt;   จะแสดงผลรวมของค่าเครดิตทั้งหมดที่แสดงบนสัญลักษณ์ที่ทริกเกอร์
-หลังจากประเมิน   &lt;Sprite=12&gt;   ทั้งหมดแล้ว   &lt;Sprite=13&gt;   แต่ละตัวที่ลงบนหน้าจอในสปินปัจจุบันจะถูกประเมินทีละตัว
-  &lt;Sprite=13&gt;   จะแสดงผลรวมของค่าเครดิตทั้งหมดที่แสดงอยู่ในตำแหน่งที่ถูกคงไว้ในปัจจุบัน
-  &lt;Sprite=12&gt;   และ   &lt;Sprite=13&gt;   ทุกตัวที่ลงจะถูกคงไว้จนจบโบนัส
+สัญลักษณ์   &lt;img src = '13' height=50 offset= 5/&gt;   ทั้งหมดที่ปรากฏในสปินที่ทริกเกอร์จะถูกคงไว้ตลอดโบนัส
+หากมี   &lt;img src = '12' height=50 offset= 5/&gt;   อย่างน้อย 1 ตัวลงบนหน้าจอ แต่ละ   &lt;img src = '12' height=50 offset= 5/&gt;   จะแสดงผลรวมของค่าเครดิตทั้งหมดที่แสดงบนสัญลักษณ์ที่ทริกเกอร์
+หลังจากประเมิน   &lt;img src = '12' height=50 offset= 5/&gt;   ทั้งหมดแล้ว   &lt;img src = '14' height=50 offset= 5/&gt;   แต่ละตัวที่ลงบนหน้าจอในสปินปัจจุบันจะถูกประเมินทีละตัว
+  &lt;img src = '14' height=50 offset= 5/&gt;   จะแสดงผลรวมของค่าเครดิตทั้งหมดที่แสดงอยู่ในตำแหน่งที่ถูกคงไว้ในปัจจุบัน
+  &lt;img src = '12' height=50 offset= 5/&gt;   และ   &lt;img src = '14' height=50 offset= 5/&gt;   ทุกตัวที่ลงจะถูกคงไว้จนจบโบนัส
 ในแต่ละสปิน หากจำนวนสปินที่เล่นไปแล้วไม่เกิน 12 ครั้ง อาจมี “+1 Spin” ปรากฏในตำแหน่งสุ่มที่ยังไม่ถูกคงไว้
 “+1 Spin” จะมอบสปินเพิ่มเติม 1 ครั้ง
 หากทั้ง 15 ตำแหน่งถูกคงไว้ทั้งหมด จะได้รับค่าที่แสดงในมิเตอร์ Grand Jackpot
-สปินที่เหลือจะเล่นต่อก็ต่อเมื่อมีอย่างน้อย 1 ตำแหน่งที่ไม่ถูกครอบด้วย   &lt;Sprite=11&gt;  ,   &lt;Sprite=12&gt;   หรือ   &lt;Sprite=13&gt;  
-สัญลักษณ์ทั้งหมดบนวงล้อ ยกเว้น “+1 Spin”,   &lt;Sprite=12&gt;   และ   &lt;Sprite=13&gt;   จะถูกแสดงเป็นสีเทาและจะไม่ถูกนำมาประเมิน
+สปินที่เหลือจะเล่นต่อก็ต่อเมื่อมีอย่างน้อย 1 ตำแหน่งที่ไม่ถูกครอบด้วย   &lt;img src = '13' height=50 offset= 5/&gt;  ,   &lt;img src = '12' height=50 offset= 5/&gt;   หรือ   &lt;img src = '14' height=50 offset= 5/&gt;  
+สัญลักษณ์ทั้งหมดบนวงล้อ ยกเว้น “+1 Spin”,   &lt;img src = '12' height=50 offset= 5/&gt;   และ   &lt;img src = '14' height=50 offset= 5/&gt;   จะถูกแสดงเป็นสีเทาและจะไม่ถูกนำมาประเมิน
 ในระหว่าง Top Up Bonus จะใช้ชุดวงล้ออีกชุดหนึ่ง
-ในระหว่าง Top Up Bonus จะไม่มี   &lt;Sprite=11&gt;   ปรากฏบนวงล้อ และโบนัสสปินจะไม่ให้โบนัสเพิ่มเติม</t>
-  </si>
-  <si>
-    <t>UI_POPUP_PAY_PAGE7_TITLE1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI_POPUP_PAY_PAGE7_CONTENTS1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>JACKPOT BONUS</t>
-  </si>
-  <si>
-    <t>累积大奖奖励</t>
-  </si>
-  <si>
-    <t>累積大獎獎勵</t>
-  </si>
-  <si>
-    <t>Jackpot Bonus</t>
-  </si>
-  <si>
-    <t>ジャックポットボーナス</t>
-  </si>
-  <si>
-    <t>โบนัสแจ็กพอต</t>
-  </si>
-  <si>
-    <t>The Jackpot Bonus may be triggered if 1 or more    &lt;Sprite=10&gt;    land on screen during the base game.
-A pick field is displayed with 12    &lt;Sprite=14&gt;   . Picks will reveal one of the available prizes.
+ในระหว่าง Top Up Bonus จะไม่มี   &lt;img src = '13' height=50 offset= 5/&gt;   ปรากฏบนวงล้อ และโบนัสสปินจะไม่ให้โบนัสเพิ่มเติม</t>
+  </si>
+  <si>
+    <t>6 putaran dianugerahkan.
+Semua    &lt;img src = '13' height=50 offset= 5/&gt;    yang muncul pada putaran pencetus dikekalkan semasa bonus.
+Jika 1 atau lebih    &lt;img src = '12' height=50 offset= 5/&gt;    mendarat pada skrin, setiap    &lt;img src = '12' height=50 offset= 5/&gt;    akan memaparkan jumlah semua nilai kredit yang dipaparkan pada simbol pencetus.
+Selepas semua    &lt;img src = '12' height=50 offset= 5/&gt;    dinilai, setiap    &lt;img src = '14' height=50 offset= 5/&gt;    yang mendarat pada skrin bagi putaran semasa dinilai satu demi satu.
+  &lt;img src = '14' height=50 offset= 5/&gt;    memaparkan jumlah semua nilai kredit yang sedang dipaparkan pada kedudukan yang dikekalkan.
+Setiap    &lt;img src = '12' height=50 offset= 5/&gt;    dan    &lt;img src = '14' height=50 offset= 5/&gt;    yang mendarat akan dikekalkan sehingga bonus tamat.
+Setiap putaran, jika bilangan putaran yang dimainkan ialah 12 atau kurang, “+1 Spin” mungkin muncul pada kedudukan rawak yang tidak dikekalkan.
+“+1 Spin” menganugerahkan 1 putaran tambahan.
+Jika kesemua 15 kedudukan dikekalkan, nilai yang dipaparkan dalam meter Grand Jackpot dianugerahkan.
+Putaran yang berbaki hanya akan dimainkan jika terdapat sekurang-kurangnya 1 kedudukan yang tidak diliputi oleh    &lt;img src = '13' height=50 offset= 5/&gt;   ,    &lt;img src = '12' height=50 offset= 5/&gt;   , atau    &lt;img src = '14' height=50 offset= 5/&gt;   .
+Semua simbol selain “+1 Spin”,    &lt;img src = '12' height=50 offset= 5/&gt;   , dan    &lt;img src = '14' height=50 offset= 5/&gt;    yang muncul pada gelung akan dikelabukan dan tidak dinilai.
+Set gelung yang berbeza digunakan semasa Top Up Bonus.
+  &lt;img src = '13' height=50 offset= 5/&gt;    tidak muncul pada gelung semasa Top Up Bonus. Putaran bonus tidak menganugerahkan bonus tambahan.</t>
+  </si>
+  <si>
+    <t>Trao 6 lượt quay.
+Tất cả    &lt;img src = '13' height=50 offset= 5/&gt;    xuất hiện trên lượt quay kích hoạt được giữ lại trong suốt bonus.
+Nếu 1 hoặc nhiều    &lt;img src = '12' height=50 offset= 5/&gt;    rơi trên màn hình, mỗi    &lt;img src = '12' height=50 offset= 5/&gt;    sẽ hiển thị tổng tất cả giá trị tín dụng hiển thị trên các biểu tượng kích hoạt.
+Sau khi tất cả    &lt;img src = '12' height=50 offset= 5/&gt;    được đánh giá, mỗi    &lt;img src = '14' height=50 offset= 5/&gt;    rơi trên màn hình ở lượt quay hiện tại được đánh giá lần lượt từng cái.
+  &lt;img src = '14' height=50 offset= 5/&gt;    hiển thị tổng tất cả giá trị tín dụng hiện đang hiển thị trên các vị trí được giữ.
+Mỗi    &lt;img src = '12' height=50 offset= 5/&gt;    và    &lt;img src = '14' height=50 offset= 5/&gt;    rơi xuống sẽ được giữ cho đến khi kết thúc bonus.
+Mỗi lượt quay, nếu số lượt quay đã chơi là 12 hoặc ít hơn, “+1 Spin” có thể xuất hiện ở một vị trí ngẫu nhiên không được giữ.
+“+1 Spin” trao thêm 1 lượt quay.
+Nếu tất cả 15 vị trí được giữ, giá trị hiển thị trong đồng hồ Grand Jackpot được trao.
+Các lượt quay còn lại chỉ được chơi nếu có ít nhất 1 vị trí không được bao phủ bởi    &lt;img src = '13' height=50 offset= 5/&gt;   ,    &lt;img src = '12' height=50 offset= 5/&gt;   , hoặc    &lt;img src = '14' height=50 offset= 5/&gt;   .
+Tất cả biểu tượng ngoài “+1 Spin”,    &lt;img src = '12' height=50 offset= 5/&gt;   , và    &lt;img src = '14' height=50 offset= 5/&gt;    xuất hiện trên reel sẽ bị làm xám và không được đánh giá.
+Một bộ reel khác được sử dụng trong Top Up Bonus.
+  &lt;img src = '13' height=50 offset= 5/&gt;    không xuất hiện trên reel trong Top Up Bonus. Lượt quay bonus không trao bonus bổ sung.</t>
+  </si>
+  <si>
+    <t>The Jackpot Bonus may be triggered if 1 or more     &lt;img src = '11' height=50 offset=10/&gt;    land on screen during the base game.
+A pick field is displayed with 12     &lt;img src = '16' height=50 offset=10/&gt;   . Picks will reveal one of the available prizes.
 Available prizes include the Mini Jackpot, Minor Jackpot, Major Jackpot, and Grand Jackpot.
 Picks are made until 3 matching symbols are revealed, and the value displayed in the corresponding meter is awarded.
 The accumulation of coins in the bowl increases the chances of triggering the Jackpot Bonus.</t>
   </si>
   <si>
-    <t>기본 게임 중 화면에 1개 이상의   &lt;Sprite=10&gt;  이 등장하면 잭팟 보너스가 트리거될 수 있습니다.
-12개의   &lt;Sprite=14&gt;  로 구성된 선택 필드가 표시됩니다. 선택 시 이용 가능한 보상 중 하나가 공개됩니다.
+    <t>기본 게임 중 화면에 1개 이상의    &lt;img src = '11' height=50 offset=10/&gt;  이 등장하면 잭팟 보너스가 트리거될 수 있습니다.
+12개의    &lt;img src = '16' height=50 offset=10/&gt;  로 구성된 선택 필드가 표시됩니다. 선택 시 이용 가능한 보상 중 하나가 공개됩니다.
 이용 가능한 보상에는 Mini Jackpot, Minor Jackpot, Major Jackpot 및 Grand Jackpot이 포함됩니다.
 3개의 동일한 심볼이 공개될 때까지 선택이 진행되며, 해당 미터에 표시된 값이 지급됩니다.
 볼에 쌓이는 코인의 누적량이 잭팟 보너스 트리거 확률을 증가시킵니다.</t>
   </si>
   <si>
-    <t>在基础游戏期间，如果屏幕上出现1个或以上的   &lt;Sprite=10&gt;  ，则可能触发Jackpot Bonus。
-将显示一个包含12个   &lt;Sprite=14&gt;   的选择区域。每次选择会揭示一个可获得的奖励。
+    <t>在基础游戏期间，如果屏幕上出现1个或以上的    &lt;img src = '11' height=50 offset=10/&gt;  ，则可能触发Jackpot Bonus。
+将显示一个包含12个    &lt;img src = '16' height=50 offset=10/&gt;   的选择区域。每次选择会揭示一个可获得的奖励。
 可获得的奖励包括 Mini Jackpot、Minor Jackpot、Major Jackpot 和 Grand Jackpot。
 选择将持续进行，直到揭示出3个相同的符号，并奖励对应计量器中显示的数值。
 碗中金币的累积会增加触发Jackpot Bonus的概率。</t>
   </si>
   <si>
-    <t>在基礎遊戲期間，如果畫面上出現1個或以上的   &lt;Sprite=10&gt;  ，則可能觸發Jackpot Bonus。
-將顯示一個包含12個   &lt;Sprite=14&gt;   的選擇區域。每次選擇會揭示一個可獲得的獎勵。
+    <t>在基礎遊戲期間，如果畫面上出現1個或以上的    &lt;img src = '11' height=50 offset=10/&gt;  ，則可能觸發Jackpot Bonus。
+將顯示一個包含12個    &lt;img src = '16' height=50 offset=10/&gt;   的選擇區域。每次選擇會揭示一個可獲得的獎勵。
 可獲得的獎勵包括 Mini Jackpot、Minor Jackpot、Major Jackpot 和 Grand Jackpot。
 選擇將持續進行，直到揭示出3個相同的符號，並獎勵對應計量器中顯示的數值。
 碗中金幣的累積會增加觸發Jackpot Bonus的機率。</t>
   </si>
   <si>
-    <t>Maaaring ma-trigger ang Jackpot Bonus kung may 1 o higit pang   &lt;Sprite=10&gt;   na lumapag sa screen sa base game.
-Isang pick field na may 12   &lt;Sprite=14&gt;   ang ipapakita. Ang bawat pick ay magpapakita ng isa sa mga available na premyo.
+    <t>Maaaring ma-trigger ang Jackpot Bonus kung may 1 o higit pang    &lt;img src = '11' height=50 offset=10/&gt;   na lumapag sa screen sa base game.
+Isang pick field na may 12    &lt;img src = '16' height=50 offset=10/&gt;   ang ipapakita. Ang bawat pick ay magpapakita ng isa sa mga available na premyo.
 Kabilang sa mga available na premyo ang Mini Jackpot, Minor Jackpot, Major Jackpot, at Grand Jackpot.
 Magpapatuloy ang pagpili hanggang sa maipakita ang 3 magkakatugmang simbolo, at ang value na ipinapakita sa kaukulang meter ang ibibigay.
 Ang pag-ipon ng mga coin sa bowl ay nagpapataas ng tsansa na ma-trigger ang Jackpot Bonus.</t>
   </si>
   <si>
-    <t>ベースゲーム中に画面上に1つ以上の   &lt;Sprite=10&gt;   が停止した場合、ジャックポットボーナスが発動することがあります。
-12個の   &lt;Sprite=14&gt;   で構成されたピックフィールドが表示されます。選択すると、利用可能な賞のいずれかが表示されます。
+    <t>ベースゲーム中に画面上に1つ以上の    &lt;img src = '11' height=50 offset=10/&gt;   が停止した場合、ジャックポットボーナスが発動することがあります。
+12個の    &lt;img src = '16' height=50 offset=10/&gt;   で構成されたピックフィールドが表示されます。選択すると、利用可能な賞のいずれかが表示されます。
 利用可能な賞には、Mini Jackpot、Minor Jackpot、Major Jackpot、Grand Jackpot が含まれます。
 3つの一致するシンボルが表示されるまで選択が行われ、対応するメーターに表示された値が付与されます。
 ボウルに蓄積されるコインの量が、ジャックポットボーナスの発動確率を高めます。</t>
   </si>
   <si>
-    <t>โบนัสแจ็คพอตอาจถูกทริกเกอร์ หากมี   &lt;Sprite=10&gt;   อย่างน้อย 1 ตัวลงบนหน้าจอในระหว่างเกมหลัก
-จะแสดงหน้าจอเลือกที่มี   &lt;Sprite=14&gt;   จำนวน 12 ตัว การเลือกแต่ละครั้งจะเผยหนึ่งในรางวัลที่มีให้
+    <t>โบนัสแจ็คพอตอาจถูกทริกเกอร์ หากมี    &lt;img src = '11' height=50 offset=10/&gt;   อย่างน้อย 1 ตัวลงบนหน้าจอในระหว่างเกมหลัก
+จะแสดงหน้าจอเลือกที่มี    &lt;img src = '16' height=50 offset=10/&gt;   จำนวน 12 ตัว การเลือกแต่ละครั้งจะเผยหนึ่งในรางวัลที่มีให้
 รางวัลที่มีให้รวมถึง Mini Jackpot, Minor Jackpot, Major Jackpot และ Grand Jackpot
 จะทำการเลือกต่อไปจนกว่าจะพบสัญลักษณ์ที่เหมือนกัน 3 ตัว และจะได้รับค่าที่แสดงในมิเตอร์ที่เกี่ยวข้อง
 การสะสมเหรียญในชามจะเพิ่มโอกาสในการทริกเกอร์โบนัสแจ็คพอต</t>
   </si>
   <si>
-    <t>UI_POPUP_PAY_PAGE8_TITLE1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI_POPUP_PAY_PAGE8_CONTENTS1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GAME RULES</t>
-  </si>
-  <si>
-    <t>游戏规则</t>
-  </si>
-  <si>
-    <t>遊戲規則</t>
-  </si>
-  <si>
-    <t>Mga Patakaran ng Laro</t>
-  </si>
-  <si>
-    <t>ゲームルール</t>
-  </si>
-  <si>
-    <t>กติกาเกม</t>
+    <t>Jackpot Bonus mungkin dicetuskan jika 1 atau lebih     &lt;img src = '11' height=50 offset=10/&gt;    mendarat pada skrin semasa base game.
+Medan pilihan dengan 12     &lt;img src = '16' height=50 offset=10/&gt;    dipaparkan. Pilihan akan mendedahkan salah satu hadiah yang tersedia.
+Hadiah yang tersedia termasuk Mini Jackpot, Minor Jackpot, Major Jackpot, dan Grand Jackpot.
+Pilihan dibuat sehingga 3 simbol yang sepadan didedahkan, dan nilai yang dipaparkan dalam meter yang berkaitan dianugerahkan.
+Pengumpulan syiling dalam mangkuk meningkatkan peluang mencetuskan Jackpot Bonus.</t>
+  </si>
+  <si>
+    <t>Jackpot Bonus có thể được kích hoạt nếu 1 hoặc nhiều     &lt;img src = '11' height=50 offset=10/&gt;    rơi trên màn hình trong trò chơi cơ bản.
+Một vùng chọn với 12     &lt;img src = '16' height=50 offset=10/&gt;    được hiển thị. Mỗi lần chọn sẽ tiết lộ một trong các giải thưởng có sẵn.
+Các giải thưởng có sẵn bao gồm Mini Jackpot, Minor Jackpot, Major Jackpot, và Grand Jackpot.
+Việc chọn tiếp tục cho đến khi 3 biểu tượng khớp nhau được tiết lộ, và giá trị hiển thị trong đồng hồ tương ứng được trao.
+Việc tích lũy xu trong bát làm tăng cơ hội kích hoạt Jackpot Bonus.</t>
   </si>
   <si>
     <t>If the same symbol appears at least once on each reel and there are 3 or more in sequence from left to right, it results in a win.
@@ -2972,7 +2589,7 @@
 The total win from the feature is recorded in the history as the cumulative win of the entire cycle.
 Jackpot winnings earned during the feature are recorded in the history.
 The SPACE and ENTER keys on the keyboard can be used to start or stop the spin.
-&lt;color=yellow&gt;The theoretical RTP of this game is 95.81%. &lt;color=white&gt;
+&lt;color=#fff71f&gt;The theoretical RTP of this game is 95.81%. &lt;/color&gt;
 In the event of a malfunction, all bets and pays are void.
 The game's Return to Player (RTP) is guaranteed to be achieved within 100,000,000 rounds of play.</t>
   </si>
@@ -2985,7 +2602,7 @@
 피처에서의 총 당첨금은 전체 사이클의 누적 당첨금으로 기록됩니다.
 피처 동안 획득한 잭팟 당첨금은 히스토리에 기록됩니다.
 키보드의 SPACE 및 ENTER 키를 사용하여 스핀을 시작하거나 중지할 수 있습니다.
-&lt;color=yellow&gt;이 게임의 이론적 RTP는 95.81%입니다. &lt;color=white&gt;
+&lt;color=#fff71f&gt;이 게임의 이론적 RTP는 95.81%입니다. &lt;/color&gt;
 오류가 발생한 경우 모든 베팅 및 당첨은 무효 처리됩니다.
 이 게임의 RTP는 100,000,000회 플레이 내에 달성되도록 보장됩니다.</t>
   </si>
@@ -2998,7 +2615,7 @@
 功能中的总中奖金额将作为整个周期的累计中奖金额记录在历史中。
 功能期间获得的Jackpot中奖将记录在历史中。
 键盘上的SPACE和ENTER键可用于开始或停止旋转。
-&lt;color=yellow&gt;本游戏的理论RTP为95.81%。 &lt;color=white&gt;
+&lt;color=#fff71f&gt;本游戏的理论RTP为95.81%。 &lt;/color&gt;
 若发生故障，所有投注和支付均无效。
 本游戏的RTP保证在100,000,000次游戏中实现。</t>
   </si>
@@ -3011,7 +2628,7 @@
 功能中的總中獎金額將作為整個週期的累計中獎金額記錄在歷史中。
 功能期間獲得的Jackpot中獎將記錄在歷史中。
 鍵盤上的SPACE和ENTER鍵可用於開始或停止旋轉。
-&lt;color=yellow&gt;本遊戲的理論RTP為95.81%。 &lt;color=white&gt;
+&lt;color=#fff71f&gt;本遊戲的理論RTP為95.81%。 &lt;/color&gt;
 若發生故障，所有投注和支付均無效。
 本遊戲的RTP保證在100,000,000次遊戲中實現。</t>
   </si>
@@ -3024,7 +2641,7 @@
 Ang kabuuang panalo mula sa feature ay itinatala sa history bilang pinagsama-samang panalo ng buong cycle.
 Ang jackpot winnings na nakuha sa panahon ng feature ay itinatala sa history.
 Ang SPACE at ENTER keys sa keyboard ay maaaring gamitin upang simulan o ihinto ang spin.
-&lt;color=yellow&gt;Ang teoretikal na RTP ng larong ito ay 95.81%. &lt;color=white&gt;
+&lt;color=#fff71f&gt;Ang teoretikal na RTP ng larong ito ay 95.81%. &lt;/color&gt;
 Sa kaso ng malfunction, lahat ng bet at payout ay walang bisa.
 Ang RTP ng laro ay garantisadong maaabot sa loob ng 100,000,000 rounds ng paglalaro.</t>
   </si>
@@ -3037,7 +2654,7 @@
 フィーチャーでの総当選額は、全サイクルの累計当選額として履歴に記録されます。
 フィーチャー中に獲得したジャックポット当選は履歴に記録されます。
 キーボードのSPACEキーおよびENTERキーでスピンの開始または停止が可能です。
-&lt;color=yellow&gt;本ゲームの理論RTPは95.81%です。 &lt;color=white&gt;
+&lt;color=#fff71f&gt;本ゲームの理論RTPは95.81%です。 &lt;/color&gt;
 不具合が発生した場合、すべてのベットおよび支払いは無効となります。
 本ゲームのRTPは100,000,000回のプレイ内で達成されることが保証されています。</t>
   </si>
@@ -3050,500 +2667,9 @@
 ยอดชนะรวมจากฟีเจอร์จะถูกบันทึกในประวัติเป็นยอดชนะสะสมของทั้งรอบ
 เงินรางวัลแจ็คพอตที่ได้รับในระหว่างฟีเจอร์จะถูกบันทึกในประวัติ
 สามารถใช้ปุ่ม SPACE และ ENTER บนคีย์บอร์ดเพื่อเริ่มหรือหยุดการหมุน
-&lt;color=yellow&gt;ค่า RTP ตามทฤษฎีของเกมนี้คือ 95.81% &lt;color=white&gt;
+&lt;color=#fff71f&gt;ค่า RTP ตามทฤษฎีของเกมนี้คือ 95.81% &lt;/color&gt;
 ในกรณีที่เกิดความผิดพลาด การเดิมพันและการจ่ายทั้งหมดจะถือเป็นโมฆะ
 RTP ของเกมนี้รับประกันว่าจะบรรลุภายใน 100,000,000 รอบการเล่น</t>
-  </si>
-  <si>
-    <t>S$</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RM</t>
-  </si>
-  <si>
-    <t>₫</t>
-  </si>
-  <si>
-    <t>Singapore(sg)</t>
-  </si>
-  <si>
-    <t>Malaysia(ms)</t>
-  </si>
-  <si>
-    <t>Vietnam(vi)</t>
-  </si>
-  <si>
-    <t>Pelancaran pertama mungkin mengambil masa lebih lama untuk dimuatkan.</t>
-  </si>
-  <si>
-    <t>Lần khởi chạy đầu tiên có thể mất nhiều thời gian tải hơn.</t>
-  </si>
-  <si>
-    <t>TEMUI PELBAGAI CIRI DAN KEJUTAN!</t>
-  </si>
-  <si>
-    <t>KHÁM PHÁ CÁC TÍNH NĂNG VÀ BẤT NGỜ KHÁC NHAU!</t>
-  </si>
-  <si>
-    <t>KETIK KEGEMARAN ANDA, LEPASKAN KESERONOKAN!</t>
-  </si>
-  <si>
-    <t>CHẠM VÀO MỤC YÊU THÍCH, GIẢI PHÓNG NIỀM VUI!</t>
-  </si>
-  <si>
-    <t>TEMUI KEGEMBIRAAN REZEKI YANG TIDAK DISANGKA!</t>
-  </si>
-  <si>
-    <t>KHÁM PHÁ SỰ PHẤN KHÍCH CỦA VẬN MAY BẤT NGỜ!</t>
-  </si>
-  <si>
-    <t>MASUK KE FREE SPINS DAN HADAPI LEGENDA PURBA!</t>
-  </si>
-  <si>
-    <t>VÀO FREE SPINS VÀ ĐỐI MẶT VỚI HUYỀN THOẠI CỔ ĐẠI!</t>
-  </si>
-  <si>
-    <t>HARAPKAN LEBIH BANYAK SIMBOL MERAH DAN HIJAU BERSINAR!</t>
-  </si>
-  <si>
-    <t>HÃY HY VỌNG NHIỀU BIỂU TƯỢNG ĐỎ VÀ XANH LÁ TỎA SÁNG HƠN!</t>
-  </si>
-  <si>
-    <t>DEDAHKAN ARTIFAK PURBA MENERUSI MATA RA!</t>
-  </si>
-  <si>
-    <t>KHÁM PHÁ NHỮNG DI VẬT CỔ ĐẠI QUA CON MẮT CỦA RA!</t>
-  </si>
-  <si>
-    <t>TARUHAN</t>
-  </si>
-  <si>
-    <t>CƯỢC</t>
-  </si>
-  <si>
-    <t>KREDIT</t>
-  </si>
-  <si>
-    <t>TÍN DỤNG</t>
-  </si>
-  <si>
-    <t>KLIK UNTUK BERTUKAR ANTARA
-PAPARAN WANG DAN SYILING</t>
-  </si>
-  <si>
-    <t>NHẤP ĐỂ CHUYỂN GIỮA
-CHẾ ĐỘ XEM TIỀN VÀ XU</t>
-  </si>
-  <si>
-    <t>SEMOGA BERJAYA!</t>
-  </si>
-  <si>
-    <t>CHÚC MAY MẮN!</t>
-  </si>
-  <si>
-    <t>LETAKKAN TARUHAN ANDA!</t>
-  </si>
-  <si>
-    <t>ĐẶT CƯỢC CỦA BẠN!</t>
-  </si>
-  <si>
-    <t>PUTAR UNTUK MENANG!</t>
-  </si>
-  <si>
-    <t>QUAY ĐỂ THẮNG!</t>
-  </si>
-  <si>
-    <t>AUTO SPIN BERBAKI</t>
-  </si>
-  <si>
-    <t>SỐ AUTO SPIN CÒN LẠI</t>
-  </si>
-  <si>
-    <t>FREE SPIN BERBAKI</t>
-  </si>
-  <si>
-    <t>SỐ FREE SPIN CÒN LẠI</t>
-  </si>
-  <si>
-    <t>JUMLAH KEMENANGAN</t>
-  </si>
-  <si>
-    <t>TỔNG TIỀN THẮNG</t>
-  </si>
-  <si>
-    <t>MENANG</t>
-  </si>
-  <si>
-    <t>THẮNG</t>
-  </si>
-  <si>
-    <t>TETAPAN AUTOPLAY</t>
-  </si>
-  <si>
-    <t>CÀI ĐẶT AUTOPLAY</t>
-  </si>
-  <si>
-    <t>BILANGAN AUTOSPIN</t>
-  </si>
-  <si>
-    <t>SỐ LƯỢNG AUTOSPIN</t>
-  </si>
-  <si>
-    <t>PUTARAN PANTAS</t>
-  </si>
-  <si>
-    <t>QUAY NHANH</t>
-  </si>
-  <si>
-    <t>MULAKAN AUTOPLAY ({Count})</t>
-  </si>
-  <si>
-    <t>BẮT ĐẦU AUTOPLAY ({Count})</t>
-  </si>
-  <si>
-    <t>PUTARAN TURBO</t>
-  </si>
-  <si>
-    <t>QUAY TURBO</t>
-  </si>
-  <si>
-    <t>PENGGANDA TARUHAN</t>
-  </si>
-  <si>
-    <t>HỆ SỐ NHÂN CƯỢC</t>
-  </si>
-  <si>
-    <t>NILAI SYILING</t>
-  </si>
-  <si>
-    <t>GIÁ TRỊ XU</t>
-  </si>
-  <si>
-    <t>TARUHAN MAKS</t>
-  </si>
-  <si>
-    <t>CƯỢC TỐI ĐA</t>
-  </si>
-  <si>
-    <t>JUMLAH TARUHAN</t>
-  </si>
-  <si>
-    <t>TỔNG CƯỢC</t>
-  </si>
-  <si>
-    <t>AKTIFKAN</t>
-  </si>
-  <si>
-    <t>KÍCH HOẠT</t>
-  </si>
-  <si>
-    <t>BELI</t>
-  </si>
-  <si>
-    <t>MUA</t>
-  </si>
-  <si>
-    <t>BATAL</t>
-  </si>
-  <si>
-    <t>HỦY</t>
-  </si>
-  <si>
-    <t>BELI BONUS</t>
-  </si>
-  <si>
-    <t>MUA BONUS</t>
-  </si>
-  <si>
-    <t>TETAPAN SISTEM</t>
-  </si>
-  <si>
-    <t>CÀI ĐẶT HỆ THỐNG</t>
-  </si>
-  <si>
-    <t>MUZIK LATAR</t>
-  </si>
-  <si>
-    <t>NHẠC NỀN</t>
-  </si>
-  <si>
-    <t>HIDUPKAN ATAU MATIKAN 
-MUZIK PERMAINAN</t>
-  </si>
-  <si>
-    <t>BẬT HOẶC TẮT 
- NHẠC TRÒ CHƠI</t>
-  </si>
-  <si>
-    <t>SIARAN</t>
-  </si>
-  <si>
-    <t>PHÁT SÓNG</t>
-  </si>
-  <si>
-    <t>HIDUPKAN ATAU MATIKAN
-SIARAN KEMENANGAN PERMAINAN</t>
-  </si>
-  <si>
-    <t>BẬT HOẶC TẮT
-PHÁT SÓNG CHIẾN THẮNG TRÒ CHƠI</t>
-  </si>
-  <si>
-    <t>SKRIN PENGENALAN</t>
-  </si>
-  <si>
-    <t>MÀN HÌNH GIỚI THIỆU</t>
-  </si>
-  <si>
-    <t>PAPARKAN SKRIN PENGENALAN SEBELUM 
-MEMULAKAN PERMAINAN</t>
-  </si>
-  <si>
-    <t>HIỂN THỊ MÀN HÌNH GIỚI THIỆU TRƯỚC 
-KHI BẮT ĐẦU TRÒ CHƠI</t>
-  </si>
-  <si>
-    <t>KESAN BUNYI</t>
-  </si>
-  <si>
-    <t>HIỆU ỨNG ÂM THANH</t>
-  </si>
-  <si>
-    <t>HIDUPKAN ATAU MATIKAN 
-BUNYI PERMAINAN</t>
-  </si>
-  <si>
-    <t>BẬT HOẶC TẮT 
-ÂM THANH TRÒ CHƠI</t>
-  </si>
-  <si>
-    <t>KELANTANGAN</t>
-  </si>
-  <si>
-    <t>ÂM LƯỢNG</t>
-  </si>
-  <si>
-    <t>SAHKAN</t>
-  </si>
-  <si>
-    <t>XÁC NHẬN</t>
-  </si>
-  <si>
-    <t>Rangkaian</t>
-  </si>
-  <si>
-    <t>Mạng</t>
-  </si>
-  <si>
-    <t>Anda telah terputus sambungan daripada pelayan.</t>
-  </si>
-  <si>
-    <t>Bạn đã bị ngắt kết nối khỏi máy chủ.</t>
-  </si>
-  <si>
-    <t>Log Masuk Semula</t>
-  </si>
-  <si>
-    <t>Đăng nhập lại</t>
-  </si>
-  <si>
-    <t>BAKI TIDAK MENCUKUPI</t>
-  </si>
-  <si>
-    <t>SỐ DƯ KHÔNG ĐỦ</t>
-  </si>
-  <si>
-    <t>Sila tambah nilai dana dalam dompet tunai anda.
-Jika baki tidak dikemas kini selepas tambah nilai,
-sila muat semula dompet tunai anda.</t>
-  </si>
-  <si>
-    <t>Vui lòng nạp tiền vào ví tiền mặt của bạn.
-Nếu số dư không được cập nhật sau khi nạp,
-vui lòng làm mới ví tiền mặt của bạn.</t>
-  </si>
-  <si>
-    <t>Ralat</t>
-  </si>
-  <si>
-    <t>Lỗi</t>
-  </si>
-  <si>
-    <t>ID Simbol salah.
-Anda telah terputus sambungan daripada pelayan.</t>
-  </si>
-  <si>
-    <t>ID Biểu tượng sai.
-Bạn đã bị ngắt kết nối khỏi máy chủ.</t>
-  </si>
-  <si>
-    <t>Pautan permainan ini telah tamat tempoh.</t>
-  </si>
-  <si>
-    <t>Liên kết trò chơi này đã hết hạn.</t>
-  </si>
-  <si>
-    <t>Permintaan tidak sah.</t>
-  </si>
-  <si>
-    <t>Yêu cầu không hợp lệ.</t>
-  </si>
-  <si>
-    <t>Dalam permainan bonus, &lt;Sprite=10&gt; kekal pada papan dan meningkatkan peluang kemenangan anda.                    Apabila anda mengumpul &lt;Sprite=11&gt;, anda menerima hadiah simbol.                    &lt;Sprite=10&gt; kekal di medan sehingga permainan tamat. Apabila ia bertindan, pengganda meningkat.</t>
-  </si>
-  <si>
-    <t>Trong trò chơi bonus, &lt;Sprite=10&gt; vẫn ở trên bảng và tăng cơ hội thắng của bạn.                    Khi bạn thu thập &lt;Sprite=11&gt;, bạn nhận được phần thưởng biểu tượng.                    &lt;Sprite=10&gt; vẫn ở trên sân cho đến khi trò chơi kết thúc. Khi nó xếp chồng, hệ số nhân tăng lên.</t>
-  </si>
-  <si>
-    <t>Setiap kali  &lt;Sprite=11&gt;  muncul, anda dianugerahkan hadiah simbol.</t>
-  </si>
-  <si>
-    <t>Mỗi khi  &lt;Sprite=11&gt;  xuất hiện, bạn được trao phần thưởng biểu tượng.</t>
-  </si>
-  <si>
-    <t>BAYARAN</t>
-  </si>
-  <si>
-    <t>TRẢ THƯỞNG</t>
-  </si>
-  <si>
-    <t>Sebelum putaran gelung base game bermula, beberapa kedudukan digantikan dengan mana-mana satu simbol kecuali  &lt;Sprite=10&gt;  dan  &lt;Sprite=11&gt; . 
-Hanya kemenangan tertinggi dibayar bagi setiap kombinasi menang.
-Kombinasi menang hanya boleh mengandungi satu simbol daripada setiap gelung bersebelahan, bermula dari gelung paling kiri.
-Simbol yang sama, atau penggantinya, pada satu gelung bukan sebahagian daripada kombinasi menang yang sama, tetapi boleh mencipta kombinasi menang yang berasingan.
-Semua kemenangan ways didarab dengan pengganda taruhan.</t>
-  </si>
-  <si>
-    <t>Trước khi reel của trò chơi cơ bản bắt đầu quay, một số vị trí được thay thế bằng bất kỳ biểu tượng nào ngoại trừ  &lt;Sprite=10&gt;  và  &lt;Sprite=11&gt; . 
-Chỉ phần thắng cao nhất được trả cho mỗi tổ hợp thắng.
-Các tổ hợp thắng chỉ có thể chứa một biểu tượng từ mỗi reel liền kề, bắt đầu từ reel ngoài cùng bên trái.
-Các biểu tượng giống nhau, hoặc biểu tượng thay thế, trên cùng một reel không thuộc cùng một tổ hợp thắng, nhưng có thể tạo ra các tổ hợp thắng riêng biệt.
-Tất cả phần thắng theo ways đều được nhân với hệ số nhân cược.</t>
-  </si>
-  <si>
-    <t>muncul pada gelung 2, 3, dan 4 dan menjadi WILD untuk semua simbol yang muncul dalam base game kecuali  &lt;Sprite=11&gt; .</t>
-  </si>
-  <si>
-    <t>xuất hiện trên reel 2, 3 và 4 và là WILD cho tất cả biểu tượng xuất hiện trong trò chơi cơ bản ngoại trừ  &lt;Sprite=11&gt; .</t>
-  </si>
-  <si>
-    <t>Semasa base game, setiap  &lt;Sprite=11&gt;  akan memaparkan nilai kredit antara 10% dan 500% daripada jumlah taruhan.</t>
-  </si>
-  <si>
-    <t>Trong trò chơi cơ bản, mỗi  &lt;Sprite=11&gt;  sẽ hiển thị giá trị tín dụng từ 10% đến 500% tổng số tiền cược.</t>
-  </si>
-  <si>
-    <t>TUAH TIDAK DISANGKA</t>
-  </si>
-  <si>
-    <t>MAY MẮN BẤT NGỜ</t>
-  </si>
-  <si>
-    <t>Tanpa mengira bilangan &lt;Sprite=0&gt; yang dikumpulkan daripada hasil gelung, Feature Game mungkin dicetuskan secara rawak. 
-Jika peristiwa bertuah berlaku, sebahagian simbol yang muncul pada gelung akan bertukar menjadi &lt;Sprite=0&gt; sehingga
-keperluan minimum 6 Shou Symbols untuk kemasukan Feature dipenuhi.
-&lt;Sprite=0&gt; yang ditukar akan diberikan Credit Value berdasarkan peluang rawak, selepas itu skrin Feature Select akan dipaparkan.
-Peristiwa bertuah ini boleh berlaku walaupun tiada &lt;Sprite=0&gt; muncul dalam hasil gelung, dan keputusannya ditentukan secara bebas pada setiap putaran.</t>
-  </si>
-  <si>
-    <t>Bất kể số lượng &lt;Sprite=0&gt; thu thập được từ kết quả reel, Feature Game có thể được kích hoạt ngẫu nhiên. 
-Nếu một sự kiện may mắn xảy ra, một số biểu tượng xuất hiện trên reel sẽ biến đổi thành &lt;Sprite=0&gt; cho đến khi
-đạt được yêu cầu tối thiểu 6 Shou Symbols để vào Feature.
-&lt;Sprite=0&gt; đã biến đổi sẽ được gán Credit Value dựa trên cơ hội ngẫu nhiên, sau đó màn hình Feature Select sẽ được hiển thị.
-Sự kiện may mắn này có thể xảy ra ngay cả khi không có &lt;Sprite=0&gt; nào xuất hiện trong kết quả reel, và kết quả được xác định độc lập trên mỗi lượt quay.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 atau lebih  &lt;Sprite=11&gt;  yang bertaburan semasa base game akan menganugerahkan jumlah nilai yang dipaparkan pada  &lt;Sprite=11&gt;  dan Feature Selection.
-Jika sekurang-kurangnya 1 kedudukan tidak mengandungi &lt;Sprite=11&gt;, maka Feature Selection menawarkan pilihan Free Games Bonus atau Top Up Bonus.
-&lt;Sprite=11&gt;  dan &lt;Sprite=10&gt; tidak muncul semasa Free Games Bonus.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 hoặc nhiều  &lt;Sprite=11&gt;  rải rác trong trò chơi cơ bản sẽ trao tổng các giá trị hiển thị trên  &lt;Sprite=11&gt;  và Feature Selection.
-Nếu có ít nhất 1 vị trí không chứa &lt;Sprite=11&gt;, thì Feature Selection cung cấp lựa chọn Free Games Bonus hoặc Top Up Bonus.
-&lt;Sprite=11&gt;  và &lt;Sprite=10&gt; không xuất hiện trong Free Games Bonus.
-</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5 High Symbols: Free Games Bonus dengan nilai 128     &lt;Sprite=6&gt; , 118     &lt;Sprite=7&gt; , 108     &lt;Sprite=8&gt; , 98     &lt;Sprite=9&gt; , atau 88     &lt;Sprite=10&gt; , atau Top Up Bonus dengan nilai 88     &lt;Sprite=10&gt;  dianugerahkan. &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5 High Symbols: Một Free Games Bonus với giá trị 128     &lt;Sprite=6&gt; , 118     &lt;Sprite=7&gt; , 108     &lt;Sprite=8&gt; , 98     &lt;Sprite=9&gt; , hoặc 88     &lt;Sprite=10&gt; , hoặc một Top Up Bonus với giá trị 88     &lt;Sprite=10&gt;  được trao. &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>Hanya simbol yang dipilih,       &lt;Sprite=2&gt;  ,       &lt;Sprite=0&gt;  ,       &lt;Sprite=5&gt;  ,       &lt;Sprite=1&gt;  ,       &lt;Sprite=4&gt;  ,       &lt;Sprite=3&gt;  , dan  &lt;Sprite=11&gt;  akan muncul semasa Free Games Bonus.</t>
-  </si>
-  <si>
-    <t>Chỉ biểu tượng được chọn,       &lt;Sprite=2&gt;  ,       &lt;Sprite=0&gt;  ,       &lt;Sprite=5&gt;  ,       &lt;Sprite=1&gt;  ,       &lt;Sprite=4&gt;  ,       &lt;Sprite=3&gt;  , và  &lt;Sprite=11&gt;  sẽ xuất hiện trong Free Games Bonus.</t>
-  </si>
-  <si>
-    <t>6 free game dianugerahkan.
-Jika sekurang-kurangnya 1  &lt;Sprite=12&gt;  muncul pada skrin, maka jumlah semua nilai yang dipaparkan pada simbol pencetus dianugerahkan bagi setiap  &lt;Sprite=12&gt;  pada skrin.
-Selain itu, jika Top Up Bonus tersedia semasa Feature Selection, nilai yang dipaparkan pada meter Fortune Grand Jackpot mungkin dianugerahkan.
-Set gelung yang berbeza digunakan semasa Free Games Bonus. Kombinasi menang bagi gelung ini adalah sama seperti base game kecuali jika dinyatakan sebaliknya.
-&lt;Sprite=12&gt;  hanya muncul pada gelung 2–4 dan menjadi WILD untuk semua simbol kecuali  &lt;Sprite=11&gt;  .
-“Shou Bonus” semasa Free Games Bonus ialah jumlah kumulatif semua  &lt;Sprite=12&gt;  dan jumlah semua nilai yang dipaparkan pada setiap  &lt;Sprite=11&gt;  semasa base game.
-“Shou Bonus” tidak termasuk sebarang jackpot yang dianugerahkan.</t>
-  </si>
-  <si>
-    <t>Trao 6 free game.
-Nếu có ít nhất 1  &lt;Sprite=12&gt;  xuất hiện trên màn hình, thì tổng tất cả giá trị hiển thị trên các biểu tượng kích hoạt được trao cho mỗi  &lt;Sprite=12&gt;  trên màn hình.
-Ngoài ra, nếu Top Up Bonus có sẵn trong Feature Selection, giá trị hiển thị trên đồng hồ Fortune Grand Jackpot có thể được trao.
-Một bộ reel khác được sử dụng trong Free Games Bonus. Các tổ hợp thắng cho những reel này giống hệt trò chơi cơ bản trừ khi có quy định khác.
-&lt;Sprite=12&gt;  chỉ xuất hiện trên reel 2–4 và là WILD cho tất cả biểu tượng ngoại trừ  &lt;Sprite=11&gt;  .
-“Shou Bonus” trong Free Games Bonus là tổng phần thưởng tích lũy của tất cả  &lt;Sprite=12&gt;  và tổng tất cả giá trị hiển thị trên mỗi  &lt;Sprite=11&gt;  trong trò chơi cơ bản.
-“Shou Bonus” không bao gồm bất kỳ jackpot nào được trao.</t>
-  </si>
-  <si>
-    <t>6 putaran dianugerahkan.
-Semua    &lt;Sprite=11&gt;    yang muncul pada putaran pencetus dikekalkan semasa bonus.
-Jika 1 atau lebih    &lt;Sprite=12&gt;    mendarat pada skrin, setiap    &lt;Sprite=12&gt;    akan memaparkan jumlah semua nilai kredit yang dipaparkan pada simbol pencetus.
-Selepas semua    &lt;Sprite=12&gt;    dinilai, setiap    &lt;Sprite=13&gt;    yang mendarat pada skrin bagi putaran semasa dinilai satu demi satu.
-  &lt;Sprite=13&gt;    memaparkan jumlah semua nilai kredit yang sedang dipaparkan pada kedudukan yang dikekalkan.
-Setiap    &lt;Sprite=12&gt;    dan    &lt;Sprite=13&gt;    yang mendarat akan dikekalkan sehingga bonus tamat.
-Setiap putaran, jika bilangan putaran yang dimainkan ialah 12 atau kurang, “+1 Spin” mungkin muncul pada kedudukan rawak yang tidak dikekalkan.
-“+1 Spin” menganugerahkan 1 putaran tambahan.
-Jika kesemua 15 kedudukan dikekalkan, nilai yang dipaparkan dalam meter Grand Jackpot dianugerahkan.
-Putaran yang berbaki hanya akan dimainkan jika terdapat sekurang-kurangnya 1 kedudukan yang tidak diliputi oleh    &lt;Sprite=11&gt;   ,    &lt;Sprite=12&gt;   , atau    &lt;Sprite=13&gt;   .
-Semua simbol selain “+1 Spin”,    &lt;Sprite=12&gt;   , dan    &lt;Sprite=13&gt;    yang muncul pada gelung akan dikelabukan dan tidak dinilai.
-Set gelung yang berbeza digunakan semasa Top Up Bonus.
-  &lt;Sprite=11&gt;    tidak muncul pada gelung semasa Top Up Bonus. Putaran bonus tidak menganugerahkan bonus tambahan.</t>
-  </si>
-  <si>
-    <t>Trao 6 lượt quay.
-Tất cả    &lt;Sprite=11&gt;    xuất hiện trên lượt quay kích hoạt được giữ lại trong suốt bonus.
-Nếu 1 hoặc nhiều    &lt;Sprite=12&gt;    rơi trên màn hình, mỗi    &lt;Sprite=12&gt;    sẽ hiển thị tổng tất cả giá trị tín dụng hiển thị trên các biểu tượng kích hoạt.
-Sau khi tất cả    &lt;Sprite=12&gt;    được đánh giá, mỗi    &lt;Sprite=13&gt;    rơi trên màn hình ở lượt quay hiện tại được đánh giá lần lượt từng cái.
-  &lt;Sprite=13&gt;    hiển thị tổng tất cả giá trị tín dụng hiện đang hiển thị trên các vị trí được giữ.
-Mỗi    &lt;Sprite=12&gt;    và    &lt;Sprite=13&gt;    rơi xuống sẽ được giữ cho đến khi kết thúc bonus.
-Mỗi lượt quay, nếu số lượt quay đã chơi là 12 hoặc ít hơn, “+1 Spin” có thể xuất hiện ở một vị trí ngẫu nhiên không được giữ.
-“+1 Spin” trao thêm 1 lượt quay.
-Nếu tất cả 15 vị trí được giữ, giá trị hiển thị trong đồng hồ Grand Jackpot được trao.
-Các lượt quay còn lại chỉ được chơi nếu có ít nhất 1 vị trí không được bao phủ bởi    &lt;Sprite=11&gt;   ,    &lt;Sprite=12&gt;   , hoặc    &lt;Sprite=13&gt;   .
-Tất cả biểu tượng ngoài “+1 Spin”,    &lt;Sprite=12&gt;   , và    &lt;Sprite=13&gt;    xuất hiện trên reel sẽ bị làm xám và không được đánh giá.
-Một bộ reel khác được sử dụng trong Top Up Bonus.
-  &lt;Sprite=11&gt;    không xuất hiện trên reel trong Top Up Bonus. Lượt quay bonus không trao bonus bổ sung.</t>
-  </si>
-  <si>
-    <t>Jackpot Bonus mungkin dicetuskan jika 1 atau lebih    &lt;Sprite=10&gt;    mendarat pada skrin semasa base game.
-Medan pilihan dengan 12    &lt;Sprite=14&gt;    dipaparkan. Pilihan akan mendedahkan salah satu hadiah yang tersedia.
-Hadiah yang tersedia termasuk Mini Jackpot, Minor Jackpot, Major Jackpot, dan Grand Jackpot.
-Pilihan dibuat sehingga 3 simbol yang sepadan didedahkan, dan nilai yang dipaparkan dalam meter yang berkaitan dianugerahkan.
-Pengumpulan syiling dalam mangkuk meningkatkan peluang mencetuskan Jackpot Bonus.</t>
-  </si>
-  <si>
-    <t>Jackpot Bonus có thể được kích hoạt nếu 1 hoặc nhiều    &lt;Sprite=10&gt;    rơi trên màn hình trong trò chơi cơ bản.
-Một vùng chọn với 12    &lt;Sprite=14&gt;    được hiển thị. Mỗi lần chọn sẽ tiết lộ một trong các giải thưởng có sẵn.
-Các giải thưởng có sẵn bao gồm Mini Jackpot, Minor Jackpot, Major Jackpot, và Grand Jackpot.
-Việc chọn tiếp tục cho đến khi 3 biểu tượng khớp nhau được tiết lộ, và giá trị hiển thị trong đồng hồ tương ứng được trao.
-Việc tích lũy xu trong bát làm tăng cơ hội kích hoạt Jackpot Bonus.</t>
-  </si>
-  <si>
-    <t>PERATURAN PERMAINAN</t>
-  </si>
-  <si>
-    <t>LUẬT CHƠI</t>
   </si>
   <si>
     <t>Jika simbol yang sama muncul sekurang-kurangnya sekali pada setiap gelung dan terdapat 3 atau lebih secara berturutan dari kiri ke kanan, ia menghasilkan kemenangan.
@@ -3554,7 +2680,7 @@
 Jumlah kemenangan daripada feature direkodkan dalam sejarah sebagai kemenangan kumulatif bagi keseluruhan kitaran.
 Kemenangan jackpot yang diperoleh semasa feature direkodkan dalam sejarah.
 Kekunci SPACE dan ENTER pada papan kekunci boleh digunakan untuk memulakan atau menghentikan putaran.
-&lt;color=yellow&gt;RTP teori permainan ini ialah 95.81%. &lt;color=white&gt;
+&lt;color=#fff71f&gt;RTP teori permainan ini ialah 95.81%. &lt;/color&gt;
 Sekiranya berlaku kerosakan, semua taruhan dan bayaran adalah terbatal.
 Return to Player (RTP) permainan ini dijamin dicapai dalam 100,000,000 pusingan permainan.</t>
   </si>
@@ -3567,7 +2693,7 @@
 Tổng tiền thắng từ feature được ghi vào lịch sử dưới dạng tiền thắng tích lũy của toàn bộ chu kỳ.
 Tiền thắng jackpot kiếm được trong feature được ghi vào lịch sử.
 Phím SPACE và ENTER trên bàn phím có thể được dùng để bắt đầu hoặc dừng lượt quay.
-&lt;color=yellow&gt;RTP lý thuyết của trò chơi này là 95.81%. &lt;color=white&gt;
+&lt;color=#fff71f&gt;RTP lý thuyết của trò chơi này là 95.81%. &lt;/color&gt;
 Trong trường hợp trục trặc, tất cả cược và trả thưởng đều vô hiệu.
 Return to Player (RTP) của trò chơi được đảm bảo đạt được trong vòng 100.000.000 vòng chơi.</t>
   </si>
@@ -3576,18 +2702,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -3596,44 +2722,10 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="222"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="222"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3645,7 +2737,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -3653,7 +2745,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -3733,16 +2825,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3750,7 +2842,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3766,7 +2858,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -4105,14 +3197,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DD518D4-2F94-4794-93C6-9F38EEF821C0}">
   <dimension ref="A1:L80"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="52.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="12" width="60.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -4141,16 +3233,16 @@
         <v>8</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>606</v>
+        <v>527</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>607</v>
+        <v>528</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="30">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -4182,13 +3274,13 @@
         <v>11</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>609</v>
+        <v>530</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>347</v>
       </c>
@@ -4220,13 +3312,13 @@
         <v>365</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>611</v>
+        <v>532</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
         <v>349</v>
       </c>
@@ -4258,13 +3350,13 @@
         <v>366</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>613</v>
+        <v>534</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="5" t="s">
         <v>350</v>
       </c>
@@ -4296,13 +3388,13 @@
         <v>373</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>615</v>
+        <v>536</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
         <v>351</v>
       </c>
@@ -4334,13 +3426,13 @@
         <v>380</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>617</v>
+        <v>538</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="30">
       <c r="A7" s="2" t="s">
         <v>352</v>
       </c>
@@ -4372,13 +3464,13 @@
         <v>387</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>619</v>
+        <v>540</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
         <v>353</v>
       </c>
@@ -4410,13 +3502,13 @@
         <v>394</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>621</v>
+        <v>542</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -4445,16 +3537,16 @@
         <v>28</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>603</v>
+        <v>524</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>604</v>
+        <v>525</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -4486,13 +3578,13 @@
         <v>30</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>623</v>
+        <v>544</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
         <v>36</v>
       </c>
@@ -4524,13 +3616,13 @@
         <v>37</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>625</v>
+        <v>546</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="30">
       <c r="A12" s="2" t="s">
         <v>43</v>
       </c>
@@ -4562,13 +3654,13 @@
         <v>44</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>627</v>
+        <v>548</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
         <v>51</v>
       </c>
@@ -4600,13 +3692,13 @@
         <v>53</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>629</v>
+        <v>550</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
         <v>60</v>
       </c>
@@ -4638,13 +3730,13 @@
         <v>61</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>631</v>
+        <v>552</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
         <v>68</v>
       </c>
@@ -4676,13 +3768,13 @@
         <v>69</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>633</v>
+        <v>554</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
         <v>76</v>
       </c>
@@ -4714,13 +3806,13 @@
         <v>77</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>635</v>
+        <v>556</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
         <v>84</v>
       </c>
@@ -4752,13 +3844,13 @@
         <v>85</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>637</v>
+        <v>558</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="2" t="s">
         <v>92</v>
       </c>
@@ -4790,13 +3882,13 @@
         <v>93</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>639</v>
+        <v>560</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="2" t="s">
         <v>100</v>
       </c>
@@ -4828,13 +3920,13 @@
         <v>101</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>641</v>
+        <v>562</v>
       </c>
       <c r="L19" s="12" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="2" t="s">
         <v>108</v>
       </c>
@@ -4866,13 +3958,13 @@
         <v>110</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>643</v>
+        <v>564</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="2" t="s">
         <v>117</v>
       </c>
@@ -4904,13 +3996,13 @@
         <v>118</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>645</v>
+        <v>566</v>
       </c>
       <c r="L21" s="12" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="2" t="s">
         <v>125</v>
       </c>
@@ -4942,13 +4034,13 @@
         <v>126</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>647</v>
+        <v>568</v>
       </c>
       <c r="L22" s="12" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="2" t="s">
         <v>133</v>
       </c>
@@ -4980,13 +4072,13 @@
         <v>134</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>649</v>
+        <v>570</v>
       </c>
       <c r="L23" s="12" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="2" t="s">
         <v>141</v>
       </c>
@@ -5018,13 +4110,13 @@
         <v>142</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>651</v>
+        <v>572</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="2" t="s">
         <v>149</v>
       </c>
@@ -5056,13 +4148,13 @@
         <v>151</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>653</v>
+        <v>574</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="2" t="s">
         <v>158</v>
       </c>
@@ -5094,13 +4186,13 @@
         <v>30</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>623</v>
+        <v>544</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="2" t="s">
         <v>159</v>
       </c>
@@ -5132,13 +4224,13 @@
         <v>160</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>655</v>
+        <v>576</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" s="2" t="s">
         <v>167</v>
       </c>
@@ -5170,13 +4262,13 @@
         <v>168</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>657</v>
+        <v>578</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" s="2" t="s">
         <v>174</v>
       </c>
@@ -5208,13 +4300,13 @@
         <v>175</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>659</v>
+        <v>580</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" s="2" t="s">
         <v>418</v>
       </c>
@@ -5246,13 +4338,13 @@
         <v>419</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>661</v>
+        <v>582</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" s="2" t="s">
         <v>426</v>
       </c>
@@ -5284,13 +4376,13 @@
         <v>175</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>659</v>
+        <v>580</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" s="2" t="s">
         <v>432</v>
       </c>
@@ -5322,13 +4414,13 @@
         <v>433</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>663</v>
+        <v>584</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33" s="2" t="s">
         <v>440</v>
       </c>
@@ -5360,13 +4452,13 @@
         <v>261</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>665</v>
+        <v>586</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34" s="2" t="s">
         <v>442</v>
       </c>
@@ -5404,7 +4496,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12">
       <c r="A35" s="2" t="s">
         <v>443</v>
       </c>
@@ -5436,13 +4528,13 @@
         <v>444</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>667</v>
+        <v>588</v>
       </c>
       <c r="L35" s="12" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36" s="2" t="s">
         <v>182</v>
       </c>
@@ -5474,13 +4566,13 @@
         <v>184</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>669</v>
+        <v>590</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37" s="2" t="s">
         <v>191</v>
       </c>
@@ -5512,13 +4604,13 @@
         <v>192</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>671</v>
+        <v>592</v>
       </c>
       <c r="L37" s="12" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="30">
       <c r="A38" s="2" t="s">
         <v>199</v>
       </c>
@@ -5550,13 +4642,13 @@
         <v>200</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>673</v>
+        <v>594</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39" s="2" t="s">
         <v>207</v>
       </c>
@@ -5588,13 +4680,13 @@
         <v>208</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>675</v>
+        <v>596</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="30">
       <c r="A40" s="2" t="s">
         <v>215</v>
       </c>
@@ -5626,13 +4718,13 @@
         <v>216</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" s="2" t="s">
         <v>223</v>
       </c>
@@ -5664,13 +4756,13 @@
         <v>224</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>679</v>
+        <v>600</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="30">
       <c r="A42" s="2" t="s">
         <v>231</v>
       </c>
@@ -5702,13 +4794,13 @@
         <v>232</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>681</v>
+        <v>602</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43" s="2" t="s">
         <v>239</v>
       </c>
@@ -5740,13 +4832,13 @@
         <v>240</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>683</v>
+        <v>604</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="30">
       <c r="A44" s="2" t="s">
         <v>246</v>
       </c>
@@ -5778,13 +4870,13 @@
         <v>247</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>685</v>
+        <v>606</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45" s="2" t="s">
         <v>254</v>
       </c>
@@ -5816,13 +4908,13 @@
         <v>255</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>687</v>
+        <v>608</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46" s="2" t="s">
         <v>18</v>
       </c>
@@ -5854,13 +4946,13 @@
         <v>261</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>665</v>
+        <v>586</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47" s="2" t="s">
         <v>19</v>
       </c>
@@ -5892,13 +4984,13 @@
         <v>266</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>689</v>
+        <v>610</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
       <c r="A48" s="2" t="s">
         <v>20</v>
       </c>
@@ -5936,7 +5028,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12">
       <c r="A49" s="2" t="s">
         <v>276</v>
       </c>
@@ -5968,13 +5060,13 @@
         <v>278</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>691</v>
+        <v>612</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50" s="2" t="s">
         <v>284</v>
       </c>
@@ -6006,13 +5098,13 @@
         <v>285</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>693</v>
+        <v>614</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51" s="2" t="s">
         <v>292</v>
       </c>
@@ -6044,13 +5136,13 @@
         <v>278</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>691</v>
+        <v>612</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52" s="2" t="s">
         <v>293</v>
       </c>
@@ -6082,13 +5174,13 @@
         <v>294</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>695</v>
+        <v>616</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53" s="2" t="s">
         <v>301</v>
       </c>
@@ -6120,13 +5212,13 @@
         <v>302</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>697</v>
+        <v>618</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="66" x14ac:dyDescent="0.3">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="60">
       <c r="A54" s="2" t="s">
         <v>309</v>
       </c>
@@ -6158,13 +5250,13 @@
         <v>310</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>699</v>
+        <v>620</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55" s="2" t="s">
         <v>317</v>
       </c>
@@ -6196,13 +5288,13 @@
         <v>318</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>701</v>
+        <v>622</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="30">
       <c r="A56" s="2" t="s">
         <v>324</v>
       </c>
@@ -6234,13 +5326,13 @@
         <v>325</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>703</v>
+        <v>624</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57" s="2" t="s">
         <v>332</v>
       </c>
@@ -6272,13 +5364,13 @@
         <v>332</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>705</v>
+        <v>626</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
       <c r="A58" s="2" t="s">
         <v>339</v>
       </c>
@@ -6310,13 +5402,13 @@
         <v>340</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>707</v>
+        <v>628</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="99" x14ac:dyDescent="0.3">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="90">
       <c r="A59" s="2" t="s">
         <v>401</v>
       </c>
@@ -6348,13 +5440,13 @@
         <v>403</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>709</v>
+        <v>630</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="30">
       <c r="A60" s="2" t="s">
         <v>402</v>
       </c>
@@ -6386,13 +5478,13 @@
         <v>410</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>711</v>
+        <v>632</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
       <c r="A61" s="2" t="s">
         <v>452</v>
       </c>
@@ -6424,13 +5516,13 @@
         <v>453</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>713</v>
+        <v>634</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="198" x14ac:dyDescent="0.3">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="195">
       <c r="A62" s="2" t="s">
         <v>459</v>
       </c>
@@ -6438,718 +5530,718 @@
         <v>458</v>
       </c>
       <c r="C62" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="I62" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="K62" s="4" t="s">
-        <v>715</v>
-      </c>
-      <c r="L62" s="4" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="33" x14ac:dyDescent="0.3">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="45">
       <c r="A64" s="2" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>475</v>
+        <v>649</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>476</v>
+        <v>650</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>477</v>
+        <v>651</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>478</v>
+        <v>652</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>479</v>
+        <v>653</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>480</v>
+        <v>654</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>481</v>
+        <v>655</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>475</v>
+        <v>649</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>717</v>
+        <v>656</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
       <c r="A65" s="2" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="49.5" x14ac:dyDescent="0.3">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="45">
       <c r="A66" s="2" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>490</v>
+        <v>658</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>491</v>
+        <v>659</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>492</v>
+        <v>660</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>493</v>
+        <v>661</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>494</v>
+        <v>662</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>495</v>
+        <v>663</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>496</v>
+        <v>664</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>490</v>
+        <v>658</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>719</v>
+        <v>665</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
       <c r="A67" s="5" t="s">
-        <v>497</v>
+        <v>667</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>458</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>721</v>
+        <v>636</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="198" x14ac:dyDescent="0.3">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="210">
       <c r="A68" s="5" t="s">
-        <v>498</v>
+        <v>668</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>458</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>505</v>
+        <v>669</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>506</v>
+        <v>670</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>507</v>
+        <v>671</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>508</v>
+        <v>672</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>509</v>
+        <v>673</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>510</v>
+        <v>674</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>511</v>
+        <v>675</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>505</v>
+        <v>669</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>723</v>
+        <v>676</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
       <c r="A69" s="2" t="s">
-        <v>512</v>
+        <v>482</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>516</v>
+        <v>486</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>516</v>
+        <v>486</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>517</v>
+        <v>487</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>518</v>
+        <v>488</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>519</v>
+        <v>489</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>520</v>
+        <v>490</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>521</v>
+        <v>491</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>516</v>
+        <v>486</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>516</v>
+        <v>486</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="148.5" x14ac:dyDescent="0.3">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="150">
       <c r="A70" s="2" t="s">
-        <v>513</v>
+        <v>483</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>522</v>
+        <v>697</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>523</v>
+        <v>698</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>524</v>
+        <v>699</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>525</v>
+        <v>700</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>526</v>
+        <v>701</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>527</v>
+        <v>702</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>528</v>
+        <v>703</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>522</v>
+        <v>697</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>725</v>
+        <v>704</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="82.5" x14ac:dyDescent="0.3">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="105">
       <c r="A71" s="2" t="s">
-        <v>514</v>
+        <v>484</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>529</v>
+        <v>678</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>530</v>
+        <v>679</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>531</v>
+        <v>682</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>532</v>
+        <v>681</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>533</v>
+        <v>680</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>534</v>
+        <v>684</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>535</v>
+        <v>683</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>529</v>
+        <v>678</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>727</v>
+        <v>685</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="66" x14ac:dyDescent="0.3">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="90">
       <c r="A72" s="2" t="s">
-        <v>515</v>
+        <v>485</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>536</v>
+        <v>687</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>537</v>
+        <v>688</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>538</v>
+        <v>689</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>539</v>
+        <v>690</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>540</v>
+        <v>691</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>541</v>
+        <v>692</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>542</v>
+        <v>693</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>536</v>
+        <v>694</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>729</v>
+        <v>695</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
       <c r="A73" s="2" t="s">
-        <v>543</v>
+        <v>492</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>545</v>
+        <v>494</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>545</v>
+        <v>494</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>546</v>
+        <v>495</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>547</v>
+        <v>496</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>548</v>
+        <v>497</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>549</v>
+        <v>498</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>550</v>
+        <v>499</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>545</v>
+        <v>494</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>545</v>
+        <v>494</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="297" x14ac:dyDescent="0.3">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="270">
       <c r="A74" s="2" t="s">
-        <v>544</v>
+        <v>493</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>551</v>
+        <v>706</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>552</v>
+        <v>707</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>553</v>
+        <v>708</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>554</v>
+        <v>709</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>555</v>
+        <v>710</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>556</v>
+        <v>711</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>557</v>
+        <v>712</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>551</v>
+        <v>706</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>731</v>
+        <v>713</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
       <c r="A75" s="2" t="s">
-        <v>558</v>
+        <v>500</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>560</v>
+        <v>502</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>560</v>
+        <v>502</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>561</v>
+        <v>503</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>562</v>
+        <v>504</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>563</v>
+        <v>505</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>564</v>
+        <v>506</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>565</v>
+        <v>507</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>560</v>
+        <v>502</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>560</v>
+        <v>502</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="409.5" x14ac:dyDescent="0.3">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="409.5">
       <c r="A76" s="2" t="s">
-        <v>559</v>
+        <v>501</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>566</v>
+        <v>715</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>567</v>
+        <v>716</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>568</v>
+        <v>717</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>569</v>
+        <v>718</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>570</v>
+        <v>719</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>571</v>
+        <v>720</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>572</v>
+        <v>721</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>566</v>
+        <v>715</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
       <c r="A77" s="2" t="s">
-        <v>573</v>
+        <v>508</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>575</v>
+        <v>510</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>575</v>
+        <v>510</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>576</v>
+        <v>511</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>577</v>
+        <v>512</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>578</v>
+        <v>513</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>579</v>
+        <v>514</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>580</v>
+        <v>515</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>575</v>
+        <v>510</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>575</v>
+        <v>510</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="180">
       <c r="A78" s="2" t="s">
-        <v>574</v>
+        <v>509</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>581</v>
+        <v>724</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>582</v>
+        <v>725</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>583</v>
+        <v>726</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>584</v>
+        <v>727</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>585</v>
+        <v>728</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>586</v>
+        <v>729</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>587</v>
+        <v>730</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>581</v>
+        <v>724</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
       <c r="A79" s="2" t="s">
-        <v>588</v>
+        <v>516</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>590</v>
+        <v>518</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>590</v>
+        <v>518</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>591</v>
+        <v>519</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>592</v>
+        <v>520</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>593</v>
+        <v>521</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>594</v>
+        <v>522</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>595</v>
+        <v>523</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>590</v>
+        <v>518</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>737</v>
+        <v>638</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="346.5" x14ac:dyDescent="0.3">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="315">
       <c r="A80" s="2" t="s">
-        <v>589</v>
+        <v>517</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>458</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>596</v>
+        <v>733</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>597</v>
+        <v>734</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>598</v>
+        <v>735</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>599</v>
+        <v>736</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>600</v>
+        <v>737</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>601</v>
+        <v>738</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>602</v>
+        <v>739</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>596</v>
+        <v>733</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
   </sheetData>

--- a/LocalizationStringTable.xlsx
+++ b/LocalizationStringTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CocosProject\FortuneofRaSecretTreasure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C7D589-1394-4BAE-979C-F3BC498EEC86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E6A7BA-6082-47B8-B246-AEDE6D192E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{01A4B2FD-E311-460F-AD11-CF593C8E3E63}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="743">
   <si>
     <t>Key</t>
   </si>
@@ -752,9 +752,6 @@
   </si>
   <si>
     <t>在遊戲開始前顯示介紹畫面</t>
-  </si>
-  <si>
-    <t>Ipakita ang intro screen bago magsimula ang laro</t>
   </si>
   <si>
     <t>ゲーム開始前にイントロ画面を表示</t>
@@ -1867,10 +1864,6 @@
   <si>
     <t>HIDUPKAN ATAU MATIKAN 
 MUZIK PERMAINAN</t>
-  </si>
-  <si>
-    <t>BẬT HOẶC TẮT 
- NHẠC TRÒ CHƠI</t>
   </si>
   <si>
     <t>SIARAN</t>
@@ -2249,9 +2242,6 @@
   </si>
   <si>
     <t>Hanya simbol yang dipilih,&lt;img src = '5' height=70 offset= -15/&gt;  ,&lt;img src = '4' height=70 offset= -15/&gt;  ,&lt;img src = '3' height=70 offset= -15/&gt;  ,&lt;img src = '2' height=70 offset= -15/&gt;  ,&lt;img src = '1' height=70 offset= -15/&gt;  ,&lt;img src = '0' height=70 offset= -15/&gt;  , dan  &lt;img src = '13' height=50 offset= -5/&gt;  akan muncul semasa Free Games Bonus.</t>
-  </si>
-  <si>
-    <t>Chỉ biểu tượng được chọn,&lt;img src = '5' height=70 offset= -15/&gt;  ,&lt;img src = '4' height=70 offset= -15/&gt;  ,&lt;img src = '3' height=70 offset= -15/&gt;  , &lt;img src = '2' height=70 offset= -15/&gt;  ,&lt;img src = '1' height=70 offset= -15/&gt;  ,&lt;img src = '0' height=70 offset= -15/&gt;  , và  &lt;img src = '13' height=50 offset= -5/&gt;sẽ xuất hiện trong Free Games Bonus.</t>
   </si>
   <si>
     <t xml:space="preserve">6 or more scattered   &lt;img src = '13' height=50 offset=0/&gt;  during the base game will award the sum of the values displayed on   &lt;img src = '13' height=50 offset=0/&gt;  and the Feature Selection.
@@ -2696,6 +2686,20 @@
 &lt;color=#fff71f&gt;RTP lý thuyết của trò chơi này là 95.81%. &lt;/color&gt;
 Trong trường hợp trục trặc, tất cả cược và trả thưởng đều vô hiệu.
 Return to Player (RTP) của trò chơi được đảm bảo đạt được trong vòng 100.000.000 vòng chơi.</t>
+  </si>
+  <si>
+    <t>Chỉ biểu tượng được chọn,&lt;img src = '5' height=70 offset= -15/&gt;  ,&lt;img src = '4' height=70 offset= -15/&gt;  ,&lt;img src = '3' height=70 offset= -15/&gt;  , &lt;img src = '2' height=70 offset= -15/&gt;  ,&lt;img src = '1' height=70 offset= -15/&gt;  ,&lt;img src = '0' height=70 offset= -15/&gt;  , và  &lt;img src = '13' height=50 offset= -5/&gt;  sẽ xuất hiện trong Free Games Bonus.</t>
+  </si>
+  <si>
+    <t>LỰA CHỌN TÍNH NĂNG</t>
+  </si>
+  <si>
+    <t>Ipakita ang intro screen bago 
+magsimula ang laro</t>
+  </si>
+  <si>
+    <t>BẬT HOẶC TẮT 
+NHẠC TRÒ CHƠI</t>
   </si>
 </sst>
 </file>
@@ -3233,13 +3237,13 @@
         <v>8</v>
       </c>
       <c r="J1" s="11" t="s">
+        <v>526</v>
+      </c>
+      <c r="K1" s="11" t="s">
         <v>527</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>528</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="30">
@@ -3274,238 +3278,238 @@
         <v>11</v>
       </c>
       <c r="K2" s="12" t="s">
+        <v>529</v>
+      </c>
+      <c r="L2" s="12" t="s">
         <v>530</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>348</v>
-      </c>
       <c r="C3" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>365</v>
-      </c>
       <c r="K3" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="L3" s="12" t="s">
         <v>532</v>
-      </c>
-      <c r="L3" s="12" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>372</v>
-      </c>
       <c r="J4" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K4" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="L4" s="12" t="s">
         <v>534</v>
-      </c>
-      <c r="L4" s="12" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>379</v>
-      </c>
       <c r="J5" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K5" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="L5" s="12" t="s">
         <v>536</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>386</v>
-      </c>
       <c r="J6" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K6" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="L6" s="12" t="s">
         <v>538</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="30">
       <c r="A7" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>393</v>
-      </c>
       <c r="J7" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K7" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="L7" s="12" t="s">
         <v>540</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>400</v>
-      </c>
       <c r="J8" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K8" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="L8" s="12" t="s">
         <v>542</v>
-      </c>
-      <c r="L8" s="12" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -3537,13 +3541,13 @@
         <v>28</v>
       </c>
       <c r="J9" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="K9" s="10" t="s">
         <v>524</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="L9" s="10" t="s">
         <v>525</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -3578,10 +3582,10 @@
         <v>30</v>
       </c>
       <c r="K10" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="L10" s="12" t="s">
         <v>544</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -3616,10 +3620,10 @@
         <v>37</v>
       </c>
       <c r="K11" s="12" t="s">
+        <v>545</v>
+      </c>
+      <c r="L11" s="12" t="s">
         <v>546</v>
-      </c>
-      <c r="L11" s="12" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="30">
@@ -3654,10 +3658,10 @@
         <v>44</v>
       </c>
       <c r="K12" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="L12" s="4" t="s">
         <v>548</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -3692,10 +3696,10 @@
         <v>53</v>
       </c>
       <c r="K13" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="L13" s="12" t="s">
         <v>550</v>
-      </c>
-      <c r="L13" s="12" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -3730,10 +3734,10 @@
         <v>61</v>
       </c>
       <c r="K14" s="12" t="s">
+        <v>551</v>
+      </c>
+      <c r="L14" s="12" t="s">
         <v>552</v>
-      </c>
-      <c r="L14" s="12" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -3768,10 +3772,10 @@
         <v>69</v>
       </c>
       <c r="K15" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="L15" s="12" t="s">
         <v>554</v>
-      </c>
-      <c r="L15" s="12" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -3806,10 +3810,10 @@
         <v>77</v>
       </c>
       <c r="K16" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="L16" s="12" t="s">
         <v>556</v>
-      </c>
-      <c r="L16" s="12" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -3844,10 +3848,10 @@
         <v>85</v>
       </c>
       <c r="K17" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="L17" s="12" t="s">
         <v>558</v>
-      </c>
-      <c r="L17" s="12" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -3882,10 +3886,10 @@
         <v>93</v>
       </c>
       <c r="K18" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="L18" s="12" t="s">
         <v>560</v>
-      </c>
-      <c r="L18" s="12" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -3920,10 +3924,10 @@
         <v>101</v>
       </c>
       <c r="K19" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="L19" s="12" t="s">
         <v>562</v>
-      </c>
-      <c r="L19" s="12" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -3958,10 +3962,10 @@
         <v>110</v>
       </c>
       <c r="K20" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="L20" s="12" t="s">
         <v>564</v>
-      </c>
-      <c r="L20" s="12" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -3996,10 +4000,10 @@
         <v>118</v>
       </c>
       <c r="K21" s="12" t="s">
+        <v>565</v>
+      </c>
+      <c r="L21" s="12" t="s">
         <v>566</v>
-      </c>
-      <c r="L21" s="12" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -4034,10 +4038,10 @@
         <v>126</v>
       </c>
       <c r="K22" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="L22" s="12" t="s">
         <v>568</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -4072,10 +4076,10 @@
         <v>134</v>
       </c>
       <c r="K23" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="L23" s="12" t="s">
         <v>570</v>
-      </c>
-      <c r="L23" s="12" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -4110,10 +4114,10 @@
         <v>142</v>
       </c>
       <c r="K24" s="12" t="s">
+        <v>571</v>
+      </c>
+      <c r="L24" s="12" t="s">
         <v>572</v>
-      </c>
-      <c r="L24" s="12" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -4148,10 +4152,10 @@
         <v>151</v>
       </c>
       <c r="K25" s="12" t="s">
+        <v>573</v>
+      </c>
+      <c r="L25" s="12" t="s">
         <v>574</v>
-      </c>
-      <c r="L25" s="12" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -4186,10 +4190,10 @@
         <v>30</v>
       </c>
       <c r="K26" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="L26" s="12" t="s">
         <v>544</v>
-      </c>
-      <c r="L26" s="12" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -4224,10 +4228,10 @@
         <v>160</v>
       </c>
       <c r="K27" s="12" t="s">
+        <v>575</v>
+      </c>
+      <c r="L27" s="12" t="s">
         <v>576</v>
-      </c>
-      <c r="L27" s="12" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -4262,10 +4266,10 @@
         <v>168</v>
       </c>
       <c r="K28" s="12" t="s">
+        <v>577</v>
+      </c>
+      <c r="L28" s="12" t="s">
         <v>578</v>
-      </c>
-      <c r="L28" s="12" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -4300,56 +4304,56 @@
         <v>175</v>
       </c>
       <c r="K29" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="L29" s="12" t="s">
         <v>580</v>
-      </c>
-      <c r="L29" s="12" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="C30" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="E30" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="F30" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="H30" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>425</v>
-      </c>
       <c r="J30" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K30" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="L30" s="12" t="s">
         <v>582</v>
-      </c>
-      <c r="L30" s="12" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>175</v>
@@ -4358,180 +4362,180 @@
         <v>176</v>
       </c>
       <c r="E31" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="G31" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="H31" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>431</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>175</v>
       </c>
       <c r="K31" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="L31" s="12" t="s">
         <v>580</v>
-      </c>
-      <c r="L31" s="12" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="C32" s="4" t="s">
+      <c r="D32" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="E32" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="F32" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="G32" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="H32" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="I32" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="I32" s="2" t="s">
-        <v>439</v>
-      </c>
       <c r="J32" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K32" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="L32" s="12" t="s">
         <v>584</v>
-      </c>
-      <c r="L32" s="12" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="E33" s="4" t="s">
+      <c r="H33" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="H33" s="2" t="s">
+      <c r="I33" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="I33" s="2" t="s">
-        <v>265</v>
-      </c>
       <c r="J33" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K33" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="L33" s="12" t="s">
         <v>586</v>
-      </c>
-      <c r="L33" s="12" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D34" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="F34" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>269</v>
-      </c>
       <c r="G34" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L34" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="C35" s="4" t="s">
+      <c r="D35" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="E35" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="F35" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="G35" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="H35" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="I35" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>450</v>
-      </c>
       <c r="J35" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K35" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="L35" s="12" t="s">
         <v>588</v>
-      </c>
-      <c r="L35" s="12" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -4566,10 +4570,10 @@
         <v>184</v>
       </c>
       <c r="K36" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="L36" s="12" t="s">
         <v>590</v>
-      </c>
-      <c r="L36" s="12" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -4604,10 +4608,10 @@
         <v>192</v>
       </c>
       <c r="K37" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="L37" s="12" t="s">
         <v>592</v>
-      </c>
-      <c r="L37" s="12" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="30">
@@ -4642,10 +4646,10 @@
         <v>200</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>595</v>
+        <v>742</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -4680,10 +4684,10 @@
         <v>208</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="30">
@@ -4718,10 +4722,10 @@
         <v>216</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -4756,10 +4760,10 @@
         <v>224</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="30">
@@ -4782,136 +4786,136 @@
         <v>235</v>
       </c>
       <c r="G42" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="H42" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="H42" s="4" t="s">
+      <c r="I42" s="4" t="s">
         <v>237</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>238</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>232</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>183</v>
       </c>
       <c r="C43" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="E43" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="F43" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="G43" s="4" t="s">
+      <c r="H43" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="I43" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="I43" s="4" t="s">
-        <v>245</v>
-      </c>
       <c r="J43" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="30">
       <c r="A44" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>183</v>
       </c>
       <c r="C44" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="E44" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="F44" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="G44" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="H44" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="I44" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="I44" s="4" t="s">
-        <v>253</v>
-      </c>
       <c r="J44" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>183</v>
       </c>
       <c r="C45" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="E45" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="F45" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="G45" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="F45" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="G45" s="4" t="s">
+      <c r="H45" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="I45" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="H45" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>259</v>
-      </c>
       <c r="J45" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -4919,37 +4923,37 @@
         <v>18</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="D46" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="E46" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="F46" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="H46" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="F46" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="H46" s="4" t="s">
+      <c r="I46" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="I46" s="4" t="s">
-        <v>265</v>
-      </c>
       <c r="J46" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K46" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="L46" s="4" t="s">
         <v>586</v>
-      </c>
-      <c r="L46" s="4" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -4957,37 +4961,37 @@
         <v>19</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C47" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="E47" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="F47" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="G47" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="H47" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="I47" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="H47" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>271</v>
-      </c>
       <c r="J47" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -4995,1253 +4999,1253 @@
         <v>20</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C48" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E48" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="E48" s="4" t="s">
+      <c r="F48" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="G48" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="I48" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="G48" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>275</v>
-      </c>
       <c r="J48" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C49" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="D49" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="E49" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="F49" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="G49" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="H49" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="G49" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="H49" s="4" t="s">
+      <c r="I49" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="I49" s="4" t="s">
-        <v>283</v>
-      </c>
       <c r="J49" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C50" s="4" t="s">
+      <c r="D50" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="E50" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="F50" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="G50" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="H50" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="H50" s="4" t="s">
+      <c r="I50" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="I50" s="4" t="s">
-        <v>291</v>
-      </c>
       <c r="J50" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="D51" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="E51" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="F51" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="G51" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="H51" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="G51" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="H51" s="4" t="s">
+      <c r="I51" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="I51" s="4" t="s">
-        <v>283</v>
-      </c>
       <c r="J51" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C52" s="4" t="s">
+      <c r="D52" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="E52" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="F52" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="G52" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="H52" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="H52" s="4" t="s">
+      <c r="I52" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="I52" s="4" t="s">
-        <v>300</v>
-      </c>
       <c r="J52" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C53" s="4" t="s">
+      <c r="D53" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="E53" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="F53" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="G53" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="H53" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="H53" s="4" t="s">
+      <c r="I53" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="I53" s="4" t="s">
-        <v>308</v>
-      </c>
       <c r="J53" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="60">
       <c r="A54" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C54" s="4" t="s">
+      <c r="D54" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="E54" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="F54" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="H54" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="H54" s="4" t="s">
+      <c r="I54" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="I54" s="4" t="s">
-        <v>316</v>
-      </c>
       <c r="J54" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C55" s="4" t="s">
+      <c r="D55" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="E55" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="F55" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="G55" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="H55" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="G55" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="H55" s="4" t="s">
+      <c r="I55" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="I55" s="4" t="s">
-        <v>323</v>
-      </c>
       <c r="J55" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="30">
       <c r="A56" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C56" s="4" t="s">
+      <c r="D56" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="E56" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="F56" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="G56" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="G56" s="4" t="s">
+      <c r="H56" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="H56" s="4" t="s">
+      <c r="I56" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="I56" s="4" t="s">
-        <v>331</v>
-      </c>
       <c r="J56" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="D57" s="4" t="s">
+      <c r="E57" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="F57" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="G57" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="H57" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="H57" s="4" t="s">
+      <c r="I57" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="I57" s="4" t="s">
-        <v>338</v>
-      </c>
       <c r="J57" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C58" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C58" s="4" t="s">
+      <c r="D58" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="E58" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="F58" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="H58" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="H58" s="4" t="s">
+      <c r="I58" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="I58" s="4" t="s">
-        <v>346</v>
-      </c>
       <c r="J58" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="90">
       <c r="A59" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C59" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="E59" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="F59" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="F59" s="4" t="s">
+      <c r="G59" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="G59" s="4" t="s">
+      <c r="H59" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="H59" s="4" t="s">
+      <c r="I59" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="I59" s="4" t="s">
-        <v>409</v>
-      </c>
       <c r="J59" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="30">
       <c r="A60" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C60" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="E60" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="F60" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="F60" s="4" t="s">
+      <c r="G60" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="G60" s="4" t="s">
+      <c r="H60" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="H60" s="4" t="s">
+      <c r="I60" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="I60" s="4" t="s">
-        <v>416</v>
-      </c>
       <c r="J60" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="C61" s="4" t="s">
+      <c r="D61" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="F61" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="E61" s="4" t="s">
+      <c r="G61" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="G61" s="4" t="s">
+      <c r="H61" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="H61" s="4" t="s">
+      <c r="I61" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="I61" s="4" t="s">
-        <v>457</v>
-      </c>
       <c r="J61" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="195">
       <c r="A62" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C62" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="F62" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="G62" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="H62" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="G62" s="4" t="s">
+      <c r="I62" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="H62" s="4" t="s">
+      <c r="J62" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="K62" s="4" t="s">
         <v>645</v>
       </c>
-      <c r="I62" s="4" t="s">
+      <c r="L62" s="4" t="s">
         <v>646</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="K62" s="4" t="s">
-        <v>647</v>
-      </c>
-      <c r="L62" s="4" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="C63" s="2" t="s">
+      <c r="D63" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="E63" s="2" t="s">
+      <c r="F63" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="G63" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="H63" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="H63" s="2" t="s">
+      <c r="I63" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="I63" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="J63" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="45">
       <c r="A64" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C64" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="E64" s="4" t="s">
         <v>649</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="F64" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="G64" s="4" t="s">
         <v>651</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="H64" s="4" t="s">
         <v>652</v>
       </c>
-      <c r="G64" s="4" t="s">
+      <c r="I64" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="H64" s="4" t="s">
+      <c r="J64" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="K64" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="I64" s="4" t="s">
+      <c r="L64" s="4" t="s">
         <v>655</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>649</v>
-      </c>
-      <c r="K64" s="4" t="s">
-        <v>656</v>
-      </c>
-      <c r="L64" s="4" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C65" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E65" s="2" t="s">
+      <c r="F65" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="F65" s="2" t="s">
+      <c r="G65" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="H65" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="H65" s="2" t="s">
+      <c r="I65" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="I65" s="2" t="s">
-        <v>475</v>
-      </c>
       <c r="J65" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="45">
       <c r="A66" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C66" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="E66" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="F66" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="G66" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="H66" s="4" t="s">
         <v>661</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="I66" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="H66" s="4" t="s">
+      <c r="J66" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="K66" s="4" t="s">
         <v>663</v>
       </c>
-      <c r="I66" s="4" t="s">
+      <c r="L66" s="4" t="s">
         <v>664</v>
-      </c>
-      <c r="J66" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="K66" s="4" t="s">
-        <v>665</v>
-      </c>
-      <c r="L66" s="4" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" s="5" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C67" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="E67" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="D67" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="E67" s="5" t="s">
+      <c r="F67" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="F67" s="5" t="s">
+      <c r="G67" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="G67" s="5" t="s">
+      <c r="H67" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="H67" s="5" t="s">
+      <c r="I67" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="I67" s="5" t="s">
-        <v>481</v>
-      </c>
       <c r="J67" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="210">
       <c r="A68" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="D68" s="7" t="s">
         <v>668</v>
       </c>
-      <c r="B68" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="C68" s="7" t="s">
+      <c r="E68" s="7" t="s">
         <v>669</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="F68" s="7" t="s">
         <v>670</v>
       </c>
-      <c r="E68" s="7" t="s">
+      <c r="G68" s="7" t="s">
         <v>671</v>
       </c>
-      <c r="F68" s="7" t="s">
+      <c r="H68" s="7" t="s">
         <v>672</v>
       </c>
-      <c r="G68" s="7" t="s">
+      <c r="I68" s="8" t="s">
         <v>673</v>
       </c>
-      <c r="H68" s="7" t="s">
+      <c r="J68" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="K68" s="4" t="s">
         <v>674</v>
       </c>
-      <c r="I68" s="8" t="s">
+      <c r="L68" s="4" t="s">
         <v>675</v>
-      </c>
-      <c r="J68" s="7" t="s">
-        <v>669</v>
-      </c>
-      <c r="K68" s="4" t="s">
-        <v>676</v>
-      </c>
-      <c r="L68" s="4" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E69" s="2" t="s">
+      <c r="F69" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="F69" s="2" t="s">
+      <c r="G69" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="H69" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="H69" s="2" t="s">
+      <c r="I69" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="I69" s="2" t="s">
-        <v>491</v>
-      </c>
       <c r="J69" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>486</v>
+        <v>740</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="150">
       <c r="A70" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C70" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="F70" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="G70" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="H70" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="I70" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="G70" s="4" t="s">
+      <c r="J70" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="K70" s="4" t="s">
         <v>701</v>
       </c>
-      <c r="H70" s="4" t="s">
+      <c r="L70" s="4" t="s">
         <v>702</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>703</v>
-      </c>
-      <c r="J70" s="4" t="s">
-        <v>697</v>
-      </c>
-      <c r="K70" s="4" t="s">
-        <v>704</v>
-      </c>
-      <c r="L70" s="4" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="105">
       <c r="A71" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C71" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="G71" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="D71" s="4" t="s">
-        <v>679</v>
-      </c>
-      <c r="E71" s="4" t="s">
+      <c r="H71" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="I71" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="G71" s="4" t="s">
-        <v>680</v>
-      </c>
-      <c r="H71" s="4" t="s">
+      <c r="J71" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="L71" s="4" t="s">
         <v>684</v>
-      </c>
-      <c r="I71" s="4" t="s">
-        <v>683</v>
-      </c>
-      <c r="J71" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="K71" s="4" t="s">
-        <v>685</v>
-      </c>
-      <c r="L71" s="4" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="90">
       <c r="A72" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C72" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="E72" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="F72" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="G72" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="F72" s="4" t="s">
+      <c r="H72" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="I72" s="4" t="s">
         <v>691</v>
       </c>
-      <c r="H72" s="4" t="s">
+      <c r="J72" s="4" t="s">
         <v>692</v>
       </c>
-      <c r="I72" s="4" t="s">
+      <c r="K72" s="4" t="s">
         <v>693</v>
       </c>
-      <c r="J72" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="K72" s="4" t="s">
-        <v>695</v>
-      </c>
       <c r="L72" s="4" t="s">
-        <v>696</v>
+        <v>739</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="L73" s="4" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="315">
+      <c r="A74" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="J73" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="K73" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="L73" s="4" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="270">
-      <c r="A74" s="2" t="s">
-        <v>493</v>
-      </c>
       <c r="B74" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C74" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="F74" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="G74" s="4" t="s">
         <v>707</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="H74" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="I74" s="4" t="s">
         <v>709</v>
       </c>
-      <c r="G74" s="4" t="s">
+      <c r="J74" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="K74" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="H74" s="4" t="s">
+      <c r="L74" s="4" t="s">
         <v>711</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="J74" s="4" t="s">
-        <v>706</v>
-      </c>
-      <c r="K74" s="4" t="s">
-        <v>713</v>
-      </c>
-      <c r="L74" s="4" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C75" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="E75" s="2" t="s">
+      <c r="F75" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="F75" s="2" t="s">
+      <c r="G75" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="G75" s="2" t="s">
+      <c r="H75" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="H75" s="2" t="s">
+      <c r="I75" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="I75" s="2" t="s">
-        <v>507</v>
-      </c>
       <c r="J75" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="409.5">
       <c r="A76" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C76" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="G76" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="E76" s="4" t="s">
+      <c r="H76" s="4" t="s">
         <v>717</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="I76" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="J76" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="K76" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="H76" s="4" t="s">
+      <c r="L76" s="4" t="s">
         <v>720</v>
-      </c>
-      <c r="I76" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="J76" s="4" t="s">
-        <v>715</v>
-      </c>
-      <c r="K76" s="4" t="s">
-        <v>722</v>
-      </c>
-      <c r="L76" s="4" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="195">
+      <c r="A78" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="J77" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="K77" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="L77" s="4" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="180">
-      <c r="A78" s="2" t="s">
-        <v>509</v>
-      </c>
       <c r="B78" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C78" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="F78" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="G78" s="4" t="s">
         <v>725</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="H78" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="I78" s="4" t="s">
         <v>727</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="J78" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="K78" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="H78" s="4" t="s">
+      <c r="L78" s="4" t="s">
         <v>729</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>730</v>
-      </c>
-      <c r="J78" s="4" t="s">
-        <v>724</v>
-      </c>
-      <c r="K78" s="4" t="s">
-        <v>731</v>
-      </c>
-      <c r="L78" s="4" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C79" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="E79" s="2" t="s">
+      <c r="F79" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="F79" s="2" t="s">
+      <c r="G79" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="G79" s="2" t="s">
+      <c r="H79" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="H79" s="2" t="s">
+      <c r="I79" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="I79" s="2" t="s">
-        <v>523</v>
-      </c>
       <c r="J79" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="315">
       <c r="A80" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C80" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="F80" s="4" t="s">
         <v>733</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="G80" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="H80" s="4" t="s">
         <v>735</v>
       </c>
-      <c r="F80" s="4" t="s">
+      <c r="I80" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="J80" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="K80" s="4" t="s">
         <v>737</v>
       </c>
-      <c r="H80" s="4" t="s">
+      <c r="L80" s="4" t="s">
         <v>738</v>
-      </c>
-      <c r="I80" s="4" t="s">
-        <v>739</v>
-      </c>
-      <c r="J80" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="K80" s="4" t="s">
-        <v>740</v>
-      </c>
-      <c r="L80" s="4" t="s">
-        <v>741</v>
       </c>
     </row>
   </sheetData>

--- a/LocalizationStringTable.xlsx
+++ b/LocalizationStringTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CocosProject\FortuneofRaSecretTreasure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E6A7BA-6082-47B8-B246-AEDE6D192E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A65BFF5-A5DB-43D4-AEF5-A174BB457771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{01A4B2FD-E311-460F-AD11-CF593C8E3E63}"/>
   </bookViews>
@@ -2164,12 +2164,6 @@
 Maaaring maganap ang lucky event na ito kahit walang &lt;img src = '13' height=50 offset=20/&gt;  na lumitaw sa reel result, at ang resulta ay independiyenteng tinutukoy sa bawat spin.</t>
   </si>
   <si>
-    <t>リール結果で集めた &lt;img src = '13' height=50 offset=20/&gt;  の数に関係なく、Feature Game がランダムに発動することがあります。
-ラッキーイベントが発生すると、フィーチャー突入に必要な最低条件である 6 個の Shou シンボルを満たすまで、リール上に出現した一部のシンボルが &lt;img src = '13' height=50 offset=20/&gt;  に変化します。
-変化した &lt;img src = '13' height=50 offset=20/&gt;  にはランダムな確率に基づいて Credit Value が付与され、その後 Feature Select 画面が表示されます。
-このラッキーイベントは、リール結果に &lt;img src = '13' height=50 offset=20/&gt;  が 1 つも出現しなくても発生することがあり、その結果は毎回のスピンで独立して決定されます。</t>
-  </si>
-  <si>
     <t>ไม่ว่าจะเก็บ &lt;img src = '13' height=50 offset=20/&gt;  ได้กี่ตัวจากผลลัพธ์ของรีล Feature Game ก็อาจถูกกระตุ้นแบบสุ่มได้
 หากเกิดเหตุการณ์นำโชค สัญลักษณ์บางตัวที่ปรากฏบนรีลจะแปลงร่างเป็น &lt;img src = '13' height=50 offset=20/&gt;  จนกว่าจะครบเงื่อนไขขั้นต่ำคือ Shou Symbol 6 ตัวสำหรับการเข้าสู่ฟีเจอร์
 &lt;img src = '13' height=50 offset=20/&gt;  ที่แปลงร่างแล้วจะได้รับ Credit Value ตามโอกาสแบบสุ่ม จากนั้นจะแสดงหน้าจอ Feature Select
@@ -2700,6 +2694,12 @@
   <si>
     <t>BẬT HOẶC TẮT 
 NHẠC TRÒ CHƠI</t>
+  </si>
+  <si>
+    <t>リール結果で集めた &lt;img src = '13' height=50 offset=20/&gt;  の数に関係なく、Feature Game がランダムに発動することがあります。
+ラッキーイベントが発生すると、フィーチャー突入に必要な最低条件である 6 個の Shou シンボルを満たすまで、リール上に出現した一部のシンボルが   &lt;img src = '13' height=50 offset=20/&gt;  に変化します。
+変化した &lt;img src = '13' height=50 offset=20/&gt;  にはランダムな確率に基づいて Credit Value が付与され、その後 Feature Select 画面が表示されます。
+このラッキーイベントは、リール結果に &lt;img src = '13' height=50 offset=20/&gt;  が 1 つも出現しなくても発生することがあり、その結果は毎回のスピンで独立して決定されます。</t>
   </si>
 </sst>
 </file>
@@ -4649,7 +4649,7 @@
         <v>593</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -4786,7 +4786,7 @@
         <v>235</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>236</v>
@@ -5777,19 +5777,19 @@
         <v>671</v>
       </c>
       <c r="H68" s="7" t="s">
+        <v>742</v>
+      </c>
+      <c r="I68" s="8" t="s">
         <v>672</v>
-      </c>
-      <c r="I68" s="8" t="s">
-        <v>673</v>
       </c>
       <c r="J68" s="7" t="s">
         <v>667</v>
       </c>
       <c r="K68" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="L68" s="4" t="s">
         <v>674</v>
-      </c>
-      <c r="L68" s="4" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -5827,7 +5827,7 @@
         <v>485</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="150">
@@ -5838,34 +5838,34 @@
         <v>457</v>
       </c>
       <c r="C70" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="E70" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="F70" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="G70" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="G70" s="4" t="s">
+      <c r="H70" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="H70" s="4" t="s">
+      <c r="I70" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="I70" s="4" t="s">
+      <c r="J70" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="K70" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="J70" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="K70" s="4" t="s">
+      <c r="L70" s="4" t="s">
         <v>701</v>
-      </c>
-      <c r="L70" s="4" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="105">
@@ -5876,34 +5876,34 @@
         <v>457</v>
       </c>
       <c r="C71" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="E71" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="G71" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="E71" s="4" t="s">
+      <c r="H71" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="I71" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="F71" s="4" t="s">
-        <v>679</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="H71" s="4" t="s">
+      <c r="J71" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="K71" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="I71" s="4" t="s">
-        <v>681</v>
-      </c>
-      <c r="J71" s="4" t="s">
-        <v>676</v>
-      </c>
-      <c r="K71" s="4" t="s">
+      <c r="L71" s="4" t="s">
         <v>683</v>
-      </c>
-      <c r="L71" s="4" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="90">
@@ -5914,34 +5914,34 @@
         <v>457</v>
       </c>
       <c r="C72" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="E72" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="F72" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="F72" s="4" t="s">
+      <c r="G72" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="H72" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="H72" s="4" t="s">
+      <c r="I72" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="I72" s="4" t="s">
+      <c r="J72" s="4" t="s">
         <v>691</v>
       </c>
-      <c r="J72" s="4" t="s">
+      <c r="K72" s="4" t="s">
         <v>692</v>
       </c>
-      <c r="K72" s="4" t="s">
-        <v>693</v>
-      </c>
       <c r="L72" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -5990,34 +5990,34 @@
         <v>457</v>
       </c>
       <c r="C74" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>703</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="E74" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="F74" s="4" t="s">
         <v>705</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="G74" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="G74" s="4" t="s">
+      <c r="H74" s="4" t="s">
         <v>707</v>
       </c>
-      <c r="H74" s="4" t="s">
+      <c r="I74" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="I74" s="4" t="s">
+      <c r="J74" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="K74" s="4" t="s">
         <v>709</v>
       </c>
-      <c r="J74" s="4" t="s">
-        <v>703</v>
-      </c>
-      <c r="K74" s="4" t="s">
+      <c r="L74" s="4" t="s">
         <v>710</v>
-      </c>
-      <c r="L74" s="4" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -6066,34 +6066,34 @@
         <v>457</v>
       </c>
       <c r="C76" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="E76" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="E76" s="4" t="s">
+      <c r="F76" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="G76" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="H76" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="H76" s="4" t="s">
+      <c r="I76" s="4" t="s">
         <v>717</v>
       </c>
-      <c r="I76" s="4" t="s">
+      <c r="J76" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="K76" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="J76" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="K76" s="4" t="s">
+      <c r="L76" s="4" t="s">
         <v>719</v>
-      </c>
-      <c r="L76" s="4" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -6142,34 +6142,34 @@
         <v>457</v>
       </c>
       <c r="C78" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>721</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="E78" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="F78" s="4" t="s">
         <v>723</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="G78" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="H78" s="4" t="s">
         <v>725</v>
       </c>
-      <c r="H78" s="4" t="s">
+      <c r="I78" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="I78" s="4" t="s">
+      <c r="J78" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="K78" s="4" t="s">
         <v>727</v>
       </c>
-      <c r="J78" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="K78" s="4" t="s">
+      <c r="L78" s="4" t="s">
         <v>728</v>
-      </c>
-      <c r="L78" s="4" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -6218,34 +6218,34 @@
         <v>457</v>
       </c>
       <c r="C80" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>730</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="E80" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="F80" s="4" t="s">
         <v>732</v>
       </c>
-      <c r="F80" s="4" t="s">
+      <c r="G80" s="4" t="s">
         <v>733</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="H80" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="H80" s="4" t="s">
+      <c r="I80" s="4" t="s">
         <v>735</v>
       </c>
-      <c r="I80" s="4" t="s">
+      <c r="J80" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="K80" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="J80" s="4" t="s">
-        <v>730</v>
-      </c>
-      <c r="K80" s="4" t="s">
+      <c r="L80" s="4" t="s">
         <v>737</v>
-      </c>
-      <c r="L80" s="4" t="s">
-        <v>738</v>
       </c>
     </row>
   </sheetData>

--- a/LocalizationStringTable.xlsx
+++ b/LocalizationStringTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CocosProject\FortuneofRaSecretTreasure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A65BFF5-A5DB-43D4-AEF5-A174BB457771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99DC94AB-9532-41DB-AB90-42DA04807A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{01A4B2FD-E311-460F-AD11-CF593C8E3E63}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="744">
   <si>
     <t>Key</t>
   </si>
@@ -2085,9 +2085,6 @@
     <t>出現在第2、3、4轉軸上，並對除  &lt;img src = '13' height=50 offset=20 /&gt;  之外的所有基礎遊戲符號作為WILD。</t>
   </si>
   <si>
-    <t>Lumilitaw sa reels 2, 3, at 4 at nagsisilbing WILD para sa lahat ng simbolo sa base game maliban sa  &lt;img src = '13' height=50 offset=20 /&gt; .</t>
-  </si>
-  <si>
     <t>リール2、3、4に出現し、 &lt;img src = '13' height=50 offset=20 /&gt;  を除くベースゲームのすべてのシンボルに対してWILDとして機能します。</t>
   </si>
   <si>
@@ -2131,13 +2128,6 @@
   </si>
   <si>
     <t>UI_POPUP_PAY_PAGE3_CONTENTS1</t>
-  </si>
-  <si>
-    <t>Regardless of the number of &lt;img src = '13' height=50 offset=20/&gt;  collected from the reel result, the Feature Game may be triggered at random. 
-If a lucky event occurs, some symbols appearing on the reels will transform into &lt;img src = '13' height=50 offset=20/&gt;  until
-the minimum requirement of 6 Shou Symbols for Feature entry is met.
-The transformed &lt;img src = '13' height=50 offset=20/&gt;  will be assigned a Credit Value based on a random chance, after which the Feature Select screen will be displayed.
-This lucky event may occur even if no &lt;img src = '13' height=50 offset=20/&gt;  appears in the reel result, and the outcome is determined independently on every spin.</t>
   </si>
   <si>
     <t>릴 결과에서 획득한 &lt;img src = '13' height=50 offset=20/&gt;  개수와 관계없이, 일정 확률에 따라 Feature Game이 발동될 수도 있습니다. 예상치 못한 행운이 발생하면,
@@ -2150,92 +2140,6 @@
 若发生幸运事件，卷轴上出现的部分符号将转变为 &lt;img src = '13' height=50 offset=20/&gt; ，直至满足进入功能所需的最低条件——6 个 Shou 符号。
 转变后的 &lt;img src = '13' height=50 offset=20/&gt;  将根据随机机率被赋予 Credit Value，随后会显示 Feature Select 画面。
 即使卷轴结果中没有出现任何 &lt;img src = '13' height=50 offset=20/&gt; ，此幸运事件仍可能发生，且其结果在每次旋转中均独立决定。</t>
-  </si>
-  <si>
-    <t>無論從捲軸結果中收集到多少個 &lt;img src = '13' height=50 offset=20/&gt; ，都可能隨機觸發 Feature Game。
-若發生幸運事件，捲軸上出現的部分符號將轉變為 &lt;img src = '13' height=50 offset=20/&gt; ，直至滿足進入功能所需的最低條件——6 個 Shou 符號。
-轉變後的 &lt;img src = '13' height=50 offset=20/&gt;  將根據隨機機率被賦予 Credit Value，隨後會顯示 Feature Select 畫面。
-即使捲軸結果中沒有出現任何 &lt;img src = '13' height=50 offset=20/&gt; ，此幸運事件仍可能發生，且其結果在每次旋轉中均獨立決定。</t>
-  </si>
-  <si>
-    <t>Anuman ang bilang ng &lt;img src = '13' height=50 offset=20/&gt;  na nakolekta mula sa reel result, maaaring ma-trigger nang random ang Feature Game.
-Kapag may naganap na lucky event, ang ilang simbolo na lumalabas sa reels ay magtatransform sa &lt;img src = '13' height=50 offset=20/&gt;  hanggang matugunan ang minimum na kinakailangan na 6 Shou Symbol para sa pagpasok sa feature.
-Ang na-transform na &lt;img src = '13' height=50 offset=20/&gt;  ay bibigyan ng Credit Value batay sa random na tsansa, pagkatapos nito ay ipapakita ang Feature Select screen.
-Maaaring maganap ang lucky event na ito kahit walang &lt;img src = '13' height=50 offset=20/&gt;  na lumitaw sa reel result, at ang resulta ay independiyenteng tinutukoy sa bawat spin.</t>
-  </si>
-  <si>
-    <t>ไม่ว่าจะเก็บ &lt;img src = '13' height=50 offset=20/&gt;  ได้กี่ตัวจากผลลัพธ์ของรีล Feature Game ก็อาจถูกกระตุ้นแบบสุ่มได้
-หากเกิดเหตุการณ์นำโชค สัญลักษณ์บางตัวที่ปรากฏบนรีลจะแปลงร่างเป็น &lt;img src = '13' height=50 offset=20/&gt;  จนกว่าจะครบเงื่อนไขขั้นต่ำคือ Shou Symbol 6 ตัวสำหรับการเข้าสู่ฟีเจอร์
-&lt;img src = '13' height=50 offset=20/&gt;  ที่แปลงร่างแล้วจะได้รับ Credit Value ตามโอกาสแบบสุ่ม จากนั้นจะแสดงหน้าจอ Feature Select
-เหตุการณ์นำโชคนี้อาจเกิดขึ้นได้แม้ไม่มี &lt;img src = '13' height=50 offset=20/&gt;  ปรากฏในผลลัพธ์ของรีล และผลลัพธ์จะถูกกำหนดอย่างเป็นอิสระในทุก ๆ การหมุน</t>
-  </si>
-  <si>
-    <t>Tanpa mengira bilangan &lt;img src = '13' height=50 offset=20/&gt;  yang dikumpulkan daripada hasil gelung, Feature Game mungkin dicetuskan secara rawak. 
-Jika peristiwa bertuah berlaku, sebahagian simbol yang muncul pada gelung akan bertukar menjadi &lt;img src = '13' height=50 offset=20/&gt;  sehingga
-keperluan minimum 6 Shou Symbols untuk kemasukan Feature dipenuhi.
-&lt;img src = '13' height=50 offset=20/&gt;  yang ditukar akan diberikan Credit Value berdasarkan peluang rawak, selepas itu skrin Feature Select akan dipaparkan.
-Peristiwa bertuah ini boleh berlaku walaupun tiada &lt;img src = '13' height=50 offset=20/&gt;  muncul dalam hasil gelung, dan keputusannya ditentukan secara bebas pada setiap putaran.</t>
-  </si>
-  <si>
-    <t>Bất kể số lượng &lt;img src = '13' height=50 offset=20/&gt;  thu thập được từ kết quả reel, Feature Game có thể được kích hoạt ngẫu nhiên. 
-Nếu một sự kiện may mắn xảy ra, một số biểu tượng xuất hiện trên reel sẽ biến đổi thành &lt;img src = '13' height=50 offset=20/&gt;  cho đến khi
-đạt được yêu cầu tối thiểu 6 Shou Symbols để vào Feature.
-&lt;img src = '13' height=50 offset=20/&gt;  đã biến đổi sẽ được gán Credit Value dựa trên cơ hội ngẫu nhiên, sau đó màn hình Feature Select sẽ được hiển thị.
-Sự kiện may mắn này có thể xảy ra ngay cả khi không có &lt;img src = '13' height=50 offset=20/&gt;  nào xuất hiện trong kết quả reel, và kết quả được xác định độc lập trên mỗi lượt quay.</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5 High Symbols: A Free Games Bonus with a value of 128 &lt;img src = '10' height=50 offset=-5/&gt; , 118 &lt;img src = '9' height=50 offset=-5/&gt; , 108 &lt;img src = '8' height=50 offset=-5/&gt; , 98 &lt;img src = '7' height=50 offset=-5/&gt; , or 88 &lt;img src = '6' height=50 offset=-5/&gt; , or a Top Up Bonus with a value of 88 &lt;img src = '6' height=50 offset=-5/&gt; is awarded. &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5개의 High Symbols: 128 &lt;img src = '10' height=50 offset=-5/&gt;  , 118 &lt;img src = '9' height=50 offset=-5/&gt;  , 108 &lt;img src = '8' height=50 offset=-5/&gt;  , 98 &lt;img src = '7' height=50 offset=-5/&gt;  , 또는 88     &lt;img src = '6' height=50 offset=-5/&gt;  의 값을 가지는 Free Games Bonus 또는 88     &lt;img src = '6' height=50 offset=-5/&gt;  의 값을 가지는 Top Up Bonus가 지급됩니다. &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5 High Symbols: Ang Free Games Bonus na may value na 128 &lt;img src = '10' height=50 offset=-5/&gt;  , 118 &lt;img src = '9' height=50 offset=-5/&gt;  , 108 &lt;img src = '8' height=50 offset=-5/&gt;  , 98 &lt;img src = '7' height=50 offset=-5/&gt;  , o 88 &lt;img src = '6' height=50 offset=-5/&gt;  , o ang Top Up Bonus na may value na 88     &lt;img src = '6' height=50 offset=-5/&gt;  ay ibinibigay. &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5個高階符號：數值為 128 &lt;img src = '10' height=50 offset=-5/&gt;  、118 &lt;img src = '9' height=50 offset=-5/&gt;  、108 &lt;img src = '8' height=50 offset=-5/&gt;  、98 &lt;img src = '7' height=50 offset=-5/&gt;  或 88 &lt;img src = '6' height=50 offset=-5/&gt;  的 Free Games Bonus，或數值為 88     &lt;img src = '6' height=50 offset=-5/&gt;  的 Top Up Bonus。 &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5个高等级符号：数值为 128 &lt;img src = '10' height=50 offset=-5/&gt; 、118 &lt;img src = '9' height=50 offset=-5/&gt;  、108 &lt;img src = '8' height=50 offset=-5/&gt;  、 98 &lt;img src = '7' height=50 offset=-5/&gt;  或 88 &lt;img src = '6' height=50 offset=-5/&gt;  的 Free Games Bonus，或数值为 88     &lt;img src = '6' height=50 offset=-5/&gt;  的 Top Up Bonus。 &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5 High Symbols: จะได้รับ Free Games Bonus ที่มีค่า 128 &lt;img src = '10' height=50 offset=-5/&gt;  , 118 &lt;img src = '9' height=50 offset=-5/&gt;, 108 &lt;img src = '8' height=50 offset=-5/&gt;  , 98 &lt;img src = '7' height=50 offset=-5/&gt;  หรือ 88 &lt;img src = '6' height=50 offset=-5/&gt;  หรือ Top Up Bonus ที่มีค่า 88 &lt;img src = '6' height=50 offset=-5/&gt; &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5つのHigh Symbols：128 &lt;img src = '10' height=50 offset=-5/&gt;  、118 &lt;img src = '9' height=50 offset=-5/&gt;  、108 &lt;img src = '8' height=50 offset=-5/&gt;  、98 &lt;img src = '7' height=50 offset=-5/&gt;  、または88 &lt;img src = '6' height=50 offset=-5/&gt;  の値を持つFree Games Bonus、または88 &lt;img src = '6' height=50 offset=-5/&gt;  の値を持つTop Up Bonusが付与されます。 &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5 High Symbols: Free Games Bonus dengan nilai 128 &lt;img src = '10' height=50 offset=-5/&gt; , 118 &lt;img src = '9' height=50 offset=-5/&gt; , 108 &lt;img src = '8' height=50 offset=-5/&gt; , 98 &lt;img src = '7' height=50 offset=-5/&gt; , atau 88 &lt;img src = '6' height=50 offset=-5/&gt; , atau Top Up Bonus dengan nilai 88 &lt;img src = '6' height=50 offset=-5/&gt;  dianugerahkan. &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5 High Symbols: Một Free Games Bonus với giá trị 128 &lt;img src = '10' height=50 offset=-5/&gt; , 118 &lt;img src = '9' height=50 offset=-5/&gt; , 108 &lt;img src = '8' height=50 offset=-5/&gt; , 98 &lt;img src = '7' height=50 offset=-5/&gt; , hoặc 88 &lt;img src = '6' height=50 offset=-5/&gt; , hoặc một Top Up Bonus với giá trị 88 &lt;img src = '6' height=50 offset=-5/&gt;  được trao. &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>Only the selected symbol,&lt;img src = '5' height=70 offset= -15/&gt;,  &lt;img src = '4' height=70 offset= -15/&gt;  ,&lt;img src = '3' height=70 offset= -15/&gt;   , &lt;img src = '2' height=70 offset= -15/&gt;  , &lt;img src = '1' height=70 offset= -15/&gt; ,&lt;img src = '0' height=70 offset= -15/&gt;, and  &lt;img src = '13' height=50 offset= -5/&gt;  will appear during the Free Games Bonus.</t>
-  </si>
-  <si>
-    <t>선택된 심볼인 &lt;img src = '5' height=70 offset= -15/&gt;  ,&lt;img src = '4' height=70 offset= -15/&gt;  ,&lt;img src = '3' height=70 offset= -15/&gt;  ,&lt;img src = '2' height=70 offset= -15/&gt;  ,&lt;img src = '1' height=70 offset= -15/&gt;  ,&lt;img src = '0' height=70 offset= -15/&gt;  , 및  &lt;img src = '13' height=50 offset= -5/&gt;  만 Free Games Bonus 동안 등장합니다.</t>
-  </si>
-  <si>
-    <t>在 Free Games Bonus 期间，仅会出现所选的符号 &lt;img src = '5' height=70 offset= -15/&gt;、&lt;img src = '4' height=70 offset= -15/&gt;、&lt;img src = '3' height=70 offset= -15/&gt;、&lt;img src = '2' height=70 offset= -15/&gt;、 &lt;img src = '1' height=70 offset= -15/&gt;、&lt;img src = '0' height=70 offset= -15/&gt; 以及  &lt;img src = '13' height=50 offset= -5/&gt;  。</t>
-  </si>
-  <si>
-    <t>在 Free Games Bonus 期間，僅會出現所選的符號 &lt;img src = '5' height=70 offset= -15/&gt;、 &lt;img src = '4' height=70 offset= -15/&gt;、&lt;img src = '3' height=70 offset= -15/&gt;、 &lt;img src = '2' height=70 offset= -15/&gt;、&lt;img src = '1' height=70 offset= -15/&gt;、&lt;img src = '0' height=70 offset= -15/&gt; 以及  &lt;img src = '13' height=50 offset= -5/&gt;  。</t>
-  </si>
-  <si>
-    <t>Tanging ang napiling simbolo,  &lt;img src = '5' height=70 offset= -15/&gt;  , &lt;img src = '4' height=70 offset= -15/&gt;  ,&lt;img src = '3' height=70 offset= -15/&gt;  ,&lt;img src = '2' height=70 offset= -15/&gt;  ,&lt;img src = '1' height=70 offset= -15/&gt;  ,&lt;img src = '0' height=70 offset= -15/&gt;  , at  &lt;img src = '13' height=50 offset= -5/&gt;  lamang ang lalabas sa panahon ng Free Games Bonus.</t>
-  </si>
-  <si>
-    <t>選択されたシンボルである&lt;img src = '5' height=70 offset= -15/&gt;、       &lt;img src = '4' height=70 offset= -15/&gt;、&lt;img src = '3' height=70 offset= -15/&gt;、&lt;img src = '2' height=70 offset= -15/&gt;、&lt;img src = '1' height=70 offset= -15/&gt;、&lt;img src = '0' height=70 offset= -15/&gt; および &lt;img src = '13' height=50 offset= -5/&gt;  のみがFree Games Bonus中に出現します。</t>
-  </si>
-  <si>
-    <t>ในระหว่าง Free Games Bonus จะมีเพียงสัญลักษณ์ที่เลือกไว้เท่านั้นที่ปรากฏ ได้แก่    &lt;img src = '5' height=70 offset= -15/&gt;  , &lt;img src = '4' height=70 offset= -15/&gt;  ,&lt;img src = '3' height=70 offset= -15/&gt;  ,&lt;img src = '2' height=70 offset= -15/&gt;  , &lt;img src = '1' height=70 offset= -15/&gt;  ,&lt;img src = '0' height=70 offset= -15/&gt; และ &lt;img src = '13' height=50 offset= -5/&gt;</t>
-  </si>
-  <si>
-    <t>Only the selected symbol, &lt;img src = '5' height=70 offset= -15/&gt;  , &lt;img src = '4' height=70 offset= -15/&gt;  ,&lt;img src = '3' height=70 offset= -15/&gt;  ,&lt;img src = '2' height=70 offset= -15/&gt;  ,&lt;img src = '1' height=70 offset= -15/&gt;  ,&lt;img src = '0' height=70 offset= -15/&gt;  , and &lt;img src = '13' height=50 offset= -5/&gt;  will appear during the Free Games Bonus.</t>
-  </si>
-  <si>
-    <t>Hanya simbol yang dipilih,&lt;img src = '5' height=70 offset= -15/&gt;  ,&lt;img src = '4' height=70 offset= -15/&gt;  ,&lt;img src = '3' height=70 offset= -15/&gt;  ,&lt;img src = '2' height=70 offset= -15/&gt;  ,&lt;img src = '1' height=70 offset= -15/&gt;  ,&lt;img src = '0' height=70 offset= -15/&gt;  , dan  &lt;img src = '13' height=50 offset= -5/&gt;  akan muncul semasa Free Games Bonus.</t>
   </si>
   <si>
     <t xml:space="preserve">6 or more scattered   &lt;img src = '13' height=50 offset=0/&gt;  during the base game will award the sum of the values displayed on   &lt;img src = '13' height=50 offset=0/&gt;  and the Feature Selection.
@@ -2320,15 +2224,6 @@
   &lt;img src = '12' height=50 offset= 15/&gt;   僅出現在第2–4轉軸上，並對除   &lt;img src = '13' height=50 offset= 15/&gt;   之外的所有符號作為WILD。
 免費遊戲獎勵期間的「Shou Bonus」為所有   &lt;img src = '12' height=50 offset= 15/&gt;   的累積獎勵，以及基礎遊戲期間每個   &lt;img src = '13' height=50 offset= 15/&gt;   上顯示的所有數值總和。
 「Shou Bonus」不包含任何已獲得的累積獎金。</t>
-  </si>
-  <si>
-    <t>6 na free games ang ibinibigay.
-Kung may hindi bababa sa 1   &lt;img src = '12' height=50 offset= 15/&gt;   na lumitaw sa screen, ang kabuuan ng lahat ng value na ipinakita sa mga triggering symbol ay ibibigay para sa bawat   &lt;img src = '12' height=50 offset= 15/&gt;   na nasa screen.
-Bukod dito, kung available ang Top Up Bonus sa panahon ng Feature Selection, maaaring maibigay ang value na ipinapakita sa Fortune Grand Jackpot meter.
-Isang alternatibong set ng reels ang gagamitin sa panahon ng Free Games Bonus. Ang mga winning combination para sa mga reel na ito ay katulad ng sa base game maliban kung may ibang nakasaad.
-Ang   &lt;img src = '12' height=50 offset= 15/&gt;   ay lumilitaw lamang sa reels 2–4 at nagsisilbing WILD para sa lahat ng simbolo maliban sa   &lt;img src = '13' height=50 offset= 15/&gt;  .
-Ang “Shou Bonus” sa panahon ng Free Games Bonus ay ang pinagsama-samang gantimpala ng lahat ng   &lt;img src = '12' height=50 offset= 15/&gt;   at ang kabuuan ng lahat ng value na ipinakita sa bawat   &lt;img src = '13' height=50 offset= 15/&gt;   sa base game.
-Ang “Shou Bonus” ay hindi kasama ang anumang jackpot na napanalunan.</t>
   </si>
   <si>
     <t>6回のフリーゲームが付与されます。
@@ -2502,69 +2397,6 @@
   &lt;img src = '13' height=50 offset= 5/&gt;    không xuất hiện trên reel trong Top Up Bonus. Lượt quay bonus không trao bonus bổ sung.</t>
   </si>
   <si>
-    <t>The Jackpot Bonus may be triggered if 1 or more     &lt;img src = '11' height=50 offset=10/&gt;    land on screen during the base game.
-A pick field is displayed with 12     &lt;img src = '16' height=50 offset=10/&gt;   . Picks will reveal one of the available prizes.
-Available prizes include the Mini Jackpot, Minor Jackpot, Major Jackpot, and Grand Jackpot.
-Picks are made until 3 matching symbols are revealed, and the value displayed in the corresponding meter is awarded.
-The accumulation of coins in the bowl increases the chances of triggering the Jackpot Bonus.</t>
-  </si>
-  <si>
-    <t>기본 게임 중 화면에 1개 이상의    &lt;img src = '11' height=50 offset=10/&gt;  이 등장하면 잭팟 보너스가 트리거될 수 있습니다.
-12개의    &lt;img src = '16' height=50 offset=10/&gt;  로 구성된 선택 필드가 표시됩니다. 선택 시 이용 가능한 보상 중 하나가 공개됩니다.
-이용 가능한 보상에는 Mini Jackpot, Minor Jackpot, Major Jackpot 및 Grand Jackpot이 포함됩니다.
-3개의 동일한 심볼이 공개될 때까지 선택이 진행되며, 해당 미터에 표시된 값이 지급됩니다.
-볼에 쌓이는 코인의 누적량이 잭팟 보너스 트리거 확률을 증가시킵니다.</t>
-  </si>
-  <si>
-    <t>在基础游戏期间，如果屏幕上出现1个或以上的    &lt;img src = '11' height=50 offset=10/&gt;  ，则可能触发Jackpot Bonus。
-将显示一个包含12个    &lt;img src = '16' height=50 offset=10/&gt;   的选择区域。每次选择会揭示一个可获得的奖励。
-可获得的奖励包括 Mini Jackpot、Minor Jackpot、Major Jackpot 和 Grand Jackpot。
-选择将持续进行，直到揭示出3个相同的符号，并奖励对应计量器中显示的数值。
-碗中金币的累积会增加触发Jackpot Bonus的概率。</t>
-  </si>
-  <si>
-    <t>在基礎遊戲期間，如果畫面上出現1個或以上的    &lt;img src = '11' height=50 offset=10/&gt;  ，則可能觸發Jackpot Bonus。
-將顯示一個包含12個    &lt;img src = '16' height=50 offset=10/&gt;   的選擇區域。每次選擇會揭示一個可獲得的獎勵。
-可獲得的獎勵包括 Mini Jackpot、Minor Jackpot、Major Jackpot 和 Grand Jackpot。
-選擇將持續進行，直到揭示出3個相同的符號，並獎勵對應計量器中顯示的數值。
-碗中金幣的累積會增加觸發Jackpot Bonus的機率。</t>
-  </si>
-  <si>
-    <t>Maaaring ma-trigger ang Jackpot Bonus kung may 1 o higit pang    &lt;img src = '11' height=50 offset=10/&gt;   na lumapag sa screen sa base game.
-Isang pick field na may 12    &lt;img src = '16' height=50 offset=10/&gt;   ang ipapakita. Ang bawat pick ay magpapakita ng isa sa mga available na premyo.
-Kabilang sa mga available na premyo ang Mini Jackpot, Minor Jackpot, Major Jackpot, at Grand Jackpot.
-Magpapatuloy ang pagpili hanggang sa maipakita ang 3 magkakatugmang simbolo, at ang value na ipinapakita sa kaukulang meter ang ibibigay.
-Ang pag-ipon ng mga coin sa bowl ay nagpapataas ng tsansa na ma-trigger ang Jackpot Bonus.</t>
-  </si>
-  <si>
-    <t>ベースゲーム中に画面上に1つ以上の    &lt;img src = '11' height=50 offset=10/&gt;   が停止した場合、ジャックポットボーナスが発動することがあります。
-12個の    &lt;img src = '16' height=50 offset=10/&gt;   で構成されたピックフィールドが表示されます。選択すると、利用可能な賞のいずれかが表示されます。
-利用可能な賞には、Mini Jackpot、Minor Jackpot、Major Jackpot、Grand Jackpot が含まれます。
-3つの一致するシンボルが表示されるまで選択が行われ、対応するメーターに表示された値が付与されます。
-ボウルに蓄積されるコインの量が、ジャックポットボーナスの発動確率を高めます。</t>
-  </si>
-  <si>
-    <t>โบนัสแจ็คพอตอาจถูกทริกเกอร์ หากมี    &lt;img src = '11' height=50 offset=10/&gt;   อย่างน้อย 1 ตัวลงบนหน้าจอในระหว่างเกมหลัก
-จะแสดงหน้าจอเลือกที่มี    &lt;img src = '16' height=50 offset=10/&gt;   จำนวน 12 ตัว การเลือกแต่ละครั้งจะเผยหนึ่งในรางวัลที่มีให้
-รางวัลที่มีให้รวมถึง Mini Jackpot, Minor Jackpot, Major Jackpot และ Grand Jackpot
-จะทำการเลือกต่อไปจนกว่าจะพบสัญลักษณ์ที่เหมือนกัน 3 ตัว และจะได้รับค่าที่แสดงในมิเตอร์ที่เกี่ยวข้อง
-การสะสมเหรียญในชามจะเพิ่มโอกาสในการทริกเกอร์โบนัสแจ็คพอต</t>
-  </si>
-  <si>
-    <t>Jackpot Bonus mungkin dicetuskan jika 1 atau lebih     &lt;img src = '11' height=50 offset=10/&gt;    mendarat pada skrin semasa base game.
-Medan pilihan dengan 12     &lt;img src = '16' height=50 offset=10/&gt;    dipaparkan. Pilihan akan mendedahkan salah satu hadiah yang tersedia.
-Hadiah yang tersedia termasuk Mini Jackpot, Minor Jackpot, Major Jackpot, dan Grand Jackpot.
-Pilihan dibuat sehingga 3 simbol yang sepadan didedahkan, dan nilai yang dipaparkan dalam meter yang berkaitan dianugerahkan.
-Pengumpulan syiling dalam mangkuk meningkatkan peluang mencetuskan Jackpot Bonus.</t>
-  </si>
-  <si>
-    <t>Jackpot Bonus có thể được kích hoạt nếu 1 hoặc nhiều     &lt;img src = '11' height=50 offset=10/&gt;    rơi trên màn hình trong trò chơi cơ bản.
-Một vùng chọn với 12     &lt;img src = '16' height=50 offset=10/&gt;    được hiển thị. Mỗi lần chọn sẽ tiết lộ một trong các giải thưởng có sẵn.
-Các giải thưởng có sẵn bao gồm Mini Jackpot, Minor Jackpot, Major Jackpot, và Grand Jackpot.
-Việc chọn tiếp tục cho đến khi 3 biểu tượng khớp nhau được tiết lộ, và giá trị hiển thị trong đồng hồ tương ứng được trao.
-Việc tích lũy xu trong bát làm tăng cơ hội kích hoạt Jackpot Bonus.</t>
-  </si>
-  <si>
     <t>If the same symbol appears at least once on each reel and there are 3 or more in sequence from left to right, it results in a win.
 All win amounts are multiplied by the base bet.
 All values are displayed as actual coin wins.
@@ -2682,9 +2514,6 @@
 Return to Player (RTP) của trò chơi được đảm bảo đạt được trong vòng 100.000.000 vòng chơi.</t>
   </si>
   <si>
-    <t>Chỉ biểu tượng được chọn,&lt;img src = '5' height=70 offset= -15/&gt;  ,&lt;img src = '4' height=70 offset= -15/&gt;  ,&lt;img src = '3' height=70 offset= -15/&gt;  , &lt;img src = '2' height=70 offset= -15/&gt;  ,&lt;img src = '1' height=70 offset= -15/&gt;  ,&lt;img src = '0' height=70 offset= -15/&gt;  , và  &lt;img src = '13' height=50 offset= -5/&gt;  sẽ xuất hiện trong Free Games Bonus.</t>
-  </si>
-  <si>
     <t>LỰA CHỌN TÍNH NĂNG</t>
   </si>
   <si>
@@ -2696,10 +2525,194 @@
 NHẠC TRÒ CHƠI</t>
   </si>
   <si>
+    <t>Regardless of the number of &lt;img src = '13' height=50 offset=20/&gt;  collected from the reel result, the Feature Game may be triggered at random. 
+If a lucky event occurs, some symbols appearing on the reels will transform into 
+&lt;img src = '13' height=50 offset=20/&gt;  until the minimum requirement of 6 Shou Symbols for Feature entry is met.
+The transformed &lt;img src = '13' height=50 offset=20/&gt;  will be assigned a Credit Value based on a random chance, after which the Feature Select screen will be displayed.
+This lucky event may occur even if no &lt;img src = '13' height=50 offset=20/&gt;  appears in the reel result, and the outcome is determined independently on every spin.</t>
+  </si>
+  <si>
+    <t>無論從捲軸結果中收集到多少個 &lt;img src = '13' height=50 offset=20/&gt; ，都可能隨機觸發 Feature Game。
+若發生幸運事件，捲軸上出現的部分符號將轉變為
+ &lt;img src = '13' height=50 offset=20/&gt; ，直至滿足進入功能所需的最低條件——6 個 Shou 符號。
+轉變後的 &lt;img src = '13' height=50 offset=20/&gt;  將根據隨機機率被賦予 Credit Value，隨後會顯示 Feature Select 畫面。
+即使捲軸結果中沒有出現任何 &lt;img src = '13' height=50 offset=20/&gt; ，此幸運事件仍可能發生，且其結果在每次旋轉中均獨立決定。</t>
+  </si>
+  <si>
+    <t>Anuman ang bilang ng &lt;img src = '13' height=50 offset=20/&gt;  na nakolekta mula sa reel result, maaaring ma-trigger nang random ang Feature Game.
+Kapag may naganap na lucky event, ang ilang simbolo na lumalabas sa reels ay magtatransform sa 
+&lt;img src = '13' height=50 offset=20/&gt;  hanggang matugunan ang minimum na kinakailangan na 6 Shou Symbol para sa pagpasok sa feature.
+Ang na-transform na &lt;img src = '13' height=50 offset=20/&gt;  ay bibigyan ng Credit Value batay sa random na tsansa, pagkatapos nito ay ipapakita ang Feature Select screen.
+Maaaring maganap ang lucky event na ito kahit walang &lt;img src = '13' height=50 offset=20/&gt;  na lumitaw sa reel result, at ang resulta ay independiyenteng tinutukoy sa bawat spin.</t>
+  </si>
+  <si>
     <t>リール結果で集めた &lt;img src = '13' height=50 offset=20/&gt;  の数に関係なく、Feature Game がランダムに発動することがあります。
-ラッキーイベントが発生すると、フィーチャー突入に必要な最低条件である 6 個の Shou シンボルを満たすまで、リール上に出現した一部のシンボルが   &lt;img src = '13' height=50 offset=20/&gt;  に変化します。
+ラッキーイベントが発生すると、フィーチャー突入に必要な最低条件である 6 個の Shou シンボルを満たすまで、リール上に出現した一部のシンボルが   
+&lt;img src = '13' height=50 offset=20/&gt;  に変化します。
 変化した &lt;img src = '13' height=50 offset=20/&gt;  にはランダムな確率に基づいて Credit Value が付与され、その後 Feature Select 画面が表示されます。
 このラッキーイベントは、リール結果に &lt;img src = '13' height=50 offset=20/&gt;  が 1 つも出現しなくても発生することがあり、その結果は毎回のスピンで独立して決定されます。</t>
+  </si>
+  <si>
+    <t>ไม่ว่าจะเก็บ &lt;img src = '13' height=50 offset=20/&gt;  ได้กี่ตัวจากผลลัพธ์ของรีล Feature Game ก็อาจถูกกระตุ้นแบบสุ่มได้
+หากเกิดเหตุการณ์นำโชค สัญลักษณ์บางตัวที่ปรากฏบนรีลจะแปลงร่างเป็น 
+&lt;img src = '13' height=50 offset=20/&gt;  จนกว่าจะครบเงื่อนไขขั้นต่ำคือ Shou Symbol 6 ตัวสำหรับการเข้าสู่ฟีเจอร์
+&lt;img src = '13' height=50 offset=20/&gt;  ที่แปลงร่างแล้วจะได้รับ Credit Value ตามโอกาสแบบสุ่ม จากนั้นจะแสดงหน้าจอ Feature Select
+เหตุการณ์นำโชคนี้อาจเกิดขึ้นได้แม้ไม่มี &lt;img src = '13' height=50 offset=20/&gt;  ปรากฏในผลลัพธ์ของรีล และผลลัพธ์จะถูกกำหนดอย่างเป็นอิสระในทุก ๆ การหมุน</t>
+  </si>
+  <si>
+    <t>Tanpa mengira bilangan &lt;img src = '13' height=50 offset=20/&gt;  yang dikumpulkan daripada hasil gelung, Feature Game mungkin dicetuskan secara rawak. 
+Jika peristiwa bertuah berlaku, sebahagian simbol yang muncul pada gelung akan bertukar menjadi 
+&lt;img src = '13' height=50 offset=20/&gt;  sehingga keperluan minimum 6 Shou Symbols untuk kemasukan Feature dipenuhi.
+&lt;img src = '13' height=50 offset=20/&gt;  yang ditukar akan diberikan Credit Value berdasarkan peluang rawak, selepas itu skrin Feature Select akan dipaparkan.
+Peristiwa bertuah ini boleh berlaku walaupun tiada &lt;img src = '13' height=50 offset=20/&gt;  muncul dalam hasil gelung, dan keputusannya ditentukan secara bebas pada setiap putaran.</t>
+  </si>
+  <si>
+    <t>Bất kể số lượng &lt;img src = '13' height=50 offset=20/&gt;  thu thập được từ kết quả reel, Feature Game có thể được kích hoạt ngẫu nhiên. 
+Nếu một sự kiện may mắn xảy ra, một số biểu tượng xuất hiện trên reel sẽ biến đổi thành 
+&lt;img src = '13' height=50 offset=20/&gt;  cho đến khi đạt được yêu cầu tối thiểu 6 Shou Symbols để vào Feature.
+&lt;img src = '13' height=50 offset=20/&gt;  đã biến đổi sẽ được gán Credit Value dựa trên cơ hội ngẫu nhiên, sau đó màn hình Feature Select sẽ được hiển thị.
+Sự kiện may mắn này có thể xảy ra ngay cả khi không có &lt;img src = '13' height=50 offset=20/&gt;  nào xuất hiện trong kết quả reel, và kết quả được xác định độc lập trên mỗi lượt quay.</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5 High Symbols: A Free Games Bonus with a value of 128 &lt;img src = '10' height=50 offset=5/&gt; , 118 &lt;img src = '9' height=50 offset=5/&gt; , 108 &lt;img src = '8' height=50 offset=5/&gt; , 98 &lt;img src = '7' height=50 offset=5/&gt; , or 88 &lt;img src = '6' height=50 offset=5/&gt; , or a Top Up Bonus with a value of 88 &lt;img src = '6' height=50 offset=5/&gt; is awarded. &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5개의 High Symbols: 128 &lt;img src = '10' height=50 offset=5/&gt;  , 118 &lt;img src = '9' height=50 offset=5/&gt;  , 108 &lt;img src = '8' height=50 offset=5/&gt;  , 98 &lt;img src = '7' height=50 offset=5/&gt;  , 또는 88     &lt;img src = '6' height=50 offset=5/&gt;  의 값을 가지는 Free Games Bonus 또는 88     &lt;img src = '6' height=50 offset=5/&gt;  의 값을 가지는 Top Up Bonus가 지급됩니다. &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5个高等级符号：数值为 128 &lt;img src = '10' height=50 offset=5/&gt; 、118 &lt;img src = '9' height=50 offset=5/&gt;  、108 &lt;img src = '8' height=50 offset=5/&gt;  、 98 &lt;img src = '7' height=50 offset=5/&gt;  或 88 &lt;img src = '6' height=50 offset=5/&gt;  的 Free Games Bonus，或数值为 88     &lt;img src = '6' height=50 offset=5/&gt;  的 Top Up Bonus。 &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5個高階符號：數值為 128 &lt;img src = '10' height=50 offset=5/&gt;  、118 &lt;img src = '9' height=50 offset=5/&gt;  、108 &lt;img src = '8' height=50 offset=5/&gt;  、98 &lt;img src = '7' height=50 offset=5/&gt;  或 88 &lt;img src = '6' height=50 offset=5/&gt;  的 Free Games Bonus，或數值為 88     &lt;img src = '6' height=50 offset=5/&gt;  的 Top Up Bonus。 &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5 High Symbols: Ang Free Games Bonus na may value na 128 &lt;img src = '10' height=50 offset=5/&gt;  , 118 &lt;img src = '9' height=50 offset=5/&gt;  , 108 &lt;img src = '8' height=50 offset=5/&gt;  , 98 &lt;img src = '7' height=50 offset=5/&gt;  , o 88 &lt;img src = '6' height=50 offset=5/&gt;  , o ang Top Up Bonus na may value na 88     &lt;img src = '6' height=50 offset=5/&gt;  ay ibinibigay. &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5つのHigh Symbols：128 &lt;img src = '10' height=50 offset=5/&gt;  、118 &lt;img src = '9' height=50 offset=5/&gt;  、108 &lt;img src = '8' height=50 offset=5/&gt;  、98 &lt;img src = '7' height=50 offset=5/&gt;  、または88 &lt;img src = '6' height=50 offset=5/&gt;  の値を持つFree Games Bonus、または88 &lt;img src = '6' height=50 offset=5/&gt;  の値を持つTop Up Bonusが付与されます。 &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5 High Symbols: จะได้รับ Free Games Bonus ที่มีค่า 128 &lt;img src = '10' height=50 offset=5/&gt;  , 118 &lt;img src = '9' height=50 offset=5/&gt;, 108 &lt;img src = '8' height=50 offset=5/&gt;  , 98 &lt;img src = '7' height=50 offset=5/&gt;  หรือ 88 &lt;img src = '6' height=50 offset=5/&gt;  หรือ Top Up Bonus ที่มีค่า 88 &lt;img src = '6' height=50 offset=5/&gt; &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5 High Symbols: Free Games Bonus dengan nilai 128 &lt;img src = '10' height=50 offset=5/&gt; , 118 &lt;img src = '9' height=50 offset=5/&gt; , 108 &lt;img src = '8' height=50 offset=5/&gt; , 98 &lt;img src = '7' height=50 offset=5/&gt; , atau 88 &lt;img src = '6' height=50 offset=5/&gt; , atau Top Up Bonus dengan nilai 88 &lt;img src = '6' height=50 offset=5/&gt;  dianugerahkan. &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5 High Symbols: Một Free Games Bonus với giá trị 128 &lt;img src = '10' height=50 offset=5/&gt; , 118 &lt;img src = '9' height=50 offset=5/&gt; , 108 &lt;img src = '8' height=50 offset=5/&gt; , 98 &lt;img src = '7' height=50 offset=5/&gt; , hoặc 88 &lt;img src = '6' height=50 offset=5/&gt; , hoặc một Top Up Bonus với giá trị 88 &lt;img src = '6' height=50 offset=5/&gt;  được trao. &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>Only the selected symbol,&lt;img src = '5' height=70 offset=-5/&gt;,  &lt;img src = '4' height=70 offset=-5/&gt;  ,&lt;img src = '3' height=70 offset=-5/&gt;   , &lt;img src = '2' height=70 offset=-5/&gt;  , &lt;img src = '1' height=70 offset=-5/&gt; ,&lt;img src = '0' height=70 offset=-5/&gt;, and  &lt;img src = '13' height=50 offset=0/&gt;  will appear during the Free Games Bonus.</t>
+  </si>
+  <si>
+    <t>선택된 심볼인 &lt;img src = '5' height=70 offset=-5/&gt;  ,&lt;img src = '4' height=70 offset=-5/&gt;  ,&lt;img src = '3' height=70 offset=-5/&gt;  ,&lt;img src = '2' height=70 offset=-5/&gt;  ,&lt;img src = '1' height=70 offset=-5/&gt;  ,&lt;img src = '0' height=70 offset=-5/&gt;  , 및  &lt;img src = '13' height=50 offset=0/&gt;  만 Free Games Bonus 동안 등장합니다.</t>
+  </si>
+  <si>
+    <t>在 Free Games Bonus 期间，仅会出现所选的符号 &lt;img src = '5' height=70 offset=-5/&gt;、&lt;img src = '4' height=70 offset=-5/&gt;、&lt;img src = '3' height=70 offset=-5/&gt;、&lt;img src = '2' height=70 offset=-5/&gt;、 &lt;img src = '1' height=70 offset=-5/&gt;、&lt;img src = '0' height=70 offset=-5/&gt; 以及  &lt;img src = '13' height=50 offset=0/&gt;  。</t>
+  </si>
+  <si>
+    <t>在 Free Games Bonus 期間，僅會出現所選的符號 &lt;img src = '5' height=70 offset=-5/&gt;、 &lt;img src = '4' height=70 offset=-5/&gt;、&lt;img src = '3' height=70 offset=-5/&gt;、 &lt;img src = '2' height=70 offset=-5/&gt;、&lt;img src = '1' height=70 offset=-5/&gt;、&lt;img src = '0' height=70 offset=-5/&gt; 以及  &lt;img src = '13' height=50 offset=0/&gt;  。</t>
+  </si>
+  <si>
+    <t>Tanging ang napiling simbolo,  &lt;img src = '5' height=70 offset=-5/&gt;  , &lt;img src = '4' height=70 offset=-5/&gt;  ,&lt;img src = '3' height=70 offset=-5/&gt;  ,&lt;img src = '2' height=70 offset=-5/&gt;  ,&lt;img src = '1' height=70 offset=-5/&gt;  ,&lt;img src = '0' height=70 offset=-5/&gt;  , at  &lt;img src = '13' height=50 offset=0/&gt;  lamang ang lalabas sa panahon ng Free Games Bonus.</t>
+  </si>
+  <si>
+    <t>選択されたシンボルである&lt;img src = '5' height=70 offset=-5/&gt;、       &lt;img src = '4' height=70 offset=-5/&gt;、&lt;img src = '3' height=70 offset=-5/&gt;、&lt;img src = '2' height=70 offset=-5/&gt;、&lt;img src = '1' height=70 offset=-5/&gt;、&lt;img src = '0' height=70 offset=-5/&gt; および &lt;img src = '13' height=50 offset=0/&gt;  のみがFree Games Bonus中に出現します。</t>
+  </si>
+  <si>
+    <t>ในระหว่าง Free Games Bonus จะมีเพียงสัญลักษณ์ที่เลือกไว้เท่านั้นที่ปรากฏ ได้แก่    &lt;img src = '5' height=70 offset=-5/&gt;  , &lt;img src = '4' height=70 offset=-5/&gt;  ,&lt;img src = '3' height=70 offset=-5/&gt;  ,&lt;img src = '2' height=70 offset=-5/&gt;  , &lt;img src = '1' height=70 offset=-5/&gt;  ,&lt;img src = '0' height=70 offset=-5/&gt; และ &lt;img src = '13' height=50 offset=0/&gt;</t>
+  </si>
+  <si>
+    <t>Only the selected symbol, &lt;img src = '5' height=70 offset=-5/&gt;  , &lt;img src = '4' height=70 offset=-5/&gt;  ,&lt;img src = '3' height=70 offset=-5/&gt;  ,&lt;img src = '2' height=70 offset=-5/&gt;  ,&lt;img src = '1' height=70 offset=-5/&gt;  ,&lt;img src = '0' height=70 offset=-5/&gt;  , and &lt;img src = '13' height=50 offset=0/&gt;  will appear during the Free Games Bonus.</t>
+  </si>
+  <si>
+    <t>Hanya simbol yang dipilih,&lt;img src = '5' height=70 offset=-5/&gt;  ,&lt;img src = '4' height=70 offset=-5/&gt;  ,&lt;img src = '3' height=70 offset=-5/&gt;  ,&lt;img src = '2' height=70 offset=-5/&gt;  ,&lt;img src = '1' height=70 offset=-5/&gt;  ,&lt;img src = '0' height=70 offset=-5/&gt;  , dan  &lt;img src = '13' height=50 offset=0/&gt;  akan muncul semasa Free Games Bonus.</t>
+  </si>
+  <si>
+    <t>Chỉ biểu tượng được chọn,&lt;img src = '5' height=70 offset=-5/&gt;  ,&lt;img src = '4' height=70 offset=-5/&gt;  ,&lt;img src = '3' height=70 offset=-5/&gt;  , &lt;img src = '2' height=70 offset=-5/&gt;  ,&lt;img src = '1' height=70 offset=-5/&gt;  ,&lt;img src = '0' height=70 offset=-5/&gt;  , và  &lt;img src = '13' height=50 offset=0/&gt;  sẽ xuất hiện trong Free Games Bonus.</t>
+  </si>
+  <si>
+    <t>Lumilitaw sa reels 2, 3, at 4 at nagsisilbing WILD 
+para sa lahat ng simbolo sa  base game maliban sa  &lt;img src = '13' height=50 offset=20 /&gt; .</t>
+  </si>
+  <si>
+    <t>6 na free games ang ibinibigay.
+Kung may hindi bababa sa 1   &lt;img src = '12' height=50 offset= 15/&gt;   na lumitaw sa screen, ang kabuuan ng lahat ng value na ipinakita sa mga triggering symbol ay ibibigay para sa bawat   &lt;img src = '12' height=50 offset= 15/&gt;   na nasa screen.
+Bukod dito, kung available ang Top Up Bonus sa panahon ng Feature Selection, maaaring maibigay ang value na ipinapakita sa Fortune Grand Jackpot meter.
+Isang alternatibong set ng reels ang gagamitin sa panahon ng Free Games Bonus. Ang mga winning combination para sa mga reel na ito ay katulad ng sa base game maliban kung may ibang nakasaad.
+Ang   &lt;img src = '12' height=50 offset= 15/&gt;   ay lumilitaw lamang sa reels 2–4 at nagsisilbing WILD para sa lahat ng simbolo maliban sa   &lt;img src = '13' height=50 offset= 15/&gt;  .
+Ang “Shou Bonus” sa panahon ng Free Games Bonus ay ang pinagsama-samang gantimpala ng lahat ng 
+&lt;img src = '12' height=50 offset= 15/&gt;   at ang kabuuan ng lahat ng value na ipinakita sa bawat   &lt;img src = '13' height=50 offset= 15/&gt;   sa base game.
+Ang “Shou Bonus” ay hindi kasama ang anumang jackpot na napanalunan.</t>
+  </si>
+  <si>
+    <t>기본 게임 중 화면에 1개 이상의  &lt;img src = '11' height=50 offset=10/&gt;  이 등장하면 잭팟 보너스가 트리거될 수 있습니다.
+12개의  &lt;img src = '16' height=50 offset=10/&gt;  로 구성된 선택 필드가 표시됩니다. 선택 시 이용 가능한 보상 중 하나가 공개됩니다.
+이용 가능한 보상에는 Mini Jackpot, Minor Jackpot, Major Jackpot 및 Grand Jackpot이 포함됩니다.
+3개의 동일한 심볼이 공개될 때까지 선택이 진행되며, 해당 미터에 표시된 값이 지급됩니다.
+볼에 쌓이는 코인의 누적량이 잭팟 보너스 트리거 확률을 증가시킵니다.</t>
+  </si>
+  <si>
+    <t>The Jackpot Bonus may be triggered if 1 or more  &lt;img src = '11' height=50 offset=10/&gt; land on screen during the base game.
+A pick field is displayed with 12  &lt;img src = '16' height=50 offset=10/&gt;   . Picks will reveal one of the available prizes.
+Available prizes include the Mini Jackpot, Minor Jackpot, Major Jackpot, and Grand Jackpot.
+Picks are made until 3 matching symbols are revealed, and the value displayed in the corresponding meter is awarded.
+The accumulation of coins in the bowl increases the chances of triggering the Jackpot Bonus.</t>
+  </si>
+  <si>
+    <t>在基础游戏期间，如果屏幕上出现1个或以上的  &lt;img src = '11' height=50 offset=10/&gt;  ，则可能触发Jackpot Bonus。
+将显示一个包含12个  &lt;img src = '16' height=50 offset=10/&gt; 的选择区域。每次选择会揭示一个可获得的奖励。
+可获得的奖励包括 Mini Jackpot、Minor Jackpot、Major Jackpot 和 Grand Jackpot。
+选择将持续进行，直到揭示出3个相同的符号，并奖励对应计量器中显示的数值。
+碗中金币的累积会增加触发Jackpot Bonus的概率。</t>
+  </si>
+  <si>
+    <t>在基礎遊戲期間，如果畫面上出現1個或以上的 &lt;img src = '11' height=50 offset=10/&gt;  ，則可能觸發Jackpot Bonus。
+將顯示一個包含12個 &lt;img src = '16' height=50 offset=10/&gt; 的選擇區域。每次選擇會揭示一個可獲得的獎勵。
+可獲得的獎勵包括 Mini Jackpot、Minor Jackpot、Major Jackpot 和 Grand Jackpot。
+選擇將持續進行，直到揭示出3個相同的符號，並獎勵對應計量器中顯示的數值。
+碗中金幣的累積會增加觸發Jackpot Bonus的機率。</t>
+  </si>
+  <si>
+    <t>Maaaring ma-trigger ang Jackpot Bonus kung may 1 o higit pang    &lt;img src = '11' height=50 offset=10/&gt;   na lumapag sa screen sa base game.
+Isang pick field na may 12 &lt;img src = '16' height=50 offset=10/&gt; ang ipapakita. Ang bawat pick ay magpapakita ng isa sa mga available na premyo.
+Kabilang sa mga available na premyo ang Mini Jackpot, Minor Jackpot, Major Jackpot, at Grand Jackpot.
+Magpapatuloy ang pagpili hanggang sa maipakita ang 3 magkakatugmang simbolo, at ang value na ipinapakita sa kaukulang meter ang ibibigay.
+Ang pag-ipon ng mga coin sa bowl ay nagpapataas ng tsansa na ma-trigger ang Jackpot Bonus.</t>
+  </si>
+  <si>
+    <t>ベースゲーム中に画面上に1つ以上の    &lt;img src = '11' height=50 offset=10/&gt;   が停止した場合、ジャックポットボーナスが発動することがあります。
+12個の &lt;img src = '16' height=50 offset=10/&gt;で構成されたピックフィールドが表示されます。選択すると、利用可能な賞のいずれかが表示されます。
+利用可能な賞には、Mini Jackpot、Minor Jackpot、Major Jackpot、Grand Jackpot が含まれます。
+3つの一致するシンボルが表示されるまで選択が行われ、対応するメーターに表示された値が付与されます。
+ボウルに蓄積されるコインの量が、ジャックポットボーナスの発動確率を高めます。</t>
+  </si>
+  <si>
+    <t>โบนัสแจ็คพอตอาจถูกทริกเกอร์ หากมี &lt;img src = '11' height=50 offset=10/&gt; อย่างน้อย 1 ตัวลงบนหน้าจอในระหว่างเกมหลัก
+จะแสดงหน้าจอเลือกที่มี &lt;img src = '16' height=50 offset=10/&gt; จำนวน 12 ตัว การเลือกแต่ละครั้งจะเผยหนึ่งในรางวัลที่มีให้
+รางวัลที่มีให้รวมถึง Mini Jackpot, Minor Jackpot, Major Jackpot และ Grand Jackpot
+จะทำการเลือกต่อไปจนกว่าจะพบสัญลักษณ์ที่เหมือนกัน 3 ตัว และจะได้รับค่าที่แสดงในมิเตอร์ที่เกี่ยวข้อง
+การสะสมเหรียญในชามจะเพิ่มโอกาสในการทริกเกอร์โบนัสแจ็คพอต</t>
+  </si>
+  <si>
+    <t>The Jackpot Bonus may be triggered if 1 or more  &lt;img src = '11' height=50 offset=10/&gt;    land on screen during the base game.
+A pick field is displayed with 12  &lt;img src = '16' height=50 offset=10/&gt;   . Picks will reveal one of the available prizes.
+Available prizes include the Mini Jackpot, Minor Jackpot, Major Jackpot, and Grand Jackpot.
+Picks are made until 3 matching symbols are revealed, and the value displayed in the corresponding meter is awarded.
+The accumulation of coins in the bowl increases the chances of triggering the Jackpot Bonus.</t>
+  </si>
+  <si>
+    <t>Jackpot Bonus mungkin dicetuskan jika 1 atau lebih  &lt;img src = '11' height=50 offset=10/&gt; mendarat pada skrin semasa base game.
+Medan pilihan dengan 12  &lt;img src = '16' height=50 offset=10/&gt;    dipaparkan. Pilihan akan mendedahkan salah satu hadiah yang tersedia.
+Hadiah yang tersedia termasuk Mini Jackpot, Minor Jackpot, Major Jackpot, dan Grand Jackpot.
+Pilihan dibuat sehingga 3 simbol yang sepadan didedahkan, dan nilai yang dipaparkan dalam meter yang berkaitan dianugerahkan.
+Pengumpulan syiling dalam mangkuk meningkatkan peluang mencetuskan Jackpot Bonus.</t>
+  </si>
+  <si>
+    <t>Jackpot Bonus có thể được kích hoạt nếu 1 hoặc nhiều  &lt;img src = '11' height=50 offset=10/&gt;  rơi trên màn hình trong trò chơi cơ bản.
+Một vùng chọn với 12  &lt;img src = '16' height=50 offset=10/&gt; được hiển thị. Mỗi lần chọn sẽ tiết lộ một trong các giải thưởng có sẵn.
+Các giải thưởng có sẵn bao gồm Mini Jackpot, Minor Jackpot, Major Jackpot, và Grand Jackpot.
+Việc chọn tiếp tục cho đến khi 3 biểu tượng khớp nhau được tiết lộ, và giá trị hiển thị trong đồng hồ tương ứng được trao.
+Việc tích lũy xu trong bát làm tăng cơ hội kích hoạt Jackpot Bonus.</t>
   </si>
 </sst>
 </file>
@@ -4649,7 +4662,7 @@
         <v>593</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>741</v>
+        <v>705</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -4786,7 +4799,7 @@
         <v>235</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>740</v>
+        <v>704</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>236</v>
@@ -5622,22 +5635,22 @@
         <v>650</v>
       </c>
       <c r="G64" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="H64" s="4" t="s">
         <v>651</v>
       </c>
-      <c r="H64" s="4" t="s">
+      <c r="I64" s="4" t="s">
         <v>652</v>
-      </c>
-      <c r="I64" s="4" t="s">
-        <v>653</v>
       </c>
       <c r="J64" s="4" t="s">
         <v>647</v>
       </c>
       <c r="K64" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="L64" s="4" t="s">
         <v>654</v>
-      </c>
-      <c r="L64" s="4" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -5686,39 +5699,39 @@
         <v>457</v>
       </c>
       <c r="C66" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>656</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="E66" s="4" t="s">
         <v>657</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="F66" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="G66" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="H66" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="H66" s="4" t="s">
+      <c r="I66" s="4" t="s">
         <v>661</v>
       </c>
-      <c r="I66" s="4" t="s">
+      <c r="J66" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="K66" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="J66" s="4" t="s">
-        <v>656</v>
-      </c>
-      <c r="K66" s="4" t="s">
+      <c r="L66" s="4" t="s">
         <v>663</v>
-      </c>
-      <c r="L66" s="4" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>457</v>
@@ -5756,40 +5769,40 @@
     </row>
     <row r="68" spans="1:12" ht="210">
       <c r="A68" s="5" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>457</v>
       </c>
       <c r="C68" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="E68" s="7" t="s">
         <v>667</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>668</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>669</v>
-      </c>
       <c r="F68" s="7" t="s">
-        <v>670</v>
+        <v>707</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>671</v>
+        <v>708</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>742</v>
+        <v>709</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>672</v>
+        <v>710</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>667</v>
+        <v>706</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>673</v>
+        <v>711</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>674</v>
+        <v>712</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -5827,7 +5840,7 @@
         <v>485</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>739</v>
+        <v>703</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="150">
@@ -5838,34 +5851,34 @@
         <v>457</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>693</v>
+        <v>668</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>694</v>
+        <v>669</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>695</v>
+        <v>670</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>696</v>
+        <v>671</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>697</v>
+        <v>672</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>698</v>
+        <v>673</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>699</v>
+        <v>674</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>693</v>
+        <v>668</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>700</v>
+        <v>675</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>701</v>
+        <v>676</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="105">
@@ -5876,34 +5889,34 @@
         <v>457</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>675</v>
+        <v>713</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>676</v>
+        <v>714</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>679</v>
+        <v>715</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>678</v>
+        <v>716</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>677</v>
+        <v>717</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>680</v>
+        <v>719</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>675</v>
+        <v>713</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>682</v>
+        <v>720</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>683</v>
+        <v>721</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="90">
@@ -5914,34 +5927,34 @@
         <v>457</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>684</v>
+        <v>722</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>685</v>
+        <v>723</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>686</v>
+        <v>724</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>687</v>
+        <v>725</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>688</v>
+        <v>726</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>689</v>
+        <v>727</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>690</v>
+        <v>728</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>691</v>
+        <v>729</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>692</v>
+        <v>730</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -5990,34 +6003,34 @@
         <v>457</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>702</v>
+        <v>677</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>703</v>
+        <v>678</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>704</v>
+        <v>679</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>705</v>
+        <v>680</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>706</v>
+        <v>733</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>707</v>
+        <v>681</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>708</v>
+        <v>682</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>702</v>
+        <v>677</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>709</v>
+        <v>683</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>710</v>
+        <v>684</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -6066,34 +6079,34 @@
         <v>457</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>711</v>
+        <v>685</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>712</v>
+        <v>686</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>713</v>
+        <v>687</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>714</v>
+        <v>688</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>715</v>
+        <v>689</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>716</v>
+        <v>690</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>717</v>
+        <v>691</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>711</v>
+        <v>685</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>718</v>
+        <v>692</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>719</v>
+        <v>693</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -6142,34 +6155,34 @@
         <v>457</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>721</v>
+        <v>734</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>722</v>
+        <v>736</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>723</v>
+        <v>737</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>724</v>
+        <v>738</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>725</v>
+        <v>739</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>726</v>
+        <v>740</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>727</v>
+        <v>742</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>728</v>
+        <v>743</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -6218,34 +6231,34 @@
         <v>457</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>729</v>
+        <v>694</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>730</v>
+        <v>695</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>731</v>
+        <v>696</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>732</v>
+        <v>697</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>733</v>
+        <v>698</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>734</v>
+        <v>699</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>735</v>
+        <v>700</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>729</v>
+        <v>694</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>736</v>
+        <v>701</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>737</v>
+        <v>702</v>
       </c>
     </row>
   </sheetData>

--- a/LocalizationStringTable.xlsx
+++ b/LocalizationStringTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CocosProject\FortuneofRaSecretTreasure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99DC94AB-9532-41DB-AB90-42DA04807A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE28D486-3DA6-49ED-8411-BD05369B68AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{01A4B2FD-E311-460F-AD11-CF593C8E3E63}"/>
   </bookViews>
@@ -1775,9 +1775,6 @@
     <t>TETAPAN AUTOPLAY</t>
   </si>
   <si>
-    <t>CÀI ĐẶT AUTOPLAY</t>
-  </si>
-  <si>
     <t>BILANGAN AUTOSPIN</t>
   </si>
   <si>
@@ -2713,6 +2710,9 @@
 Các giải thưởng có sẵn bao gồm Mini Jackpot, Minor Jackpot, Major Jackpot, và Grand Jackpot.
 Việc chọn tiếp tục cho đến khi 3 biểu tượng khớp nhau được tiết lộ, và giá trị hiển thị trong đồng hồ tương ứng được trao.
 Việc tích lũy xu trong bát làm tăng cơ hội kích hoạt Jackpot Bonus.</t>
+  </si>
+  <si>
+    <t>CÀI ĐẶT TỰ ĐỘNG CHƠI</t>
   </si>
 </sst>
 </file>
@@ -3978,7 +3978,7 @@
         <v>563</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>564</v>
+        <v>743</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -4013,10 +4013,10 @@
         <v>118</v>
       </c>
       <c r="K21" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="L21" s="12" t="s">
         <v>565</v>
-      </c>
-      <c r="L21" s="12" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -4051,10 +4051,10 @@
         <v>126</v>
       </c>
       <c r="K22" s="12" t="s">
+        <v>566</v>
+      </c>
+      <c r="L22" s="12" t="s">
         <v>567</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -4089,10 +4089,10 @@
         <v>134</v>
       </c>
       <c r="K23" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="L23" s="12" t="s">
         <v>569</v>
-      </c>
-      <c r="L23" s="12" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -4127,10 +4127,10 @@
         <v>142</v>
       </c>
       <c r="K24" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="L24" s="12" t="s">
         <v>571</v>
-      </c>
-      <c r="L24" s="12" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -4165,10 +4165,10 @@
         <v>151</v>
       </c>
       <c r="K25" s="12" t="s">
+        <v>572</v>
+      </c>
+      <c r="L25" s="12" t="s">
         <v>573</v>
-      </c>
-      <c r="L25" s="12" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -4241,10 +4241,10 @@
         <v>160</v>
       </c>
       <c r="K27" s="12" t="s">
+        <v>574</v>
+      </c>
+      <c r="L27" s="12" t="s">
         <v>575</v>
-      </c>
-      <c r="L27" s="12" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -4279,10 +4279,10 @@
         <v>168</v>
       </c>
       <c r="K28" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="L28" s="12" t="s">
         <v>577</v>
-      </c>
-      <c r="L28" s="12" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -4317,10 +4317,10 @@
         <v>175</v>
       </c>
       <c r="K29" s="12" t="s">
+        <v>578</v>
+      </c>
+      <c r="L29" s="12" t="s">
         <v>579</v>
-      </c>
-      <c r="L29" s="12" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -4355,10 +4355,10 @@
         <v>418</v>
       </c>
       <c r="K30" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="L30" s="12" t="s">
         <v>581</v>
-      </c>
-      <c r="L30" s="12" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -4393,10 +4393,10 @@
         <v>175</v>
       </c>
       <c r="K31" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="L31" s="12" t="s">
         <v>579</v>
-      </c>
-      <c r="L31" s="12" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -4431,10 +4431,10 @@
         <v>432</v>
       </c>
       <c r="K32" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="L32" s="12" t="s">
         <v>583</v>
-      </c>
-      <c r="L32" s="12" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -4469,10 +4469,10 @@
         <v>260</v>
       </c>
       <c r="K33" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="L33" s="12" t="s">
         <v>585</v>
-      </c>
-      <c r="L33" s="12" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -4545,10 +4545,10 @@
         <v>443</v>
       </c>
       <c r="K35" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="L35" s="12" t="s">
         <v>587</v>
-      </c>
-      <c r="L35" s="12" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -4583,10 +4583,10 @@
         <v>184</v>
       </c>
       <c r="K36" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="L36" s="12" t="s">
         <v>589</v>
-      </c>
-      <c r="L36" s="12" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -4621,10 +4621,10 @@
         <v>192</v>
       </c>
       <c r="K37" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="L37" s="12" t="s">
         <v>591</v>
-      </c>
-      <c r="L37" s="12" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="30">
@@ -4659,10 +4659,10 @@
         <v>200</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -4697,10 +4697,10 @@
         <v>208</v>
       </c>
       <c r="K39" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="L39" s="4" t="s">
         <v>594</v>
-      </c>
-      <c r="L39" s="4" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="30">
@@ -4735,10 +4735,10 @@
         <v>216</v>
       </c>
       <c r="K40" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="L40" s="4" t="s">
         <v>596</v>
-      </c>
-      <c r="L40" s="4" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -4773,10 +4773,10 @@
         <v>224</v>
       </c>
       <c r="K41" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="L41" s="4" t="s">
         <v>598</v>
-      </c>
-      <c r="L41" s="4" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="30">
@@ -4799,7 +4799,7 @@
         <v>235</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>236</v>
@@ -4811,10 +4811,10 @@
         <v>232</v>
       </c>
       <c r="K42" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="L42" s="4" t="s">
         <v>600</v>
-      </c>
-      <c r="L42" s="4" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -4849,10 +4849,10 @@
         <v>239</v>
       </c>
       <c r="K43" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="L43" s="4" t="s">
         <v>602</v>
-      </c>
-      <c r="L43" s="4" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="30">
@@ -4887,10 +4887,10 @@
         <v>246</v>
       </c>
       <c r="K44" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="L44" s="4" t="s">
         <v>604</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -4925,10 +4925,10 @@
         <v>254</v>
       </c>
       <c r="K45" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="L45" s="4" t="s">
         <v>606</v>
-      </c>
-      <c r="L45" s="4" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -4963,10 +4963,10 @@
         <v>260</v>
       </c>
       <c r="K46" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="L46" s="4" t="s">
         <v>585</v>
-      </c>
-      <c r="L46" s="4" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -5001,10 +5001,10 @@
         <v>265</v>
       </c>
       <c r="K47" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="L47" s="4" t="s">
         <v>608</v>
-      </c>
-      <c r="L47" s="4" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -5077,10 +5077,10 @@
         <v>277</v>
       </c>
       <c r="K49" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="L49" s="4" t="s">
         <v>610</v>
-      </c>
-      <c r="L49" s="4" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -5115,10 +5115,10 @@
         <v>284</v>
       </c>
       <c r="K50" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="L50" s="4" t="s">
         <v>612</v>
-      </c>
-      <c r="L50" s="4" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -5153,10 +5153,10 @@
         <v>277</v>
       </c>
       <c r="K51" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="L51" s="4" t="s">
         <v>610</v>
-      </c>
-      <c r="L51" s="4" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -5191,10 +5191,10 @@
         <v>293</v>
       </c>
       <c r="K52" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="L52" s="4" t="s">
         <v>614</v>
-      </c>
-      <c r="L52" s="4" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -5229,10 +5229,10 @@
         <v>301</v>
       </c>
       <c r="K53" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="L53" s="4" t="s">
         <v>616</v>
-      </c>
-      <c r="L53" s="4" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="60">
@@ -5267,10 +5267,10 @@
         <v>309</v>
       </c>
       <c r="K54" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="L54" s="4" t="s">
         <v>618</v>
-      </c>
-      <c r="L54" s="4" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -5305,10 +5305,10 @@
         <v>317</v>
       </c>
       <c r="K55" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="L55" s="4" t="s">
         <v>620</v>
-      </c>
-      <c r="L55" s="4" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="30">
@@ -5343,10 +5343,10 @@
         <v>324</v>
       </c>
       <c r="K56" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="L56" s="4" t="s">
         <v>622</v>
-      </c>
-      <c r="L56" s="4" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -5381,10 +5381,10 @@
         <v>331</v>
       </c>
       <c r="K57" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="L57" s="4" t="s">
         <v>624</v>
-      </c>
-      <c r="L57" s="4" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -5419,10 +5419,10 @@
         <v>339</v>
       </c>
       <c r="K58" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="L58" s="4" t="s">
         <v>626</v>
-      </c>
-      <c r="L58" s="4" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="90">
@@ -5457,10 +5457,10 @@
         <v>402</v>
       </c>
       <c r="K59" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="L59" s="4" t="s">
         <v>628</v>
-      </c>
-      <c r="L59" s="4" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="30">
@@ -5495,10 +5495,10 @@
         <v>409</v>
       </c>
       <c r="K60" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="L60" s="4" t="s">
         <v>630</v>
-      </c>
-      <c r="L60" s="4" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -5533,10 +5533,10 @@
         <v>452</v>
       </c>
       <c r="K61" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="L61" s="4" t="s">
         <v>632</v>
-      </c>
-      <c r="L61" s="4" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="195">
@@ -5547,34 +5547,34 @@
         <v>457</v>
       </c>
       <c r="C62" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="E62" s="4" t="s">
         <v>639</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="F62" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="G62" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="G62" s="4" t="s">
+      <c r="H62" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="H62" s="4" t="s">
+      <c r="I62" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="I62" s="4" t="s">
+      <c r="J62" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="K62" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="J62" s="4" t="s">
-        <v>638</v>
-      </c>
-      <c r="K62" s="4" t="s">
+      <c r="L62" s="4" t="s">
         <v>645</v>
-      </c>
-      <c r="L62" s="4" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -5623,34 +5623,34 @@
         <v>457</v>
       </c>
       <c r="C64" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>647</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="E64" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="F64" s="4" t="s">
         <v>649</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="G64" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="H64" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="G64" s="4" t="s">
-        <v>732</v>
-      </c>
-      <c r="H64" s="4" t="s">
+      <c r="I64" s="4" t="s">
         <v>651</v>
       </c>
-      <c r="I64" s="4" t="s">
+      <c r="J64" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="K64" s="4" t="s">
         <v>652</v>
       </c>
-      <c r="J64" s="4" t="s">
-        <v>647</v>
-      </c>
-      <c r="K64" s="4" t="s">
+      <c r="L64" s="4" t="s">
         <v>653</v>
-      </c>
-      <c r="L64" s="4" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -5699,39 +5699,39 @@
         <v>457</v>
       </c>
       <c r="C66" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>655</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="E66" s="4" t="s">
         <v>656</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="F66" s="4" t="s">
         <v>657</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="G66" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="H66" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="H66" s="4" t="s">
+      <c r="I66" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="I66" s="4" t="s">
+      <c r="J66" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="K66" s="4" t="s">
         <v>661</v>
       </c>
-      <c r="J66" s="4" t="s">
-        <v>655</v>
-      </c>
-      <c r="K66" s="4" t="s">
+      <c r="L66" s="4" t="s">
         <v>662</v>
-      </c>
-      <c r="L66" s="4" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" s="5" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>457</v>
@@ -5761,48 +5761,48 @@
         <v>475</v>
       </c>
       <c r="K67" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="L67" s="4" t="s">
         <v>634</v>
-      </c>
-      <c r="L67" s="4" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="210">
       <c r="A68" s="5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>457</v>
       </c>
       <c r="C68" s="7" t="s">
+        <v>705</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="F68" s="7" t="s">
         <v>706</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>666</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>667</v>
-      </c>
-      <c r="F68" s="7" t="s">
+      <c r="G68" s="7" t="s">
         <v>707</v>
       </c>
-      <c r="G68" s="7" t="s">
+      <c r="H68" s="7" t="s">
         <v>708</v>
       </c>
-      <c r="H68" s="7" t="s">
+      <c r="I68" s="8" t="s">
         <v>709</v>
       </c>
-      <c r="I68" s="8" t="s">
+      <c r="J68" s="7" t="s">
+        <v>705</v>
+      </c>
+      <c r="K68" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="J68" s="7" t="s">
-        <v>706</v>
-      </c>
-      <c r="K68" s="4" t="s">
+      <c r="L68" s="4" t="s">
         <v>711</v>
-      </c>
-      <c r="L68" s="4" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -5840,7 +5840,7 @@
         <v>485</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="150">
@@ -5851,34 +5851,34 @@
         <v>457</v>
       </c>
       <c r="C70" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="E70" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="F70" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="G70" s="4" t="s">
         <v>671</v>
       </c>
-      <c r="G70" s="4" t="s">
+      <c r="H70" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="H70" s="4" t="s">
+      <c r="I70" s="4" t="s">
         <v>673</v>
       </c>
-      <c r="I70" s="4" t="s">
+      <c r="J70" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="K70" s="4" t="s">
         <v>674</v>
       </c>
-      <c r="J70" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="K70" s="4" t="s">
+      <c r="L70" s="4" t="s">
         <v>675</v>
-      </c>
-      <c r="L70" s="4" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="105">
@@ -5889,34 +5889,34 @@
         <v>457</v>
       </c>
       <c r="C71" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>713</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="E71" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="E71" s="4" t="s">
+      <c r="F71" s="4" t="s">
         <v>715</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="G71" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="G71" s="4" t="s">
+      <c r="H71" s="4" t="s">
         <v>717</v>
       </c>
-      <c r="H71" s="4" t="s">
+      <c r="I71" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="I71" s="4" t="s">
+      <c r="J71" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="K71" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="J71" s="4" t="s">
-        <v>713</v>
-      </c>
-      <c r="K71" s="4" t="s">
+      <c r="L71" s="4" t="s">
         <v>720</v>
-      </c>
-      <c r="L71" s="4" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="90">
@@ -5927,34 +5927,34 @@
         <v>457</v>
       </c>
       <c r="C72" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="E72" s="4" t="s">
         <v>723</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="F72" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="F72" s="4" t="s">
+      <c r="G72" s="4" t="s">
         <v>725</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="H72" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="H72" s="4" t="s">
+      <c r="I72" s="4" t="s">
         <v>727</v>
       </c>
-      <c r="I72" s="4" t="s">
+      <c r="J72" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="J72" s="4" t="s">
+      <c r="K72" s="4" t="s">
         <v>729</v>
       </c>
-      <c r="K72" s="4" t="s">
+      <c r="L72" s="4" t="s">
         <v>730</v>
-      </c>
-      <c r="L72" s="4" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -6003,34 +6003,34 @@
         <v>457</v>
       </c>
       <c r="C74" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="E74" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="E74" s="4" t="s">
+      <c r="F74" s="4" t="s">
         <v>679</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="G74" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="H74" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="G74" s="4" t="s">
-        <v>733</v>
-      </c>
-      <c r="H74" s="4" t="s">
+      <c r="I74" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="I74" s="4" t="s">
+      <c r="J74" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="K74" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="J74" s="4" t="s">
-        <v>677</v>
-      </c>
-      <c r="K74" s="4" t="s">
+      <c r="L74" s="4" t="s">
         <v>683</v>
-      </c>
-      <c r="L74" s="4" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -6079,34 +6079,34 @@
         <v>457</v>
       </c>
       <c r="C76" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="E76" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="E76" s="4" t="s">
+      <c r="F76" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="G76" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="H76" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="H76" s="4" t="s">
+      <c r="I76" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="I76" s="4" t="s">
+      <c r="J76" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="K76" s="4" t="s">
         <v>691</v>
       </c>
-      <c r="J76" s="4" t="s">
-        <v>685</v>
-      </c>
-      <c r="K76" s="4" t="s">
+      <c r="L76" s="4" t="s">
         <v>692</v>
-      </c>
-      <c r="L76" s="4" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -6155,34 +6155,34 @@
         <v>457</v>
       </c>
       <c r="C78" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="E78" s="4" t="s">
         <v>735</v>
       </c>
-      <c r="D78" s="4" t="s">
-        <v>734</v>
-      </c>
-      <c r="E78" s="4" t="s">
+      <c r="F78" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="G78" s="4" t="s">
         <v>737</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="H78" s="4" t="s">
         <v>738</v>
       </c>
-      <c r="H78" s="4" t="s">
+      <c r="I78" s="4" t="s">
         <v>739</v>
       </c>
-      <c r="I78" s="4" t="s">
+      <c r="J78" s="4" t="s">
         <v>740</v>
       </c>
-      <c r="J78" s="4" t="s">
+      <c r="K78" s="4" t="s">
         <v>741</v>
       </c>
-      <c r="K78" s="4" t="s">
+      <c r="L78" s="4" t="s">
         <v>742</v>
-      </c>
-      <c r="L78" s="4" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -6217,10 +6217,10 @@
         <v>517</v>
       </c>
       <c r="K79" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="L79" s="4" t="s">
         <v>636</v>
-      </c>
-      <c r="L79" s="4" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="315">
@@ -6231,34 +6231,34 @@
         <v>457</v>
       </c>
       <c r="C80" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="E80" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="F80" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="F80" s="4" t="s">
+      <c r="G80" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="H80" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="H80" s="4" t="s">
+      <c r="I80" s="4" t="s">
         <v>699</v>
       </c>
-      <c r="I80" s="4" t="s">
+      <c r="J80" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="K80" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="J80" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="K80" s="4" t="s">
+      <c r="L80" s="4" t="s">
         <v>701</v>
-      </c>
-      <c r="L80" s="4" t="s">
-        <v>702</v>
       </c>
     </row>
   </sheetData>

--- a/LocalizationStringTable.xlsx
+++ b/LocalizationStringTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CocosProject\FortuneofRaSecretTreasure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE28D486-3DA6-49ED-8411-BD05369B68AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EE36EF-7EB3-4F9D-B5CF-D4D501EFD916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{01A4B2FD-E311-460F-AD11-CF593C8E3E63}"/>
   </bookViews>
@@ -2712,7 +2712,7 @@
 Việc tích lũy xu trong bát làm tăng cơ hội kích hoạt Jackpot Bonus.</t>
   </si>
   <si>
-    <t>CÀI ĐẶT TỰ ĐỘNG CHƠI</t>
+    <t>CÀI ĐẶT AUTOSPIN</t>
   </si>
 </sst>
 </file>

--- a/LocalizationStringTable.xlsx
+++ b/LocalizationStringTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CocosProject\FortuneofRaSecretTreasure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EE36EF-7EB3-4F9D-B5CF-D4D501EFD916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDE9308-D2DB-474E-9F26-A9CD09EF8138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{01A4B2FD-E311-460F-AD11-CF593C8E3E63}"/>
   </bookViews>
@@ -2571,33 +2571,6 @@
 Sự kiện may mắn này có thể xảy ra ngay cả khi không có &lt;img src = '13' height=50 offset=20/&gt;  nào xuất hiện trong kết quả reel, và kết quả được xác định độc lập trên mỗi lượt quay.</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;5 High Symbols: A Free Games Bonus with a value of 128 &lt;img src = '10' height=50 offset=5/&gt; , 118 &lt;img src = '9' height=50 offset=5/&gt; , 108 &lt;img src = '8' height=50 offset=5/&gt; , 98 &lt;img src = '7' height=50 offset=5/&gt; , or 88 &lt;img src = '6' height=50 offset=5/&gt; , or a Top Up Bonus with a value of 88 &lt;img src = '6' height=50 offset=5/&gt; is awarded. &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5개의 High Symbols: 128 &lt;img src = '10' height=50 offset=5/&gt;  , 118 &lt;img src = '9' height=50 offset=5/&gt;  , 108 &lt;img src = '8' height=50 offset=5/&gt;  , 98 &lt;img src = '7' height=50 offset=5/&gt;  , 또는 88     &lt;img src = '6' height=50 offset=5/&gt;  의 값을 가지는 Free Games Bonus 또는 88     &lt;img src = '6' height=50 offset=5/&gt;  의 값을 가지는 Top Up Bonus가 지급됩니다. &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5个高等级符号：数值为 128 &lt;img src = '10' height=50 offset=5/&gt; 、118 &lt;img src = '9' height=50 offset=5/&gt;  、108 &lt;img src = '8' height=50 offset=5/&gt;  、 98 &lt;img src = '7' height=50 offset=5/&gt;  或 88 &lt;img src = '6' height=50 offset=5/&gt;  的 Free Games Bonus，或数值为 88     &lt;img src = '6' height=50 offset=5/&gt;  的 Top Up Bonus。 &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5個高階符號：數值為 128 &lt;img src = '10' height=50 offset=5/&gt;  、118 &lt;img src = '9' height=50 offset=5/&gt;  、108 &lt;img src = '8' height=50 offset=5/&gt;  、98 &lt;img src = '7' height=50 offset=5/&gt;  或 88 &lt;img src = '6' height=50 offset=5/&gt;  的 Free Games Bonus，或數值為 88     &lt;img src = '6' height=50 offset=5/&gt;  的 Top Up Bonus。 &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5 High Symbols: Ang Free Games Bonus na may value na 128 &lt;img src = '10' height=50 offset=5/&gt;  , 118 &lt;img src = '9' height=50 offset=5/&gt;  , 108 &lt;img src = '8' height=50 offset=5/&gt;  , 98 &lt;img src = '7' height=50 offset=5/&gt;  , o 88 &lt;img src = '6' height=50 offset=5/&gt;  , o ang Top Up Bonus na may value na 88     &lt;img src = '6' height=50 offset=5/&gt;  ay ibinibigay. &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5つのHigh Symbols：128 &lt;img src = '10' height=50 offset=5/&gt;  、118 &lt;img src = '9' height=50 offset=5/&gt;  、108 &lt;img src = '8' height=50 offset=5/&gt;  、98 &lt;img src = '7' height=50 offset=5/&gt;  、または88 &lt;img src = '6' height=50 offset=5/&gt;  の値を持つFree Games Bonus、または88 &lt;img src = '6' height=50 offset=5/&gt;  の値を持つTop Up Bonusが付与されます。 &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5 High Symbols: จะได้รับ Free Games Bonus ที่มีค่า 128 &lt;img src = '10' height=50 offset=5/&gt;  , 118 &lt;img src = '9' height=50 offset=5/&gt;, 108 &lt;img src = '8' height=50 offset=5/&gt;  , 98 &lt;img src = '7' height=50 offset=5/&gt;  หรือ 88 &lt;img src = '6' height=50 offset=5/&gt;  หรือ Top Up Bonus ที่มีค่า 88 &lt;img src = '6' height=50 offset=5/&gt; &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5 High Symbols: Free Games Bonus dengan nilai 128 &lt;img src = '10' height=50 offset=5/&gt; , 118 &lt;img src = '9' height=50 offset=5/&gt; , 108 &lt;img src = '8' height=50 offset=5/&gt; , 98 &lt;img src = '7' height=50 offset=5/&gt; , atau 88 &lt;img src = '6' height=50 offset=5/&gt; , atau Top Up Bonus dengan nilai 88 &lt;img src = '6' height=50 offset=5/&gt;  dianugerahkan. &lt;color=white&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;5 High Symbols: Một Free Games Bonus với giá trị 128 &lt;img src = '10' height=50 offset=5/&gt; , 118 &lt;img src = '9' height=50 offset=5/&gt; , 108 &lt;img src = '8' height=50 offset=5/&gt; , 98 &lt;img src = '7' height=50 offset=5/&gt; , hoặc 88 &lt;img src = '6' height=50 offset=5/&gt; , hoặc một Top Up Bonus với giá trị 88 &lt;img src = '6' height=50 offset=5/&gt;  được trao. &lt;color=white&gt;</t>
-  </si>
-  <si>
     <t>Only the selected symbol,&lt;img src = '5' height=70 offset=-5/&gt;,  &lt;img src = '4' height=70 offset=-5/&gt;  ,&lt;img src = '3' height=70 offset=-5/&gt;   , &lt;img src = '2' height=70 offset=-5/&gt;  , &lt;img src = '1' height=70 offset=-5/&gt; ,&lt;img src = '0' height=70 offset=-5/&gt;, and  &lt;img src = '13' height=50 offset=0/&gt;  will appear during the Free Games Bonus.</t>
   </si>
   <si>
@@ -2713,6 +2686,33 @@
   </si>
   <si>
     <t>CÀI ĐẶT AUTOSPIN</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5 High Symbols: A Free Games Bonus with a value of 128 &lt;img src = '6' height=50 offset=5/&gt; , 118 &lt;img src = '7' height=50 offset=5/&gt; , 108 &lt;img src = '8' height=50 offset=5/&gt; , 98 &lt;img src = '9' height=50 offset=5/&gt; , or 88 &lt;img src = '10' height=50 offset=5/&gt; , or a Top Up Bonus with a value of 88 &lt;img src = '10' height=50 offset=5/&gt; is awarded. &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5개의 High Symbols: 128 &lt;img src = '6' height=50 offset=5/&gt;  , 118 &lt;img src = '7' height=50 offset=5/&gt;  , 108 &lt;img src = '8' height=50 offset=5/&gt;  , 98 &lt;img src = '9' height=50 offset=5/&gt;  , 또는 88     &lt;img src = '10' height=50 offset=5/&gt;  의 값을 가지는 Free Games Bonus 또는 88     &lt;img src = '10' height=50 offset=5/&gt;  의 값을 가지는 Top Up Bonus가 지급됩니다. &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5个高等级符号：数值为 128 &lt;img src = '6' height=50 offset=5/&gt; 、118 &lt;img src = '7' height=50 offset=5/&gt;  、108 &lt;img src = '8' height=50 offset=5/&gt;  、 98 &lt;img src = '9' height=50 offset=5/&gt;  或 88 &lt;img src = '10' height=50 offset=5/&gt;  的 Free Games Bonus，或数值为 88     &lt;img src = '10' height=50 offset=5/&gt;  的 Top Up Bonus。 &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5個高階符號：數值為 128 &lt;img src = '6' height=50 offset=5/&gt;  、118 &lt;img src = '7' height=50 offset=5/&gt;  、108 &lt;img src = '8' height=50 offset=5/&gt;  、98 &lt;img src = '9' height=50 offset=5/&gt;  或 88 &lt;img src = '10' height=50 offset=5/&gt;  的 Free Games Bonus，或數值為 88     &lt;img src = '10' height=50 offset=5/&gt;  的 Top Up Bonus。 &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5 High Symbols: Ang Free Games Bonus na may value na 128 &lt;img src = '6' height=50 offset=5/&gt;  , 118 &lt;img src = '7' height=50 offset=5/&gt;  , 108 &lt;img src = '8' height=50 offset=5/&gt;  , 98 &lt;img src = '9' height=50 offset=5/&gt;  , o 88 &lt;img src = '10' height=50 offset=5/&gt;  , o ang Top Up Bonus na may value na 88     &lt;img src = '10' height=50 offset=5/&gt;  ay ibinibigay. &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5つのHigh Symbols：128 &lt;img src = '6' height=50 offset=5/&gt;  、118 &lt;img src = '7' height=50 offset=5/&gt;  、108 &lt;img src = '8' height=50 offset=5/&gt;  、98 &lt;img src = '9' height=50 offset=5/&gt;  、または88 &lt;img src = '10' height=50 offset=5/&gt;  の値を持つFree Games Bonus、または88 &lt;img src = '10' height=50 offset=5/&gt;  の値を持つTop Up Bonusが付与されます。 &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5 High Symbols: จะได้รับ Free Games Bonus ที่มีค่า 128 &lt;img src = '6' height=50 offset=5/&gt;  , 118 &lt;img src = '7' height=50 offset=5/&gt;, 108 &lt;img src = '8' height=50 offset=5/&gt;  , 98 &lt;img src = '9' height=50 offset=5/&gt;  หรือ 88 &lt;img src = '10' height=50 offset=5/&gt;  หรือ Top Up Bonus ที่มีค่า 88 &lt;img src = '10' height=50 offset=5/&gt; &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5 High Symbols: Free Games Bonus dengan nilai 128 &lt;img src = '6' height=50 offset=5/&gt; , 118 &lt;img src = '7' height=50 offset=5/&gt; , 108 &lt;img src = '8' height=50 offset=5/&gt; , 98 &lt;img src = '9' height=50 offset=5/&gt; , atau 88 &lt;img src = '10' height=50 offset=5/&gt; , atau Top Up Bonus dengan nilai 88 &lt;img src = '10' height=50 offset=5/&gt;  dianugerahkan. &lt;color=white&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;5 High Symbols: Một Free Games Bonus với giá trị 128 &lt;img src = '6' height=50 offset=5/&gt; , 118 &lt;img src = '7' height=50 offset=5/&gt; , 108 &lt;img src = '8' height=50 offset=5/&gt; , 98 &lt;img src = '9' height=50 offset=5/&gt; , hoặc 88 &lt;img src = '10' height=50 offset=5/&gt; , hoặc một Top Up Bonus với giá trị 88 &lt;img src = '10' height=50 offset=5/&gt;  được trao. &lt;color=white&gt;</t>
   </si>
 </sst>
 </file>
@@ -3978,7 +3978,7 @@
         <v>563</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -5635,7 +5635,7 @@
         <v>649</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="H64" s="4" t="s">
         <v>650</v>
@@ -5889,34 +5889,34 @@
         <v>457</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>712</v>
+        <v>735</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>713</v>
+        <v>736</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>714</v>
+        <v>737</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>715</v>
+        <v>738</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>716</v>
+        <v>739</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>717</v>
+        <v>740</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>718</v>
+        <v>741</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>712</v>
+        <v>735</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>719</v>
+        <v>742</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>720</v>
+        <v>743</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="90">
@@ -5927,34 +5927,34 @@
         <v>457</v>
       </c>
       <c r="C72" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="L72" s="4" t="s">
         <v>721</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>722</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>723</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>724</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>725</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>726</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>727</v>
-      </c>
-      <c r="J72" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="K72" s="4" t="s">
-        <v>729</v>
-      </c>
-      <c r="L72" s="4" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -6015,7 +6015,7 @@
         <v>679</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
       <c r="H74" s="4" t="s">
         <v>680</v>
@@ -6155,34 +6155,34 @@
         <v>457</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="D78" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="L78" s="4" t="s">
         <v>733</v>
-      </c>
-      <c r="E78" s="4" t="s">
-        <v>735</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>736</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>738</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>739</v>
-      </c>
-      <c r="J78" s="4" t="s">
-        <v>740</v>
-      </c>
-      <c r="K78" s="4" t="s">
-        <v>741</v>
-      </c>
-      <c r="L78" s="4" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="79" spans="1:12">
